--- a/thesis_experiment_program.xlsx
+++ b/thesis_experiment_program.xlsx
@@ -15,18 +15,40 @@
     <sheet name="Thesis_Map" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Dictionary_Validation" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Dashboard" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Claim_Ledger" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="AI_Usage_Log" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Ethics_Governance_Notes" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="List_Category">'Dictionary_Validation'!$A$3:$A$9</definedName>
     <definedName name="List_Evidential_Role">'Dictionary_Validation'!$B$3:$B$7</definedName>
-    <definedName name="List_Stage">'Dictionary_Validation'!$C$3:$C$8</definedName>
+    <definedName name="List_Stage">'Dictionary_Validation'!$C$3:$C$9</definedName>
     <definedName name="List_Priority">'Dictionary_Validation'!$D$3:$D$6</definedName>
     <definedName name="List_Status">'Dictionary_Validation'!$E$3:$E$8</definedName>
     <definedName name="List_Reporting_Destination">'Dictionary_Validation'!$F$3:$F$7</definedName>
     <definedName name="List_Reviewed">'Dictionary_Validation'!$G$3:$G$4</definedName>
     <definedName name="List_Used_in_Thesis">'Dictionary_Validation'!$H$3:$H$4</definedName>
     <definedName name="List_Freeze_Status">'Dictionary_Validation'!$I$3:$I$4</definedName>
+    <definedName name="List_Run_Type">'Dictionary_Validation'!$J$3:$J$7</definedName>
+    <definedName name="List_Affects_Frozen_Pipeline">'Dictionary_Validation'!$K$3:$K$4</definedName>
+    <definedName name="List_Eligible_for_Method_Decision">'Dictionary_Validation'!$L$3:$L$4</definedName>
+    <definedName name="List_Claim_Type">'Dictionary_Validation'!$M$3:$M$6</definedName>
+    <definedName name="List_Evidence_Status">'Dictionary_Validation'!$N$3:$N$5</definedName>
+    <definedName name="List_Writing_Location">'Dictionary_Validation'!$O$3:$O$6</definedName>
+    <definedName name="List_Human_Verification_Status">'Dictionary_Validation'!$P$3:$P$5</definedName>
+    <definedName name="List_Ethics_Status">'Dictionary_Validation'!$Q$3:$Q$5</definedName>
+    <definedName name="List_Ethics_Topic">'Dictionary_Validation'!$R$3:$R$8</definedName>
+    <definedName name="List_Required_for_Main_Claim">'Dictionary_Validation'!$S$3:$S$4</definedName>
+    <definedName name="List_Ready_for_Chapter_4">'Dictionary_Validation'!$T$3:$T$4</definedName>
+    <definedName name="List_YesNo">'Dictionary_Validation'!$U$3:$U$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master_Experiments'!$A$1:$AF$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Run_Log'!$A$1:$Y$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Decision_Log'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Confirmatory_Set'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Thesis_Map'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Claim_Ledger'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'AI_Usage_Log'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Ethics_Governance_Notes'!$A$1:$H$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -136,7 +158,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -272,9 +294,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RunLogTable" displayName="RunLogTable" ref="A1:V31" headerRowCount="1">
-  <autoFilter ref="A1:V31"/>
-  <tableColumns count="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RunLogTable" displayName="RunLogTable" ref="A1:Y41" headerRowCount="1">
+  <autoFilter ref="A1:Y41"/>
+  <tableColumns count="25">
     <tableColumn id="1" name="Run_ID"/>
     <tableColumn id="2" name="Experiment_ID"/>
     <tableColumn id="3" name="Run_Date"/>
@@ -287,55 +309,63 @@
     <tableColumn id="10" name="Split_ID_or_Fold_Definition"/>
     <tableColumn id="11" name="Model"/>
     <tableColumn id="12" name="Feature_Set"/>
-    <tableColumn id="13" name="Primary_Metric_Value"/>
-    <tableColumn id="14" name="Secondary_Metric_1"/>
-    <tableColumn id="15" name="Secondary_Metric_2"/>
-    <tableColumn id="16" name="Robustness_Output_Summary"/>
-    <tableColumn id="17" name="Result_Summary"/>
-    <tableColumn id="18" name="Preliminary_Interpretation"/>
-    <tableColumn id="19" name="Reviewed"/>
-    <tableColumn id="20" name="Used_in_Thesis"/>
-    <tableColumn id="21" name="Artifact_Path"/>
-    <tableColumn id="22" name="Notes"/>
+    <tableColumn id="13" name="Run_Type"/>
+    <tableColumn id="14" name="Affects_Frozen_Pipeline"/>
+    <tableColumn id="15" name="Eligible_for_Method_Decision"/>
+    <tableColumn id="16" name="Primary_Metric_Value"/>
+    <tableColumn id="17" name="Secondary_Metric_1"/>
+    <tableColumn id="18" name="Secondary_Metric_2"/>
+    <tableColumn id="19" name="Robustness_Output_Summary"/>
+    <tableColumn id="20" name="Result_Summary"/>
+    <tableColumn id="21" name="Preliminary_Interpretation"/>
+    <tableColumn id="22" name="Reviewed"/>
+    <tableColumn id="23" name="Used_in_Thesis"/>
+    <tableColumn id="24" name="Artifact_Path"/>
+    <tableColumn id="25" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:L9" headerRowCount="1">
-  <autoFilter ref="A1:L9"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:N9" headerRowCount="1">
+  <autoFilter ref="A1:N9"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="Decision_ID"/>
     <tableColumn id="2" name="Decision_Topic"/>
     <tableColumn id="3" name="Stage"/>
     <tableColumn id="4" name="Candidate_Options"/>
     <tableColumn id="5" name="Evidence_Experiments"/>
-    <tableColumn id="6" name="Chosen_Option"/>
-    <tableColumn id="7" name="Why_Chosen"/>
-    <tableColumn id="8" name="Why_Not_Others"/>
-    <tableColumn id="9" name="Risks_or_Tradeoffs"/>
-    <tableColumn id="10" name="Date_Locked"/>
-    <tableColumn id="11" name="Freeze_Status"/>
-    <tableColumn id="12" name="Thesis_Use"/>
+    <tableColumn id="6" name="Decision_Criteria"/>
+    <tableColumn id="7" name="Chosen_Option"/>
+    <tableColumn id="8" name="Why_Chosen"/>
+    <tableColumn id="9" name="Why_Not_Others"/>
+    <tableColumn id="10" name="Risks_or_Tradeoffs"/>
+    <tableColumn id="11" name="Grounding_Section_or_Source_Packet"/>
+    <tableColumn id="12" name="Date_Locked"/>
+    <tableColumn id="13" name="Freeze_Status"/>
+    <tableColumn id="14" name="Thesis_Use"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ConfirmatoryTable" displayName="ConfirmatoryTable" ref="A1:I6" headerRowCount="1">
-  <autoFilter ref="A1:I6"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ConfirmatoryTable" displayName="ConfirmatoryTable" ref="A1:L6" headerRowCount="1">
+  <autoFilter ref="A1:L6"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Experiment_ID"/>
     <tableColumn id="2" name="Short_Title"/>
     <tableColumn id="3" name="Final_Pipeline_Version"/>
     <tableColumn id="4" name="Claim_Supported"/>
     <tableColumn id="5" name="Status"/>
-    <tableColumn id="6" name="Main_Result_Summary"/>
-    <tableColumn id="7" name="Robustness_Status"/>
-    <tableColumn id="8" name="Ready_for_Chapter_4"/>
-    <tableColumn id="9" name="Confirmatory_Eligible"/>
+    <tableColumn id="6" name="Eligible_to_Run"/>
+    <tableColumn id="7" name="Completed"/>
+    <tableColumn id="8" name="Required_for_Main_Claim"/>
+    <tableColumn id="9" name="Ready_for_Chapter_4"/>
+    <tableColumn id="10" name="Confirmatory_Eligible"/>
+    <tableColumn id="11" name="Main_Result_Summary"/>
+    <tableColumn id="12" name="Robustness_Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -355,6 +385,59 @@
     <tableColumn id="8" name="Notes_for_Writing"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ClaimLedgerTable" displayName="ClaimLedgerTable" ref="A1:H31" headerRowCount="1">
+  <autoFilter ref="A1:H31"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Claim_ID"/>
+    <tableColumn id="2" name="Claim_Text"/>
+    <tableColumn id="3" name="Claim_Type"/>
+    <tableColumn id="4" name="Supported_By_Experiments"/>
+    <tableColumn id="5" name="Evidence_Status"/>
+    <tableColumn id="6" name="Writing_Location"/>
+    <tableColumn id="7" name="Interpretation_Limit"/>
+    <tableColumn id="8" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="AIUsageTable" displayName="AIUsageTable" ref="A1:J41" headerRowCount="1">
+  <autoFilter ref="A1:J41"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Entry_ID"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="Task"/>
+    <tableColumn id="4" name="Tool"/>
+    <tableColumn id="5" name="Input_Summary"/>
+    <tableColumn id="6" name="Output_Summary"/>
+    <tableColumn id="7" name="What_Was_Adopted"/>
+    <tableColumn id="8" name="Human_Verification_Status"/>
+    <tableColumn id="9" name="Thesis_Use"/>
+    <tableColumn id="10" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="EthicsTable" displayName="EthicsTable" ref="A1:H31" headerRowCount="1">
+  <autoFilter ref="A1:H31"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Note_ID"/>
+    <tableColumn id="2" name="Experiment_ID_or_Decision_ID"/>
+    <tableColumn id="3" name="Topic"/>
+    <tableColumn id="4" name="Risk_or_Concern"/>
+    <tableColumn id="5" name="Mitigation_or_Response"/>
+    <tableColumn id="6" name="Thesis_Section"/>
+    <tableColumn id="7" name="Status"/>
+    <tableColumn id="8" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -647,23 +730,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Thesis Experiment Program Workbook</t>
+          <t>Thesis Experiment Program Workbook (v2)</t>
         </is>
       </c>
     </row>
@@ -675,7 +759,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Scientific control workbook for pre-interpretation experiment specification, traceable decision locking, leakage-aware execution, and thesis reporting alignment.</t>
+          <t>Scientific control system for thesis experiment governance: pre-interpretation design, lock tracking, leakage-aware execution traceability, and chapter-ready evidence mapping.</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -684,6 +768,7 @@
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
@@ -694,16 +779,17 @@
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Rules of use</t>
+          <t>Evidence tiers</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>One exact question per experiment. One manipulated factor unless justified. Define split logic and leakage controls before running. No interpretation before criteria are specified.</t>
+          <t>Primary confirmatory; Primary-supporting robustness; Secondary decision-support; Exploratory extension. Each tier has explicit interpretation boundaries.</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -712,6 +798,7 @@
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -722,16 +809,17 @@
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Evidential tiers</t>
+          <t>Stage system</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Primary confirmatory; Primary-supporting robustness; Secondary decision-support; Exploratory extension.</t>
+          <t>Stage 1 Target lock -&gt; Stage 2 Split lock -&gt; Stage 3 Model lock -&gt; Stage 4 Feature/preprocessing lock -&gt; Stage 5 Confirmatory analysis -&gt; Stage 6 Robustness analysis -&gt; Stage 7 Exploratory extension.</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -740,6 +828,7 @@
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
@@ -750,6 +839,7 @@
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -759,7 +849,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Confirmatory claims require locked decisions (target, split, model, weighting, tuning, feature representation, scaling) in Decision_Log.</t>
+          <t>Confirmatory eligibility requires D01-D07 locked in Decision_Log. Chapter 4 readiness additionally requires required confirmatory/supporting items completed and marked Ready_for_Chapter_4=YES.</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -768,6 +858,7 @@
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -778,16 +869,17 @@
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Color legend</t>
+          <t>Governance additions</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Green: confirmatory/locked/YES. Orange: exploratory/open. Yellow: critical priority. Gray: dropped. Red: missing required setup.</t>
+          <t>Claim_Ledger enforces claim discipline. AI_Usage_Log supports tool transparency and human verification traceability. Ethics_Governance_Notes supports risk/mitigation accountability.</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -796,6 +888,7 @@
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -806,6 +899,7 @@
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -815,7 +909,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Master_Experiments -&gt; Run_Log -&gt; Decision_Log -&gt; Confirmatory_Set -&gt; Thesis_Map -&gt; Dashboard.</t>
+          <t>Master_Experiments -&gt; Run_Log -&gt; Decision_Log -&gt; Confirmatory_Set -&gt; Claim_Ledger/AI_Usage_Log/Ethics_Governance_Notes -&gt; Thesis_Map -&gt; Dashboard.</t>
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
@@ -824,6 +918,7 @@
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -834,11 +929,12 @@
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Use this workbook as the single source of truth for thesis experiment planning, locking, and chapter mapping.</t>
+          <t>This workbook is aligned to thesis method-choice/method-application workflow and reporting governance requirements.</t>
         </is>
       </c>
     </row>
@@ -846,22 +942,1046 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Generated by create_thesis_experiment_workbook.py</t>
+          <t>Generated by create_thesis_experiment_workbook.py (v2)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A22:H23"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B9:H10"/>
-    <mergeCell ref="B18:H19"/>
-    <mergeCell ref="B3:H4"/>
-    <mergeCell ref="B12:H13"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B15:H16"/>
+    <mergeCell ref="B9:I10"/>
+    <mergeCell ref="B12:I13"/>
+    <mergeCell ref="B18:I19"/>
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B6:I7"/>
+    <mergeCell ref="B15:I16"/>
+    <mergeCell ref="A22:I23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Entry_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Input_Summary</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Output_Summary</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>What_Was_Adopted</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Human_Verification_Status</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Thesis_Use</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>AI001</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>GPT-5.3-Codex</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Workbook package revision and governance alignment</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Not reviewed</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J41"/>
+  <dataValidations count="2">
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Human_Verification_Status</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Used_in_Thesis</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Note_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Experiment_ID_or_Decision_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Risk_or_Concern</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Mitigation_or_Response</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Thesis_Section</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>EN01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Interpretation limits</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Risk of over-claiming confirmatory evidence beyond split/domain scope</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Enforce interpretation boundaries in Claim_Ledger and Chapter 5 limitations</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 5</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>EN02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>AI/tool transparency</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Insufficient traceability of AI-assisted drafting decisions</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Maintain AI_Usage_Log with human verification status before thesis inclusion</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Chapter 2/Appendix</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H31"/>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Ethics_Topic</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Ethics_Status</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -878,25 +1998,25 @@
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="36" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="34" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="36" customWidth="1" min="23" max="23"/>
     <col width="34" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
     <col width="36" customWidth="1" min="26" max="26"/>
@@ -1093,7 +2213,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 1 - Target lock</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
@@ -1123,12 +2243,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -1138,22 +2258,22 @@
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>within_subject_loso_session (primary) with frozen transfer as secondary stress context.</t>
+          <t>within_subject_loso_session for primary comparison; frozen transfer as secondary check</t>
         </is>
       </c>
       <c r="O2" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P2" s="8" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q2" s="8" t="inlineStr">
         <is>
-          <t>ridge fixed baseline.</t>
+          <t>ridge baseline unless model family is manipulated.</t>
         </is>
       </c>
       <c r="R2" s="8" t="inlineStr">
@@ -1168,7 +2288,7 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U2" s="8" t="inlineStr">
@@ -1178,17 +2298,17 @@
       </c>
       <c r="V2" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W2" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X2" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y2" s="8" t="inlineStr">
@@ -1198,7 +2318,7 @@
       </c>
       <c r="Z2" s="8" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA2" s="8" t="inlineStr">
@@ -1215,7 +2335,7 @@
       <c r="AD2" s="8" t="inlineStr"/>
       <c r="AE2" s="8" t="inlineStr"/>
       <c r="AF2" s="8">
-        <f>IF($AA2="Dropped","N/A",IF(AND($H2&lt;&gt;"",$J2&lt;&gt;"",$K2&lt;&gt;"",$M2&lt;&gt;"",$N2&lt;&gt;"",$P2&lt;&gt;"",$Q2&lt;&gt;"",$Y2&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA2="Dropped","N/A",IF(AND($H2&lt;&gt;"",$J2&lt;&gt;"",$K2&lt;&gt;"",$M2&lt;&gt;"",$N2&lt;&gt;"",$P2&lt;&gt;"",$R2&lt;&gt;"",$U2&lt;&gt;"",$V2&lt;&gt;"",$W2&lt;&gt;"",$Z2&lt;&gt;"",$Y2&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -1242,7 +2362,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 1 - Target lock</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1262,7 +2382,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1272,32 +2392,32 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -1317,27 +2437,27 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -1347,7 +2467,7 @@
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
@@ -1364,7 +2484,7 @@
       <c r="AD3" s="3" t="inlineStr"/>
       <c r="AE3" s="3" t="inlineStr"/>
       <c r="AF3" s="3">
-        <f>IF($AA3="Dropped","N/A",IF(AND($H3&lt;&gt;"",$J3&lt;&gt;"",$K3&lt;&gt;"",$M3&lt;&gt;"",$N3&lt;&gt;"",$P3&lt;&gt;"",$Q3&lt;&gt;"",$Y3&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA3="Dropped","N/A",IF(AND($H3&lt;&gt;"",$J3&lt;&gt;"",$K3&lt;&gt;"",$M3&lt;&gt;"",$N3&lt;&gt;"",$P3&lt;&gt;"",$R3&lt;&gt;"",$U3&lt;&gt;"",$V3&lt;&gt;"",$W3&lt;&gt;"",$Z3&lt;&gt;"",$Y3&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -1391,7 +2511,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 1 - Target lock</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -1411,7 +2531,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -1421,32 +2541,32 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q4" s="8" t="inlineStr">
@@ -1466,27 +2586,27 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U4" s="8" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V4" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W4" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X4" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y4" s="8" t="inlineStr">
@@ -1496,7 +2616,7 @@
       </c>
       <c r="Z4" s="8" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA4" s="8" t="inlineStr">
@@ -1513,7 +2633,7 @@
       <c r="AD4" s="8" t="inlineStr"/>
       <c r="AE4" s="8" t="inlineStr"/>
       <c r="AF4" s="8">
-        <f>IF($AA4="Dropped","N/A",IF(AND($H4&lt;&gt;"",$J4&lt;&gt;"",$K4&lt;&gt;"",$M4&lt;&gt;"",$N4&lt;&gt;"",$P4&lt;&gt;"",$Q4&lt;&gt;"",$Y4&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA4="Dropped","N/A",IF(AND($H4&lt;&gt;"",$J4&lt;&gt;"",$K4&lt;&gt;"",$M4&lt;&gt;"",$N4&lt;&gt;"",$P4&lt;&gt;"",$R4&lt;&gt;"",$U4&lt;&gt;"",$V4&lt;&gt;"",$W4&lt;&gt;"",$Z4&lt;&gt;"",$Y4&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -1540,7 +2660,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 2 - Split lock</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1560,7 +2680,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1570,17 +2690,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1590,12 +2710,12 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>High under weak splits.</t>
+          <t>High under weak splits</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1615,27 +2735,27 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Retain strictest split matching claim; weaker splits only as inflation demonstrations.</t>
+          <t>Retain strictest split matching claim; weaker splits only as inflation/leakage demonstrations.</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1645,7 +2765,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1662,7 +2782,7 @@
       <c r="AD5" s="3" t="inlineStr"/>
       <c r="AE5" s="3" t="inlineStr"/>
       <c r="AF5" s="3">
-        <f>IF($AA5="Dropped","N/A",IF(AND($H5&lt;&gt;"",$J5&lt;&gt;"",$K5&lt;&gt;"",$M5&lt;&gt;"",$N5&lt;&gt;"",$P5&lt;&gt;"",$Q5&lt;&gt;"",$Y5&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA5="Dropped","N/A",IF(AND($H5&lt;&gt;"",$J5&lt;&gt;"",$K5&lt;&gt;"",$M5&lt;&gt;"",$N5&lt;&gt;"",$P5&lt;&gt;"",$R5&lt;&gt;"",$U5&lt;&gt;"",$V5&lt;&gt;"",$W5&lt;&gt;"",$Z5&lt;&gt;"",$Y5&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +2809,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 2 - Split lock</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1699,7 +2819,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Cross-person framing</t>
+          <t>Cross-person transfer framing</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -1709,7 +2829,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1719,17 +2839,17 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr">
@@ -1739,12 +2859,12 @@
       </c>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>Fit once on train subject only; no re-fit/re-tune on test subject.</t>
+          <t>Fit only on train subject; no test subject re-fit/re-tune</t>
         </is>
       </c>
       <c r="Q6" s="8" t="inlineStr">
@@ -1764,7 +2884,7 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U6" s="8" t="inlineStr">
@@ -1774,17 +2894,17 @@
       </c>
       <c r="V6" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W6" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X6" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y6" s="8" t="inlineStr">
@@ -1794,7 +2914,7 @@
       </c>
       <c r="Z6" s="8" t="inlineStr">
         <is>
-          <t>Transfer evidence under domain shift, not population generalization.</t>
+          <t>Transfer evidence under domain shift, not population-level generalization.</t>
         </is>
       </c>
       <c r="AA6" s="8" t="inlineStr">
@@ -1811,7 +2931,7 @@
       <c r="AD6" s="8" t="inlineStr"/>
       <c r="AE6" s="8" t="inlineStr"/>
       <c r="AF6" s="8">
-        <f>IF($AA6="Dropped","N/A",IF(AND($H6&lt;&gt;"",$J6&lt;&gt;"",$K6&lt;&gt;"",$M6&lt;&gt;"",$N6&lt;&gt;"",$P6&lt;&gt;"",$Q6&lt;&gt;"",$Y6&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA6="Dropped","N/A",IF(AND($H6&lt;&gt;"",$J6&lt;&gt;"",$K6&lt;&gt;"",$M6&lt;&gt;"",$N6&lt;&gt;"",$P6&lt;&gt;"",$R6&lt;&gt;"",$U6&lt;&gt;"",$V6&lt;&gt;"",$W6&lt;&gt;"",$Z6&lt;&gt;"",$Y6&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -1838,7 +2958,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 3 - Model lock</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1848,17 +2968,17 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Final model family lock</t>
+          <t>Model family lock</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Which linear model is most appropriate: ridge, logistic regression, or linear SVM?</t>
+          <t>Which linear model is the most appropriate default: ridge, logistic regression, or linear SVM?</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1868,32 +2988,32 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1913,27 +3033,27 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Prefer simplest model with comparable performance and better robustness/stability.</t>
+          <t>Prefer simplest model with comparable predictive performance and better robustness/stability.</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1943,7 +3063,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1960,7 +3080,7 @@
       <c r="AD7" s="3" t="inlineStr"/>
       <c r="AE7" s="3" t="inlineStr"/>
       <c r="AF7" s="3">
-        <f>IF($AA7="Dropped","N/A",IF(AND($H7&lt;&gt;"",$J7&lt;&gt;"",$K7&lt;&gt;"",$M7&lt;&gt;"",$N7&lt;&gt;"",$P7&lt;&gt;"",$Q7&lt;&gt;"",$Y7&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA7="Dropped","N/A",IF(AND($H7&lt;&gt;"",$J7&lt;&gt;"",$K7&lt;&gt;"",$M7&lt;&gt;"",$N7&lt;&gt;"",$P7&lt;&gt;"",$R7&lt;&gt;"",$U7&lt;&gt;"",$V7&lt;&gt;"",$W7&lt;&gt;"",$Z7&lt;&gt;"",$Y7&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -1987,7 +3107,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 3 - Model lock</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2002,12 +3122,12 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Does class weighting improve fairness across classes without instability?</t>
+          <t>Does class weighting improve fairness across classes without creating instability?</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -2017,32 +3137,32 @@
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P8" s="8" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
@@ -2062,27 +3182,27 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U8" s="8" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V8" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W8" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X8" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y8" s="8" t="inlineStr">
@@ -2092,7 +3212,7 @@
       </c>
       <c r="Z8" s="8" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA8" s="8" t="inlineStr">
@@ -2109,7 +3229,7 @@
       <c r="AD8" s="8" t="inlineStr"/>
       <c r="AE8" s="8" t="inlineStr"/>
       <c r="AF8" s="8">
-        <f>IF($AA8="Dropped","N/A",IF(AND($H8&lt;&gt;"",$J8&lt;&gt;"",$K8&lt;&gt;"",$M8&lt;&gt;"",$N8&lt;&gt;"",$P8&lt;&gt;"",$Q8&lt;&gt;"",$Y8&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA8="Dropped","N/A",IF(AND($H8&lt;&gt;"",$J8&lt;&gt;"",$K8&lt;&gt;"",$M8&lt;&gt;"",$N8&lt;&gt;"",$P8&lt;&gt;"",$R8&lt;&gt;"",$U8&lt;&gt;"",$V8&lt;&gt;"",$W8&lt;&gt;"",$Z8&lt;&gt;"",$Y8&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -2136,7 +3256,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 3 - Model lock</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2156,7 +3276,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2166,32 +3286,32 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2211,27 +3331,27 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Keep fixed settings unless nested tuning gives clear, stable gain.</t>
+          <t>Keep fixed settings unless nested tuning yields a clear and stable gain.</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2241,7 +3361,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -2258,7 +3378,7 @@
       <c r="AD9" s="3" t="inlineStr"/>
       <c r="AE9" s="3" t="inlineStr"/>
       <c r="AF9" s="3">
-        <f>IF($AA9="Dropped","N/A",IF(AND($H9&lt;&gt;"",$J9&lt;&gt;"",$K9&lt;&gt;"",$M9&lt;&gt;"",$N9&lt;&gt;"",$P9&lt;&gt;"",$Q9&lt;&gt;"",$Y9&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA9="Dropped","N/A",IF(AND($H9&lt;&gt;"",$J9&lt;&gt;"",$K9&lt;&gt;"",$M9&lt;&gt;"",$N9&lt;&gt;"",$P9&lt;&gt;"",$R9&lt;&gt;"",$U9&lt;&gt;"",$V9&lt;&gt;"",$W9&lt;&gt;"",$Z9&lt;&gt;"",$Y9&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -2285,7 +3405,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 4 - Feature/preprocessing lock</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -2300,12 +3420,12 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Should primary representation remain whole-brain masked voxels or use theory-justified ROIs?</t>
+          <t>Should the primary representation remain whole-brain masked voxels or use theory-justified ROIs?</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -2315,32 +3435,32 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P10" s="8" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q10" s="8" t="inlineStr">
@@ -2360,27 +3480,27 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V10" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W10" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X10" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y10" s="8" t="inlineStr">
@@ -2390,7 +3510,7 @@
       </c>
       <c r="Z10" s="8" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA10" s="8" t="inlineStr">
@@ -2407,7 +3527,7 @@
       <c r="AD10" s="8" t="inlineStr"/>
       <c r="AE10" s="8" t="inlineStr"/>
       <c r="AF10" s="8">
-        <f>IF($AA10="Dropped","N/A",IF(AND($H10&lt;&gt;"",$J10&lt;&gt;"",$K10&lt;&gt;"",$M10&lt;&gt;"",$N10&lt;&gt;"",$P10&lt;&gt;"",$Q10&lt;&gt;"",$Y10&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA10="Dropped","N/A",IF(AND($H10&lt;&gt;"",$J10&lt;&gt;"",$K10&lt;&gt;"",$M10&lt;&gt;"",$N10&lt;&gt;"",$P10&lt;&gt;"",$R10&lt;&gt;"",$U10&lt;&gt;"",$V10&lt;&gt;"",$W10&lt;&gt;"",$Z10&lt;&gt;"",$Y10&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -2434,7 +3554,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 4 - Feature/preprocessing lock</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2449,12 +3569,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Does unsupervised dimensionality reduction improve performance or stability enough to justify complexity?</t>
+          <t>Does unsupervised dimensionality reduction improve performance or stability enough to justify added complexity?</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2464,32 +3584,32 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2509,27 +3629,27 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2539,7 +3659,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -2556,7 +3676,7 @@
       <c r="AD11" s="3" t="inlineStr"/>
       <c r="AE11" s="3" t="inlineStr"/>
       <c r="AF11" s="3">
-        <f>IF($AA11="Dropped","N/A",IF(AND($H11&lt;&gt;"",$J11&lt;&gt;"",$K11&lt;&gt;"",$M11&lt;&gt;"",$N11&lt;&gt;"",$P11&lt;&gt;"",$Q11&lt;&gt;"",$Y11&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA11="Dropped","N/A",IF(AND($H11&lt;&gt;"",$J11&lt;&gt;"",$K11&lt;&gt;"",$M11&lt;&gt;"",$N11&lt;&gt;"",$P11&lt;&gt;"",$R11&lt;&gt;"",$U11&lt;&gt;"",$V11&lt;&gt;"",$W11&lt;&gt;"",$Z11&lt;&gt;"",$Y11&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -2583,7 +3703,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 4 - Feature/preprocessing lock</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2598,12 +3718,12 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>How sensitive are results to scaling strategy?</t>
+          <t>How sensitive are the results to scaling strategy?</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -2613,32 +3733,32 @@
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O12" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P12" s="8" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q12" s="8" t="inlineStr">
@@ -2658,27 +3778,27 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U12" s="8" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V12" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W12" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y12" s="8" t="inlineStr">
@@ -2688,7 +3808,7 @@
       </c>
       <c r="Z12" s="8" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA12" s="8" t="inlineStr">
@@ -2705,7 +3825,7 @@
       <c r="AD12" s="8" t="inlineStr"/>
       <c r="AE12" s="8" t="inlineStr"/>
       <c r="AF12" s="8">
-        <f>IF($AA12="Dropped","N/A",IF(AND($H12&lt;&gt;"",$J12&lt;&gt;"",$K12&lt;&gt;"",$M12&lt;&gt;"",$N12&lt;&gt;"",$P12&lt;&gt;"",$Q12&lt;&gt;"",$Y12&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA12="Dropped","N/A",IF(AND($H12&lt;&gt;"",$J12&lt;&gt;"",$K12&lt;&gt;"",$M12&lt;&gt;"",$N12&lt;&gt;"",$P12&lt;&gt;"",$R12&lt;&gt;"",$U12&lt;&gt;"",$V12&lt;&gt;"",$W12&lt;&gt;"",$Z12&lt;&gt;"",$Y12&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -2732,7 +3852,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Stage 2 - Robustness support</t>
+          <t>Stage 6 - Robustness analysis</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2742,17 +3862,17 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Chance-level distinguishability</t>
+          <t>Chance-level distinguishability support</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Are main predictive results distinguishable from chance under exact same split logic?</t>
+          <t>Are the main predictive results distinguishable from chance under the exact same split logic?</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2762,32 +3882,32 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Exact confirmatory split logic with train-only permutation.</t>
+          <t>exact confirmatory split logic with train-only permutation</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2807,27 +3927,27 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -2837,7 +3957,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2854,7 +3974,7 @@
       <c r="AD13" s="3" t="inlineStr"/>
       <c r="AE13" s="3" t="inlineStr"/>
       <c r="AF13" s="3">
-        <f>IF($AA13="Dropped","N/A",IF(AND($H13&lt;&gt;"",$J13&lt;&gt;"",$K13&lt;&gt;"",$M13&lt;&gt;"",$N13&lt;&gt;"",$P13&lt;&gt;"",$Q13&lt;&gt;"",$Y13&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA13="Dropped","N/A",IF(AND($H13&lt;&gt;"",$J13&lt;&gt;"",$K13&lt;&gt;"",$M13&lt;&gt;"",$N13&lt;&gt;"",$P13&lt;&gt;"",$R13&lt;&gt;"",$U13&lt;&gt;"",$V13&lt;&gt;"",$W13&lt;&gt;"",$Z13&lt;&gt;"",$Y13&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -2881,7 +4001,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Stage 2 - Robustness support</t>
+          <t>Stage 6 - Robustness analysis</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -2891,7 +4011,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Non-trivial signal check</t>
+          <t>Non-trivial predictive value support</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -2901,7 +4021,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -2911,32 +4031,32 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O14" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P14" s="8" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q14" s="8" t="inlineStr">
@@ -2956,27 +4076,27 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U14" s="8" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V14" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X14" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y14" s="8" t="inlineStr">
@@ -2986,7 +4106,7 @@
       </c>
       <c r="Z14" s="8" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA14" s="8" t="inlineStr">
@@ -3003,7 +4123,7 @@
       <c r="AD14" s="8" t="inlineStr"/>
       <c r="AE14" s="8" t="inlineStr"/>
       <c r="AF14" s="8">
-        <f>IF($AA14="Dropped","N/A",IF(AND($H14&lt;&gt;"",$J14&lt;&gt;"",$K14&lt;&gt;"",$M14&lt;&gt;"",$N14&lt;&gt;"",$P14&lt;&gt;"",$Q14&lt;&gt;"",$Y14&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA14="Dropped","N/A",IF(AND($H14&lt;&gt;"",$J14&lt;&gt;"",$K14&lt;&gt;"",$M14&lt;&gt;"",$N14&lt;&gt;"",$P14&lt;&gt;"",$R14&lt;&gt;"",$U14&lt;&gt;"",$V14&lt;&gt;"",$W14&lt;&gt;"",$Z14&lt;&gt;"",$Y14&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -3030,7 +4150,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Stage 2 - Robustness support</t>
+          <t>Stage 6 - Robustness analysis</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -3050,7 +4170,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -3060,32 +4180,32 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3105,27 +4225,27 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3135,7 +4255,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>Model-behavior evidence only; no localization claims.</t>
+          <t>Model-behavior evidence only; not direct neural localization.</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -3152,7 +4272,7 @@
       <c r="AD15" s="3" t="inlineStr"/>
       <c r="AE15" s="3" t="inlineStr"/>
       <c r="AF15" s="3">
-        <f>IF($AA15="Dropped","N/A",IF(AND($H15&lt;&gt;"",$J15&lt;&gt;"",$K15&lt;&gt;"",$M15&lt;&gt;"",$N15&lt;&gt;"",$P15&lt;&gt;"",$Q15&lt;&gt;"",$Y15&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA15="Dropped","N/A",IF(AND($H15&lt;&gt;"",$J15&lt;&gt;"",$K15&lt;&gt;"",$M15&lt;&gt;"",$N15&lt;&gt;"",$P15&lt;&gt;"",$R15&lt;&gt;"",$U15&lt;&gt;"",$V15&lt;&gt;"",$W15&lt;&gt;"",$Z15&lt;&gt;"",$Y15&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -3179,7 +4299,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Stage 2 - Robustness support</t>
+          <t>Stage 6 - Robustness analysis</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -3194,12 +4314,12 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Do main conclusions depend excessively on one subset such as one task or modality?</t>
+          <t>Do the main conclusions depend excessively on one subset, such as one task or modality?</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -3209,32 +4329,32 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O16" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q16" s="8" t="inlineStr">
@@ -3254,27 +4374,27 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V16" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W16" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X16" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y16" s="8" t="inlineStr">
@@ -3284,7 +4404,7 @@
       </c>
       <c r="Z16" s="8" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA16" s="8" t="inlineStr">
@@ -3301,7 +4421,7 @@
       <c r="AD16" s="8" t="inlineStr"/>
       <c r="AE16" s="8" t="inlineStr"/>
       <c r="AF16" s="8">
-        <f>IF($AA16="Dropped","N/A",IF(AND($H16&lt;&gt;"",$J16&lt;&gt;"",$K16&lt;&gt;"",$M16&lt;&gt;"",$N16&lt;&gt;"",$P16&lt;&gt;"",$Q16&lt;&gt;"",$Y16&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA16="Dropped","N/A",IF(AND($H16&lt;&gt;"",$J16&lt;&gt;"",$K16&lt;&gt;"",$M16&lt;&gt;"",$N16&lt;&gt;"",$P16&lt;&gt;"",$R16&lt;&gt;"",$U16&lt;&gt;"",$V16&lt;&gt;"",$W16&lt;&gt;"",$Z16&lt;&gt;"",$Y16&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -3328,7 +4448,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Stage 3 - Confirmatory core</t>
+          <t>Stage 5 - Confirmatory analysis</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -3338,7 +4458,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Primary evidential core</t>
+          <t>Primary confirmatory claim</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -3348,7 +4468,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -3358,12 +4478,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -3378,12 +4498,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3403,7 +4523,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -3413,17 +4533,17 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -3433,7 +4553,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -3450,7 +4570,7 @@
       <c r="AD17" s="3" t="inlineStr"/>
       <c r="AE17" s="3" t="inlineStr"/>
       <c r="AF17" s="3">
-        <f>IF($AA17="Dropped","N/A",IF(AND($H17&lt;&gt;"",$J17&lt;&gt;"",$K17&lt;&gt;"",$M17&lt;&gt;"",$N17&lt;&gt;"",$P17&lt;&gt;"",$Q17&lt;&gt;"",$Y17&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA17="Dropped","N/A",IF(AND($H17&lt;&gt;"",$J17&lt;&gt;"",$K17&lt;&gt;"",$M17&lt;&gt;"",$N17&lt;&gt;"",$P17&lt;&gt;"",$R17&lt;&gt;"",$U17&lt;&gt;"",$V17&lt;&gt;"",$W17&lt;&gt;"",$Z17&lt;&gt;"",$Y17&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -3477,7 +4597,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Stage 3 - Confirmatory core</t>
+          <t>Stage 5 - Confirmatory analysis</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -3487,17 +4607,17 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Secondary confirmatory transfer evidence</t>
+          <t>Secondary confirmatory transfer claim</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Does final locked pipeline transfer meaningfully across individuals under frozen directional transfer?</t>
+          <t>Does the final locked pipeline transfer meaningfully across individuals under frozen directional transfer?</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -3507,12 +4627,12 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>Internal repeated-session BAS2 dataset (sub-001, sub-002) unless explicitly external.</t>
+          <t>Internal repeated-session BAS2 dataset (sub-001 and sub-002) unless explicitly external.</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -3522,17 +4642,17 @@
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>frozen_cross_person_transfer (both directions)</t>
+          <t>frozen_cross_person_transfer both directions</t>
         </is>
       </c>
       <c r="O18" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q18" s="8" t="inlineStr">
@@ -3552,7 +4672,7 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -3562,17 +4682,17 @@
       </c>
       <c r="V18" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y18" s="8" t="inlineStr">
@@ -3582,7 +4702,7 @@
       </c>
       <c r="Z18" s="8" t="inlineStr">
         <is>
-          <t>Not population-level generalization.</t>
+          <t>Directional transfer evidence only; not population-level generalization.</t>
         </is>
       </c>
       <c r="AA18" s="8" t="inlineStr">
@@ -3599,7 +4719,7 @@
       <c r="AD18" s="8" t="inlineStr"/>
       <c r="AE18" s="8" t="inlineStr"/>
       <c r="AF18" s="8">
-        <f>IF($AA18="Dropped","N/A",IF(AND($H18&lt;&gt;"",$J18&lt;&gt;"",$K18&lt;&gt;"",$M18&lt;&gt;"",$N18&lt;&gt;"",$P18&lt;&gt;"",$Q18&lt;&gt;"",$Y18&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA18="Dropped","N/A",IF(AND($H18&lt;&gt;"",$J18&lt;&gt;"",$K18&lt;&gt;"",$M18&lt;&gt;"",$N18&lt;&gt;"",$P18&lt;&gt;"",$R18&lt;&gt;"",$U18&lt;&gt;"",$V18&lt;&gt;"",$W18&lt;&gt;"",$Z18&lt;&gt;"",$Y18&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -3626,7 +4746,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Stage 4 - External exploratory</t>
+          <t>Stage 7 - Exploratory extension</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3636,17 +4756,17 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>External split-consistency check</t>
+          <t>External split-consistency exploration</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Does same leakage-aware split logic materially affect conclusions on compatible external open-source data?</t>
+          <t>Does the same leakage-aware split logic materially affect conclusions on a compatible external open-source dataset?</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3656,32 +4776,32 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>External open-source dataset if available/approved</t>
+          <t>External open-source dataset if available and approved</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -3701,27 +4821,27 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -3731,7 +4851,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3748,7 +4868,7 @@
       <c r="AD19" s="3" t="inlineStr"/>
       <c r="AE19" s="3" t="inlineStr"/>
       <c r="AF19" s="3">
-        <f>IF($AA19="Dropped","N/A",IF(AND($H19&lt;&gt;"",$J19&lt;&gt;"",$K19&lt;&gt;"",$M19&lt;&gt;"",$N19&lt;&gt;"",$P19&lt;&gt;"",$Q19&lt;&gt;"",$Y19&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA19="Dropped","N/A",IF(AND($H19&lt;&gt;"",$J19&lt;&gt;"",$K19&lt;&gt;"",$M19&lt;&gt;"",$N19&lt;&gt;"",$P19&lt;&gt;"",$R19&lt;&gt;"",$U19&lt;&gt;"",$V19&lt;&gt;"",$W19&lt;&gt;"",$Z19&lt;&gt;"",$Y19&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -3775,7 +4895,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Stage 4 - External exploratory</t>
+          <t>Stage 7 - Exploratory extension</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -3785,17 +4905,17 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>External model-ranking portability check</t>
+          <t>External model portability exploration</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Does relative ranking of reasonable model choices remain similar on external data?</t>
+          <t>Does the relative ranking of reasonable model choices remain similar on external data?</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Evaluate under leakage-aware splits before interpretation.</t>
+          <t>Evaluate under leakage-aware claim-matched split logic before interpretation.</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -3805,32 +4925,32 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Data index version, preprocessing order, metric definitions, seed policy.</t>
+          <t>Dataset index version, train-only fitting policy, metric definitions, seed policy, artifact schema.</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>External open-source dataset if available/approved</t>
+          <t>External open-source dataset if available and approved</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>coarse_affect unless this experiment manipulates target definition.</t>
+          <t>coarse_affect unless this experiment manipulates target granularity.</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Claim-matched leakage-safe split (within_subject_loso_session unless manipulated).</t>
+          <t>Claim-matched leakage-safe split strategy.</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>Performance inflation if split logic or fit scope leaks train-test information.</t>
+          <t>Performance inflation if split logic or fit scope leaks train/test information.</t>
         </is>
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>Use explicit split manifests and train-only fitting; frozen transfer for cross-person runs.</t>
+          <t>Predefined split manifests, train-only fitting, frozen transfer where applicable, no test-driven tuning.</t>
         </is>
       </c>
       <c r="Q20" s="8" t="inlineStr">
@@ -3850,27 +4970,27 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>Fold-level stability checks and leakage stress checks where relevant.</t>
+          <t>Fold-level checks and stress controls where relevant.</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>Pre-specified criterion set before interpretation.</t>
+          <t>Pre-specified criterion recorded before interpretation.</t>
         </is>
       </c>
       <c r="V20" s="8" t="inlineStr">
         <is>
-          <t>Stable claim-matched behavior with no leakage indicators.</t>
+          <t>Stable claim-consistent performance without leakage indicators.</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>Weak-split inflation, instability, or minority-class collapse.</t>
+          <t>Weak-split inflation, instability, class collapse, or directionally inconsistent evidence.</t>
         </is>
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>Small sample size, class imbalance, domain shift, and model sensitivity.</t>
+          <t>Class imbalance, sample limits, domain shift, and model/split sensitivity.</t>
         </is>
       </c>
       <c r="Y20" s="8" t="inlineStr">
@@ -3880,7 +5000,7 @@
       </c>
       <c r="Z20" s="8" t="inlineStr">
         <is>
-          <t>Interpret only within the specified split logic and evidence tier.</t>
+          <t>Interpret only under stated split logic/evidence tier; no causal or localization claims.</t>
         </is>
       </c>
       <c r="AA20" s="8" t="inlineStr">
@@ -3897,7 +5017,7 @@
       <c r="AD20" s="8" t="inlineStr"/>
       <c r="AE20" s="8" t="inlineStr"/>
       <c r="AF20" s="8">
-        <f>IF($AA20="Dropped","N/A",IF(AND($H20&lt;&gt;"",$J20&lt;&gt;"",$K20&lt;&gt;"",$M20&lt;&gt;"",$N20&lt;&gt;"",$P20&lt;&gt;"",$Q20&lt;&gt;"",$Y20&lt;&gt;""),"READY","INCOMPLETE"))</f>
+        <f>IF($AA20="Dropped","N/A",IF(AND($H20&lt;&gt;"",$J20&lt;&gt;"",$K20&lt;&gt;"",$M20&lt;&gt;"",$N20&lt;&gt;"",$P20&lt;&gt;"",$R20&lt;&gt;"",$U20&lt;&gt;"",$V20&lt;&gt;"",$W20&lt;&gt;"",$Z20&lt;&gt;"",$Y20&lt;&gt;""),"READY","INCOMPLETE"))</f>
         <v/>
       </c>
     </row>
@@ -3917,26 +5037,26 @@
       <formula>$AA2="Dropped"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="4">
-      <formula>OR($H2="",$J2="",$K2="",$M2="",$N2="",$P2="",$Q2="",$Y2="")</formula>
+      <formula>OR($H2="",$J2="",$K2="",$M2="",$N2="",$P2="",$R2="",$U2="",$V2="",$W2="",$Z2="",$Y2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=List_Category</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=List_Evidential_Role</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=List_Stage</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=List_Priority</formula1>
     </dataValidation>
-    <dataValidation sqref="Y2:Y400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="Y2:Y500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=List_Reporting_Destination</formula1>
     </dataValidation>
-    <dataValidation sqref="AA2:AA400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AA2:AA500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=List_Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -3950,7 +5070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3967,14 +5087,17 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="36" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="36" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4040,50 +5163,65 @@
       </c>
       <c r="M1" s="7" t="inlineStr">
         <is>
+          <t>Run_Type</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Affects_Frozen_Pipeline</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Eligible_for_Method_Decision</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
           <t>Primary_Metric_Value</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>Secondary_Metric_1</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>Secondary_Metric_2</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>Robustness_Output_Summary</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>Result_Summary</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>Preliminary_Interpretation</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>Reviewed</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>Used_in_Thesis</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="X1" s="7" t="inlineStr">
         <is>
           <t>Artifact_Path</t>
         </is>
       </c>
-      <c r="V1" s="7" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -4112,6 +5250,9 @@
       <c r="T2" s="8" t="n"/>
       <c r="U2" s="8" t="n"/>
       <c r="V2" s="8" t="n"/>
+      <c r="W2" s="8" t="n"/>
+      <c r="X2" s="8" t="n"/>
+      <c r="Y2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -4136,6 +5277,9 @@
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
+      <c r="W3" s="3" t="n"/>
+      <c r="X3" s="3" t="n"/>
+      <c r="Y3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n"/>
@@ -4160,6 +5304,9 @@
       <c r="T4" s="8" t="n"/>
       <c r="U4" s="8" t="n"/>
       <c r="V4" s="8" t="n"/>
+      <c r="W4" s="8" t="n"/>
+      <c r="X4" s="8" t="n"/>
+      <c r="Y4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -4184,6 +5331,9 @@
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -4208,6 +5358,9 @@
       <c r="T6" s="8" t="n"/>
       <c r="U6" s="8" t="n"/>
       <c r="V6" s="8" t="n"/>
+      <c r="W6" s="8" t="n"/>
+      <c r="X6" s="8" t="n"/>
+      <c r="Y6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -4232,6 +5385,9 @@
       <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
+      <c r="W7" s="3" t="n"/>
+      <c r="X7" s="3" t="n"/>
+      <c r="Y7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n"/>
@@ -4256,6 +5412,9 @@
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
       <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -4280,6 +5439,9 @@
       <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n"/>
+      <c r="W9" s="3" t="n"/>
+      <c r="X9" s="3" t="n"/>
+      <c r="Y9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
@@ -4304,6 +5466,9 @@
       <c r="T10" s="8" t="n"/>
       <c r="U10" s="8" t="n"/>
       <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -4328,6 +5493,9 @@
       <c r="T11" s="3" t="n"/>
       <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
@@ -4352,6 +5520,9 @@
       <c r="T12" s="8" t="n"/>
       <c r="U12" s="8" t="n"/>
       <c r="V12" s="8" t="n"/>
+      <c r="W12" s="8" t="n"/>
+      <c r="X12" s="8" t="n"/>
+      <c r="Y12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -4376,6 +5547,9 @@
       <c r="T13" s="3" t="n"/>
       <c r="U13" s="3" t="n"/>
       <c r="V13" s="3" t="n"/>
+      <c r="W13" s="3" t="n"/>
+      <c r="X13" s="3" t="n"/>
+      <c r="Y13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
@@ -4400,6 +5574,9 @@
       <c r="T14" s="8" t="n"/>
       <c r="U14" s="8" t="n"/>
       <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -4424,6 +5601,9 @@
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="3" t="n"/>
+      <c r="W15" s="3" t="n"/>
+      <c r="X15" s="3" t="n"/>
+      <c r="Y15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
@@ -4448,6 +5628,9 @@
       <c r="T16" s="8" t="n"/>
       <c r="U16" s="8" t="n"/>
       <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -4472,6 +5655,9 @@
       <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n"/>
       <c r="V17" s="3" t="n"/>
+      <c r="W17" s="3" t="n"/>
+      <c r="X17" s="3" t="n"/>
+      <c r="Y17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
@@ -4496,6 +5682,9 @@
       <c r="T18" s="8" t="n"/>
       <c r="U18" s="8" t="n"/>
       <c r="V18" s="8" t="n"/>
+      <c r="W18" s="8" t="n"/>
+      <c r="X18" s="8" t="n"/>
+      <c r="Y18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -4520,6 +5709,9 @@
       <c r="T19" s="3" t="n"/>
       <c r="U19" s="3" t="n"/>
       <c r="V19" s="3" t="n"/>
+      <c r="W19" s="3" t="n"/>
+      <c r="X19" s="3" t="n"/>
+      <c r="Y19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -4544,6 +5736,9 @@
       <c r="T20" s="8" t="n"/>
       <c r="U20" s="8" t="n"/>
       <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -4568,6 +5763,9 @@
       <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
       <c r="V21" s="3" t="n"/>
+      <c r="W21" s="3" t="n"/>
+      <c r="X21" s="3" t="n"/>
+      <c r="Y21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -4592,6 +5790,9 @@
       <c r="T22" s="8" t="n"/>
       <c r="U22" s="8" t="n"/>
       <c r="V22" s="8" t="n"/>
+      <c r="W22" s="8" t="n"/>
+      <c r="X22" s="8" t="n"/>
+      <c r="Y22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -4616,6 +5817,9 @@
       <c r="T23" s="3" t="n"/>
       <c r="U23" s="3" t="n"/>
       <c r="V23" s="3" t="n"/>
+      <c r="W23" s="3" t="n"/>
+      <c r="X23" s="3" t="n"/>
+      <c r="Y23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n"/>
@@ -4640,6 +5844,9 @@
       <c r="T24" s="8" t="n"/>
       <c r="U24" s="8" t="n"/>
       <c r="V24" s="8" t="n"/>
+      <c r="W24" s="8" t="n"/>
+      <c r="X24" s="8" t="n"/>
+      <c r="Y24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -4664,6 +5871,9 @@
       <c r="T25" s="3" t="n"/>
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="n"/>
+      <c r="W25" s="3" t="n"/>
+      <c r="X25" s="3" t="n"/>
+      <c r="Y25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n"/>
@@ -4688,6 +5898,9 @@
       <c r="T26" s="8" t="n"/>
       <c r="U26" s="8" t="n"/>
       <c r="V26" s="8" t="n"/>
+      <c r="W26" s="8" t="n"/>
+      <c r="X26" s="8" t="n"/>
+      <c r="Y26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -4712,6 +5925,9 @@
       <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="n"/>
       <c r="V27" s="3" t="n"/>
+      <c r="W27" s="3" t="n"/>
+      <c r="X27" s="3" t="n"/>
+      <c r="Y27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
@@ -4736,6 +5952,9 @@
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
+      <c r="W28" s="8" t="n"/>
+      <c r="X28" s="8" t="n"/>
+      <c r="Y28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -4760,6 +5979,9 @@
       <c r="T29" s="3" t="n"/>
       <c r="U29" s="3" t="n"/>
       <c r="V29" s="3" t="n"/>
+      <c r="W29" s="3" t="n"/>
+      <c r="X29" s="3" t="n"/>
+      <c r="Y29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
@@ -4784,6 +6006,9 @@
       <c r="T30" s="8" t="n"/>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
+      <c r="W30" s="8" t="n"/>
+      <c r="X30" s="8" t="n"/>
+      <c r="Y30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -4808,13 +6033,296 @@
       <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n"/>
       <c r="V31" s="3" t="n"/>
+      <c r="W31" s="3" t="n"/>
+      <c r="X31" s="3" t="n"/>
+      <c r="Y31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="8" t="n"/>
+      <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="8" t="n"/>
+      <c r="R32" s="8" t="n"/>
+      <c r="S32" s="8" t="n"/>
+      <c r="T32" s="8" t="n"/>
+      <c r="U32" s="8" t="n"/>
+      <c r="V32" s="8" t="n"/>
+      <c r="W32" s="8" t="n"/>
+      <c r="X32" s="8" t="n"/>
+      <c r="Y32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
+      <c r="R33" s="3" t="n"/>
+      <c r="S33" s="3" t="n"/>
+      <c r="T33" s="3" t="n"/>
+      <c r="U33" s="3" t="n"/>
+      <c r="V33" s="3" t="n"/>
+      <c r="W33" s="3" t="n"/>
+      <c r="X33" s="3" t="n"/>
+      <c r="Y33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
+      <c r="O34" s="8" t="n"/>
+      <c r="P34" s="8" t="n"/>
+      <c r="Q34" s="8" t="n"/>
+      <c r="R34" s="8" t="n"/>
+      <c r="S34" s="8" t="n"/>
+      <c r="T34" s="8" t="n"/>
+      <c r="U34" s="8" t="n"/>
+      <c r="V34" s="8" t="n"/>
+      <c r="W34" s="8" t="n"/>
+      <c r="X34" s="8" t="n"/>
+      <c r="Y34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="n"/>
+      <c r="Q35" s="3" t="n"/>
+      <c r="R35" s="3" t="n"/>
+      <c r="S35" s="3" t="n"/>
+      <c r="T35" s="3" t="n"/>
+      <c r="U35" s="3" t="n"/>
+      <c r="V35" s="3" t="n"/>
+      <c r="W35" s="3" t="n"/>
+      <c r="X35" s="3" t="n"/>
+      <c r="Y35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="8" t="n"/>
+      <c r="O36" s="8" t="n"/>
+      <c r="P36" s="8" t="n"/>
+      <c r="Q36" s="8" t="n"/>
+      <c r="R36" s="8" t="n"/>
+      <c r="S36" s="8" t="n"/>
+      <c r="T36" s="8" t="n"/>
+      <c r="U36" s="8" t="n"/>
+      <c r="V36" s="8" t="n"/>
+      <c r="W36" s="8" t="n"/>
+      <c r="X36" s="8" t="n"/>
+      <c r="Y36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="3" t="n"/>
+      <c r="Q37" s="3" t="n"/>
+      <c r="R37" s="3" t="n"/>
+      <c r="S37" s="3" t="n"/>
+      <c r="T37" s="3" t="n"/>
+      <c r="U37" s="3" t="n"/>
+      <c r="V37" s="3" t="n"/>
+      <c r="W37" s="3" t="n"/>
+      <c r="X37" s="3" t="n"/>
+      <c r="Y37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="8" t="n"/>
+      <c r="O38" s="8" t="n"/>
+      <c r="P38" s="8" t="n"/>
+      <c r="Q38" s="8" t="n"/>
+      <c r="R38" s="8" t="n"/>
+      <c r="S38" s="8" t="n"/>
+      <c r="T38" s="8" t="n"/>
+      <c r="U38" s="8" t="n"/>
+      <c r="V38" s="8" t="n"/>
+      <c r="W38" s="8" t="n"/>
+      <c r="X38" s="8" t="n"/>
+      <c r="Y38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="3" t="n"/>
+      <c r="T39" s="3" t="n"/>
+      <c r="U39" s="3" t="n"/>
+      <c r="V39" s="3" t="n"/>
+      <c r="W39" s="3" t="n"/>
+      <c r="X39" s="3" t="n"/>
+      <c r="Y39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="8" t="n"/>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="8" t="n"/>
+      <c r="R40" s="8" t="n"/>
+      <c r="S40" s="8" t="n"/>
+      <c r="T40" s="8" t="n"/>
+      <c r="U40" s="8" t="n"/>
+      <c r="V40" s="8" t="n"/>
+      <c r="W40" s="8" t="n"/>
+      <c r="X40" s="8" t="n"/>
+      <c r="Y40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="n"/>
+      <c r="Q41" s="3" t="n"/>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" s="3" t="n"/>
+      <c r="T41" s="3" t="n"/>
+      <c r="U41" s="3" t="n"/>
+      <c r="V41" s="3" t="n"/>
+      <c r="W41" s="3" t="n"/>
+      <c r="X41" s="3" t="n"/>
+      <c r="Y41" s="3" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <autoFilter ref="A1:Y41"/>
+  <dataValidations count="5">
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Run_Type</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Affects_Frozen_Pipeline</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Eligible_for_Method_Decision</formula1>
+    </dataValidation>
+    <dataValidation sqref="V2:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=List_Reviewed</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=List_Used_in_Thesis</formula1>
     </dataValidation>
   </dataValidations>
@@ -4831,21 +6339,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4876,35 +6386,45 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Decision_Criteria</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>Chosen_Option</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Why_Chosen</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Why_Not_Others</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Risks_or_Tradeoffs</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Grounding_Section_or_Source_Packet</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Date_Locked</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Freeze_Status</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Thesis_Use</t>
         </is>
@@ -4923,7 +6443,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 1 - Target lock</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -4938,25 +6458,35 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>To be locked after evidence review</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr"/>
+          <t>Construct validity + class balance + learnability under strict split</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>To be locked after method-choice evidence review</t>
+        </is>
+      </c>
       <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>Construct validity vs learnability tradeoff.</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Tradeoff between construct validity and learnability</t>
+        </is>
+      </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
+          <t>To be linked after background/method revision</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
-        <is>
-          <t>Locks confirmatory target.</t>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 3 method lock feeding Chapter 4 confirmatory analyses</t>
         </is>
       </c>
     </row>
@@ -4973,12 +6503,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 2 - Split lock</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>within_subject_loso_session; weaker alternatives</t>
+          <t>within_subject_loso_session; weaker alternatives for stress testing</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -4988,25 +6518,35 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>To be locked after split stress test</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
+          <t>Prefer strictest split matching claim while documenting weak-split inflation</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>To be locked after split-strength evidence review</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Weak split may inflate performance.</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Weak split inflation risk</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
+          <t>To be linked after method section split rationale update</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Locks claim-matched split logic.</t>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Defines primary inference logic and leakage controls</t>
         </is>
       </c>
     </row>
@@ -5023,7 +6563,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 3 - Model lock</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -5038,25 +6578,35 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
+          <t>Simplicity + robustness + comparable performance</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
           <t>To be locked after model comparison</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>Performance-stability-complexity tradeoff.</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Complexity vs stability tradeoff</t>
+        </is>
+      </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
+          <t>To be linked after model-choice subsection revision</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>Locks confirmatory model.</t>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>Sets final confirmatory model family</t>
         </is>
       </c>
     </row>
@@ -5073,12 +6623,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 3 - Model lock</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>No weighting; class weighting</t>
+          <t>No class weighting; balanced weighting</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5088,25 +6638,35 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>To be locked after fairness/stability check</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
+          <t>Minority-class fairness gain without instability</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>To be locked after weighting sensitivity</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Minority fairness vs instability tradeoff.</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Fairness-stability tension</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>To be linked after class-imbalance discussion draft</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Locks class weighting.</t>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Controls fairness assumptions in final pipeline</t>
         </is>
       </c>
     </row>
@@ -5123,12 +6683,12 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 3 - Model lock</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Fixed settings; light nested tuning</t>
+          <t>Fixed explicit settings; light nested tuning</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -5138,25 +6698,35 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>To be locked after tuning check</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr"/>
+          <t>Keep fixed unless clear stable gain from tuning</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>To be locked after tuning strategy review</t>
+        </is>
+      </c>
       <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Added tuning complexity and overfit risk.</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Overfitting and complexity risk with tuning</t>
+        </is>
+      </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
+          <t>To be linked after reproducibility subsection update</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>Locks configuration policy.</t>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>Determines model configuration policy</t>
         </is>
       </c>
     </row>
@@ -5173,12 +6743,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 4 - Feature/preprocessing lock</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Whole-brain; ROI</t>
+          <t>Whole-brain masked voxels; theory-justified ROI</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5188,25 +6758,35 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>To be locked after representation evidence</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
+          <t>Validity + stability + complexity tradeoff</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>To be locked after feature-space evidence review</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Feature-space choice affects validity and stability.</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Representation choice impacts validity and interpretability</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
+          <t>To be linked after feature-method section update</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Locks feature space.</t>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Locks final feature representation</t>
         </is>
       </c>
     </row>
@@ -5223,12 +6803,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 4 - Feature/preprocessing lock</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>No scaling; standard/robust scaling</t>
+          <t>No scaling; standard/robust scaling (train-only)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -5238,25 +6818,35 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>To be locked after scaling sensitivity check</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
+          <t>Train-only scaling with best stability and simplicity</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>To be locked after scaling sensitivity</t>
+        </is>
+      </c>
       <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>Scaling can shift classifier behavior.</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Scaling can alter class boundaries</t>
+        </is>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
+          <t>To be linked after preprocessing subsection revision</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>Locks preprocessing.</t>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>Locks preprocessing policy</t>
         </is>
       </c>
     </row>
@@ -5273,12 +6863,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Stage 4 - External exploratory</t>
+          <t>Stage 7 - Exploratory extension</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>No external; external replication/portability</t>
+          <t>No external data; external replication/portability</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5288,39 +6878,50 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>To be decided after confirmatory completion</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>External work remains exploratory and non-core</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>To be decided after confirmatory core completion</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Comparability and validity limits for external data.</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Comparability and external validity limits</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
+          <t>To be linked after discussion/limitations revision</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Controls exploratory scope.</t>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Controls exploratory external scope and appendix use</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K200">
+  <autoFilter ref="A1:N9"/>
+  <conditionalFormatting sqref="M2:M200">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$K2="Locked"</formula>
+      <formula>$M2="Locked"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$K2="Open"</formula>
+      <formula>$M2="Open"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=List_Freeze_Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -5337,18 +6938,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5379,22 +6983,37 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Eligible_to_Run</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Required_for_Main_Claim</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Ready_for_Chapter_4</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Confirmatory_Eligible</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
           <t>Main_Result_Summary</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Robustness_Status</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Ready_for_Chapter_4</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>Confirmatory_Eligible</t>
         </is>
       </c>
     </row>
@@ -5424,21 +7043,35 @@
         <v/>
       </c>
       <c r="F2" s="8">
+        <f>IF(AND($J2="YES",IFERROR(INDEX(Master_Experiments!$AF:$AF,MATCH($A2,Master_Experiments!$A:$A,0)),"INCOMPLETE")="READY"),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="G2" s="8">
+        <f>IF(IFERROR(INDEX(Master_Experiments!$AA:$AA,MATCH($A2,Master_Experiments!$A:$A,0)),"Planned")="Completed","YES","NO")</f>
+        <v/>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="8">
+        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="K2" s="8">
         <f>IFERROR(INDEX(Master_Experiments!$AC:$AC,MATCH($A2,Master_Experiments!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
-      </c>
-      <c r="H2" s="8">
-        <f>IF(AND($E2="Completed",$I2="YES"),"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="I2" s="8">
-        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$K:$K,"Locked")&gt;0),"YES","NO")</f>
-        <v/>
       </c>
     </row>
     <row r="3">
@@ -5459,7 +7092,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Non-trivial model value support</t>
+          <t>Non-trivial predictive value support</t>
         </is>
       </c>
       <c r="E3" s="3">
@@ -5467,21 +7100,35 @@
         <v/>
       </c>
       <c r="F3" s="3">
+        <f>IF(AND($J3="YES",IFERROR(INDEX(Master_Experiments!$AF:$AF,MATCH($A3,Master_Experiments!$A:$A,0)),"INCOMPLETE")="READY"),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3">
+        <f>IF(IFERROR(INDEX(Master_Experiments!$AA:$AA,MATCH($A3,Master_Experiments!$A:$A,0)),"Planned")="Completed","YES","NO")</f>
+        <v/>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="3">
+        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="K3" s="3">
         <f>IFERROR(INDEX(Master_Experiments!$AC:$AC,MATCH($A3,Master_Experiments!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
-      </c>
-      <c r="H3" s="3">
-        <f>IF(AND($E3="Completed",$I3="YES"),"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="I3" s="3">
-        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$K:$K,"Locked")&gt;0),"YES","NO")</f>
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -5502,7 +7149,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Model-behavior stability support</t>
+          <t>Model-behavior robustness support</t>
         </is>
       </c>
       <c r="E4" s="8">
@@ -5510,21 +7157,35 @@
         <v/>
       </c>
       <c r="F4" s="8">
+        <f>IF(AND($J4="YES",IFERROR(INDEX(Master_Experiments!$AF:$AF,MATCH($A4,Master_Experiments!$A:$A,0)),"INCOMPLETE")="READY"),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="G4" s="8">
+        <f>IF(IFERROR(INDEX(Master_Experiments!$AA:$AA,MATCH($A4,Master_Experiments!$A:$A,0)),"Planned")="Completed","YES","NO")</f>
+        <v/>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="8">
+        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="K4" s="8">
         <f>IFERROR(INDEX(Master_Experiments!$AC:$AC,MATCH($A4,Master_Experiments!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
-      </c>
-      <c r="H4" s="8">
-        <f>IF(AND($E4="Completed",$I4="YES"),"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="I4" s="8">
-        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$K:$K,"Locked")&gt;0),"YES","NO")</f>
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -5553,21 +7214,35 @@
         <v/>
       </c>
       <c r="F5" s="3">
+        <f>IF(AND($J5="YES",IFERROR(INDEX(Master_Experiments!$AF:$AF,MATCH($A5,Master_Experiments!$A:$A,0)),"INCOMPLETE")="READY"),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3">
+        <f>IF(IFERROR(INDEX(Master_Experiments!$AA:$AA,MATCH($A5,Master_Experiments!$A:$A,0)),"Planned")="Completed","YES","NO")</f>
+        <v/>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="3">
+        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="K5" s="3">
         <f>IFERROR(INDEX(Master_Experiments!$AC:$AC,MATCH($A5,Master_Experiments!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
-      </c>
-      <c r="H5" s="3">
-        <f>IF(AND($E5="Completed",$I5="YES"),"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="I5" s="3">
-        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$K:$K,"Locked")&gt;0),"YES","NO")</f>
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -5588,7 +7263,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Directional transfer claim</t>
+          <t>Secondary transfer claim</t>
         </is>
       </c>
       <c r="E6" s="8">
@@ -5596,32 +7271,73 @@
         <v/>
       </c>
       <c r="F6" s="8">
+        <f>IF(AND($J6="YES",IFERROR(INDEX(Master_Experiments!$AF:$AF,MATCH($A6,Master_Experiments!$A:$A,0)),"INCOMPLETE")="READY"),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="G6" s="8">
+        <f>IF(IFERROR(INDEX(Master_Experiments!$AA:$AA,MATCH($A6,Master_Experiments!$A:$A,0)),"Planned")="Completed","YES","NO")</f>
+        <v/>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J6" s="8">
+        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="K6" s="8">
         <f>IFERROR(INDEX(Master_Experiments!$AC:$AC,MATCH($A6,Master_Experiments!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="H6" s="8">
-        <f>IF(AND($E6="Completed",$I6="YES"),"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="I6" s="8">
-        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$K:$K,"Locked")&gt;0),"YES","NO")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L6"/>
+  <conditionalFormatting sqref="J2:J200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$J2="YES"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F200">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F2="YES"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G200">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>$G2="YES"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I2:I200">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="4" dxfId="0">
       <formula>$I2="YES"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="4">
-      <formula>$I2="NO"</formula>
-    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Status</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Required_for_Main_Claim</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Ready_for_Chapter_4</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Status</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5641,11 +7357,11 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5728,7 +7444,7 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Feeds D01</t>
+          <t>Reference Decision D01</t>
         </is>
       </c>
     </row>
@@ -5750,7 +7466,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Task pooling choice</t>
+          <t>Task pooling method choice</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5765,7 +7481,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Task pooling decision</t>
+          <t>Task pooling policy</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
@@ -5788,7 +7504,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Modality pooling choice</t>
+          <t>Modality pooling method choice</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -5803,7 +7519,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Modality pooling decision</t>
+          <t>Modality pooling policy</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr"/>
@@ -5841,7 +7557,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Strict split justification</t>
+          <t>Justifies strict split</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
@@ -5879,7 +7595,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Frozen directional transfer protocol</t>
+          <t>Directional transfer design</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr"/>
@@ -5902,7 +7618,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Model comparison evidence</t>
+          <t>Model family selection</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5940,7 +7656,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Class-weighting evidence</t>
+          <t>Class weighting decision</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -5955,7 +7671,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Weighting decision</t>
+          <t>Weighting policy lock</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
@@ -5978,7 +7694,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Tuning strategy evidence</t>
+          <t>Hyperparameter policy</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5993,7 +7709,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Fixed vs nested tuning</t>
+          <t>Fixed vs tuning decision</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
@@ -6069,7 +7785,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Complexity vs stability tradeoff</t>
+          <t>Complexity/stability tradeoff</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
@@ -6107,7 +7823,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Scaling lock</t>
+          <t>Scaling policy lock</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr"/>
@@ -6145,7 +7861,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Beyond-chance evidence</t>
+          <t>Beyond-chance support</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
@@ -6183,7 +7899,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Non-trivial predictive value</t>
+          <t>Non-trivial value support</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr"/>
@@ -6263,7 +7979,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Bounds dependence on subsets</t>
+          <t>Sensitivity/limitations support</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr"/>
@@ -6415,12 +8131,13 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Exploratory portability check</t>
+          <t>Exploratory portability</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6434,20 +8151,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="80" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="84" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6456,7 +8185,7 @@
           <t>Controlled vocabularies (drives dropdown validation)</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>Term definitions</t>
         </is>
@@ -6508,12 +8237,72 @@
           <t>Freeze_Status</t>
         </is>
       </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>Run_Type</t>
+        </is>
+      </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
+          <t>Affects_Frozen_Pipeline</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>Eligible_for_Method_Decision</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>Claim_Type</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>Evidence_Status</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>Writing_Location</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>Human_Verification_Status</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>Ethics_Status</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>Ethics_Topic</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>Required_for_Main_Claim</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>Ready_for_Chapter_4</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr">
+        <is>
+          <t>YesNo</t>
+        </is>
+      </c>
+      <c r="V2" s="10" t="inlineStr">
+        <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="W2" s="10" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
@@ -6532,7 +8321,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Stage 0 - Program design</t>
+          <t>Stage 1 - Target lock</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -6565,14 +8354,74 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Method-choice</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Data governance</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
           <t>confirmatory</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Primary evidence analysis with pre-specified pipeline and decision rules.</t>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>Pre-specified, locked-pipeline evidence analysis supporting main thesis claims.</t>
         </is>
       </c>
     </row>
@@ -6589,7 +8438,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Stage 1 - Method choice</t>
+          <t>Stage 2 - Split lock</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
@@ -6622,14 +8471,74 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Decision-support</t>
+        </is>
+      </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>Confirmatory finding</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Chapter 4</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>Partially verified</t>
+        </is>
+      </c>
+      <c r="Q4" s="11" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>Bias/fairness</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V4" s="11" t="inlineStr">
+        <is>
           <t>decision-support</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>Method-choice evidence used before confirmatory lock.</t>
+      <c r="W4" s="8" t="inlineStr">
+        <is>
+          <t>Method-choice analysis performed before locking confirmatory settings.</t>
         </is>
       </c>
     </row>
@@ -6646,7 +8555,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Stage 2 - Robustness support</t>
+          <t>Stage 3 - Model lock</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -6664,14 +8573,49 @@
           <t>Chapter 4 Supporting robustness</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Robustness support</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 5</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>Interpretation limits</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>exploratory</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Hypothesis-generating or extension analysis outside confirmatory core.</t>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>Hypothesis-generating extension outside confirmatory core.</t>
         </is>
       </c>
     </row>
@@ -6688,7 +8632,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Stage 3 - Confirmatory core</t>
+          <t>Stage 4 - Feature/preprocessing lock</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -6706,14 +8650,34 @@
           <t>Chapter 5 Discussion</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>Exploratory observation</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="R6" s="11" t="inlineStr">
+        <is>
+          <t>AI/tool transparency</t>
+        </is>
+      </c>
+      <c r="V6" s="11" t="inlineStr">
         <is>
           <t>construct validity</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>How well operational labels/features represent the intended construct.</t>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>How well labels/features operationalize intended constructs.</t>
         </is>
       </c>
     </row>
@@ -6730,7 +8694,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Stage 4 - External exploratory</t>
+          <t>Stage 5 - Confirmatory analysis</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -6743,14 +8707,24 @@
           <t>Appendix</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Exploratory</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>Reproducibility</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>internal validity</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Protection against confounds and leakage in experiment design.</t>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>Protection against confounds and leakage in design and execution.</t>
         </is>
       </c>
     </row>
@@ -6762,7 +8736,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Stage 5 - Thesis write-up</t>
+          <t>Stage 6 - Robustness analysis</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -6770,14 +8744,19 @@
           <t>Dropped</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="R8" s="11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="V8" s="11" t="inlineStr">
         <is>
           <t>statistical conclusion validity</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>Reliability of inference from metrics and comparisons.</t>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>Reliability of metric-based inference.</t>
         </is>
       </c>
     </row>
@@ -6787,57 +8766,62 @@
           <t>External exploratory</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Stage 7 - Exploratory extension</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>external validity</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>How far findings transfer to other settings/data.</t>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>Extent findings transfer to other data contexts.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="K10" s="11" t="inlineStr">
+      <c r="V10" s="11" t="inlineStr">
         <is>
           <t>leakage</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>Information contamination across train-test boundaries that inflates performance.</t>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>Train-test information contamination that inflates apparent performance.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="K11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>domain shift</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Distribution mismatch between training and testing domains.</t>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>Distribution shift between train and test domains.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="K12" s="11" t="inlineStr">
+      <c r="V12" s="11" t="inlineStr">
         <is>
           <t>interpretability stability</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>Consistency of model explanation signals across folds.</t>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>Consistency of model-behavior explanation signals across folds.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6849,23 +8833,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Thesis Experiment Program Dashboard (v2)</t>
         </is>
       </c>
     </row>
@@ -6893,7 +8878,7 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTA(Master_Experiments!$A$2:$A$200)</f>
+        <f>COUNTA(Master_Experiments!$A$2:$A$500)</f>
         <v/>
       </c>
       <c r="D4" s="4">
@@ -6920,7 +8905,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF(Master_Experiments!$AA$2:$AA$200,"Completed")</f>
+        <f>COUNTIF(Master_Experiments!$AA$2:$AA$500,"Completed")</f>
         <v/>
       </c>
       <c r="D5" s="4">
@@ -6947,7 +8932,7 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(Master_Experiments!$F$2:$F$200,"Critical",Master_Experiments!$AA$2:$AA$200,"Completed")</f>
+        <f>COUNTIFS(Master_Experiments!$F$2:$F$500,"Critical",Master_Experiments!$AA$2:$AA$500,"Completed")</f>
         <v/>
       </c>
       <c r="D6" s="4">
@@ -6974,7 +8959,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF(Decision_Log!$K$2:$K$200,"Open")</f>
+        <f>COUNTIF(Decision_Log!$M$2:$M$500,"Open")</f>
         <v/>
       </c>
       <c r="D7" s="4">
@@ -7001,7 +8986,7 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIF(Decision_Log!$K$2:$K$200,"Locked")</f>
+        <f>COUNTIF(Decision_Log!$M$2:$M$500,"Locked")</f>
         <v/>
       </c>
       <c r="D8" s="4">
@@ -7028,7 +9013,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>IF(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$K:$K,"Locked")&gt;0,"YES","NO")</f>
+        <f>IF(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$M:$M,"Locked")&gt;0,"YES","NO")</f>
         <v/>
       </c>
       <c r="D9" s="4">
@@ -7047,7 +9032,7 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>IF(COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$K:$K,"Locked")&gt;0,"YES","NO")</f>
+        <f>IF(COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$M:$M,"Locked")&gt;0,"YES","NO")</f>
         <v/>
       </c>
       <c r="D10" s="4">
@@ -7066,62 +9051,128 @@
         </is>
       </c>
       <c r="B11" s="4">
-        <f>IF(COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$K:$K,"Locked")&gt;0,"YES","NO")</f>
+        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Feature pipeline locked?</t>
+          <t>Feature/preprocessing locked?</t>
         </is>
       </c>
       <c r="B12" s="11">
-        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$K:$K,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$K:$K,"Locked")&gt;0),"YES","NO")</f>
+        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Confirmatory ready?</t>
+          <t>Confirmatory eligibility achieved?</t>
         </is>
       </c>
       <c r="B13" s="4">
-        <f>IF(AND(B9="YES",B10="YES",B11="YES",B12="YES",COUNTIFS(Confirmatory_Set!$I:$I,"YES")&gt;=5),"YES","NO")</f>
+        <f>IF(COUNTIFS(Confirmatory_Set!$J:$J,"YES")=COUNTIFS(Confirmatory_Set!$A:$A,"&lt;&gt;"),"YES","NO")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Experiments mapped to Chapter 4 main results</t>
+          <t>Confirmatory ready for Chapter 4?</t>
         </is>
       </c>
       <c r="B14" s="11">
-        <f>COUNTIFS(Thesis_Map!$B$2:$B$200,"Chapter 4",Thesis_Map!$E$2:$E$200,"Main")</f>
+        <f>IF(AND(B13="YES",COUNTIFS(Confirmatory_Set!$H:$H,"YES",Confirmatory_Set!$G:$G,"YES",Confirmatory_Set!$I:$I,"YES")=COUNTIFS(Confirmatory_Set!$H:$H,"YES")),"YES","NO")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Experiments mapped to Chapter 4 main results</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <f>COUNTIFS(Thesis_Map!$B$2:$B$500,"Chapter 4",Thesis_Map!$E$2:$E$500,"Main")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
           <t>Experiments mapped only to Appendix</t>
         </is>
       </c>
-      <c r="B15" s="4">
-        <f>COUNTIF(Thesis_Map!$B$2:$B$200,"Appendix")</f>
+      <c r="B16" s="11">
+        <f>COUNTIF(Thesis_Map!$B$2:$B$500,"Appendix")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Claims with Evidence_Status = supported</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <f>COUNTIF(Claim_Ledger!$E$2:$E$500,"supported")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Claims with Evidence_Status = partial</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
+        <f>COUNTIF(Claim_Ledger!$E$2:$E$500,"partial")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Claims with Evidence_Status = open</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <f>COUNTIF(Claim_Ledger!$E$2:$E$500,"open")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>AI log entries</t>
+        </is>
+      </c>
+      <c r="B20" s="11">
+        <f>COUNTA(AI_Usage_Log!$A$2:$A$500)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Open ethics/governance notes</t>
+        </is>
+      </c>
+      <c r="B21" s="4">
+        <f>COUNTIF(Ethics_Governance_Notes!$G$2:$G$500,"Open")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B9:B13">
+  <conditionalFormatting sqref="B9:B14">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>B9="YES"</formula>
     </cfRule>
@@ -7131,4 +9182,469 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Claim_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Claim_Text</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Claim_Type</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Supported_By_Experiments</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Evidence_Status</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Writing_Location</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Interpretation_Limit</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Primary within-person held-out-session decoding demonstrates meaningful generalization under locked pipeline.</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Confirmatory finding</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>E16,E12,E13,E14</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 4</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Interpret only within claim-matched split and current dataset scope.</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Frozen directional cross-person transfer indicates cross-case portability under domain shift.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Confirmatory finding</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>E17,E12,E13</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Chapter 4</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Not a population-level generalization claim.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Method lock decisions reduce leakage risk and interpretation drift.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Method-choice</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>E01,E04,E05,E06,E09,E11</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Governance claim; not a performance claim.</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H31"/>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Claim_Type</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Evidence_Status</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Writing_Location</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/thesis_experiment_program.xlsx
+++ b/thesis_experiment_program.xlsx
@@ -9,17 +9,22 @@
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Master_Experiments" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Run_Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decision_Log" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Confirmatory_Set" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Thesis_Map" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Dictionary_Validation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Claim_Ledger" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="AI_Usage_Log" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Ethics_Governance_Notes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Data_Selection_Design" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Grouping_Strategy_Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Data_Profile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Run_Log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Decision_Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Confirmatory_Set" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Thesis_Map" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Dictionary_Validation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Dashboard" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Claim_Ledger" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AI_Usage_Log" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Ethics_Governance_Notes" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
+    <definedName name="List_Data_Slice_ID">'Data_Selection_Design'!$A$2:INDEX('Data_Selection_Design'!$A:$A,MATCH("zzz",'Data_Selection_Design'!$A:$A))</definedName>
+    <definedName name="List_Grouping_Strategy_ID">'Grouping_Strategy_Map'!$A$2:INDEX('Grouping_Strategy_Map'!$A:$A,MATCH("zzz",'Grouping_Strategy_Map'!$A:$A))</definedName>
     <definedName name="List_Category">'Dictionary_Validation'!$A$3:$A$9</definedName>
     <definedName name="List_Evidential_Role">'Dictionary_Validation'!$B$3:$B$7</definedName>
     <definedName name="List_Stage">'Dictionary_Validation'!$C$3:$C$9</definedName>
@@ -41,14 +46,31 @@
     <definedName name="List_Required_for_Main_Claim">'Dictionary_Validation'!$S$3:$S$4</definedName>
     <definedName name="List_Ready_for_Chapter_4">'Dictionary_Validation'!$T$3:$T$4</definedName>
     <definedName name="List_YesNo">'Dictionary_Validation'!$U$3:$U$4</definedName>
+    <definedName name="List_Subject_Scope">'Dictionary_Validation'!$V$3:$V$5</definedName>
+    <definedName name="List_Session_Scope">'Dictionary_Validation'!$W$3:$W$7</definedName>
+    <definedName name="List_Task_Scope">'Dictionary_Validation'!$X$3:$X$7</definedName>
+    <definedName name="List_Modality_Scope">'Dictionary_Validation'!$Y$3:$Y$6</definedName>
+    <definedName name="List_Class_Balance_Policy">'Dictionary_Validation'!$Z$3:$Z$6</definedName>
+    <definedName name="List_Split_Family">'Dictionary_Validation'!$AA$3:$AA$7</definedName>
+    <definedName name="List_Imbalance_Status">'Dictionary_Validation'!$AB$3:$AB$6</definedName>
+    <definedName name="List_Leakage_Check_Status">'Dictionary_Validation'!$AC$3:$AC$6</definedName>
+    <definedName name="List_Thesis_Use_Tag">'Dictionary_Validation'!$AD$3:$AD$7</definedName>
+    <definedName name="List_Use_Case">'Dictionary_Validation'!$AE$3:$AE$9</definedName>
+    <definedName name="List_Group_Unit">'Dictionary_Validation'!$AF$3:$AF$9</definedName>
+    <definedName name="List_Grouping_Level">'Dictionary_Validation'!$AG$3:$AG$9</definedName>
+    <definedName name="List_Transfer_Direction">'Dictionary_Validation'!$AH$3:$AH$7</definedName>
+    <definedName name="List_Leakage_Risk_Level">'Dictionary_Validation'!$AI$3:$AI$6</definedName>
+    <definedName name="List_Target_Type">'Dictionary_Validation'!$AJ$3:$AJ$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master_Experiments'!$A$1:$AF$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Run_Log'!$A$1:$Y$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Decision_Log'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Confirmatory_Set'!$A$1:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Thesis_Map'!$A$1:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Claim_Ledger'!$A$1:$H$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'AI_Usage_Log'!$A$1:$J$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Ethics_Governance_Notes'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Data_Selection_Design'!$A$1:$R$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Grouping_Strategy_Map'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Run_Log'!$A$1:$AK$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Decision_Log'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Confirmatory_Set'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Thesis_Map'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Claim_Ledger'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AI_Usage_Log'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ethics_Governance_Notes'!$A$1:$H$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,7 +79,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +97,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -148,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -161,18 +191,23 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -294,41 +329,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RunLogTable" displayName="RunLogTable" ref="A1:Y41" headerRowCount="1">
-  <autoFilter ref="A1:Y41"/>
-  <tableColumns count="25">
-    <tableColumn id="1" name="Run_ID"/>
-    <tableColumn id="2" name="Experiment_ID"/>
-    <tableColumn id="3" name="Run_Date"/>
-    <tableColumn id="4" name="Dataset_Name"/>
-    <tableColumn id="5" name="Data_Subset"/>
-    <tableColumn id="6" name="Code_Commit_or_Version"/>
-    <tableColumn id="7" name="Config_File_or_Path"/>
-    <tableColumn id="8" name="Random_Seed"/>
-    <tableColumn id="9" name="Target"/>
-    <tableColumn id="10" name="Split_ID_or_Fold_Definition"/>
-    <tableColumn id="11" name="Model"/>
-    <tableColumn id="12" name="Feature_Set"/>
-    <tableColumn id="13" name="Run_Type"/>
-    <tableColumn id="14" name="Affects_Frozen_Pipeline"/>
-    <tableColumn id="15" name="Eligible_for_Method_Decision"/>
-    <tableColumn id="16" name="Primary_Metric_Value"/>
-    <tableColumn id="17" name="Secondary_Metric_1"/>
-    <tableColumn id="18" name="Secondary_Metric_2"/>
-    <tableColumn id="19" name="Robustness_Output_Summary"/>
-    <tableColumn id="20" name="Result_Summary"/>
-    <tableColumn id="21" name="Preliminary_Interpretation"/>
-    <tableColumn id="22" name="Reviewed"/>
-    <tableColumn id="23" name="Used_in_Thesis"/>
-    <tableColumn id="24" name="Artifact_Path"/>
-    <tableColumn id="25" name="Notes"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DataSelectionTable" displayName="DataSelectionTable" ref="A1:R41" headerRowCount="1">
+  <autoFilter ref="A1:R41"/>
+  <tableColumns count="18">
+    <tableColumn id="1" name="Data_Slice_ID"/>
+    <tableColumn id="2" name="Slice_Name"/>
+    <tableColumn id="3" name="Purpose"/>
+    <tableColumn id="4" name="Subject_Scope"/>
+    <tableColumn id="5" name="Session_Scope"/>
+    <tableColumn id="6" name="Time_Window"/>
+    <tableColumn id="7" name="Task_Scope"/>
+    <tableColumn id="8" name="Modality_Scope"/>
+    <tableColumn id="9" name="Target_Type"/>
+    <tableColumn id="10" name="Label_Set"/>
+    <tableColumn id="11" name="Inclusion_Rule"/>
+    <tableColumn id="12" name="Exclusion_Rule"/>
+    <tableColumn id="13" name="Class_Balance_Policy"/>
+    <tableColumn id="14" name="Minimum_Samples_Rule"/>
+    <tableColumn id="15" name="Leakage_Risk"/>
+    <tableColumn id="16" name="Valid_Use_Case"/>
+    <tableColumn id="17" name="Thesis_Use"/>
+    <tableColumn id="18" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:N9" headerRowCount="1">
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:N9" headerRowCount="1">
   <autoFilter ref="A1:N9"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Decision_ID"/>
@@ -350,8 +378,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ConfirmatoryTable" displayName="ConfirmatoryTable" ref="A1:L6" headerRowCount="1">
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="ConfirmatoryTable" displayName="ConfirmatoryTable" ref="A1:L6" headerRowCount="1">
   <autoFilter ref="A1:L6"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Experiment_ID"/>
@@ -371,8 +399,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ThesisMapTable" displayName="ThesisMapTable" ref="A1:H20" headerRowCount="1">
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="ThesisMapTable" displayName="ThesisMapTable" ref="A1:H20" headerRowCount="1">
   <autoFilter ref="A1:H20"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Experiment_ID"/>
@@ -388,8 +416,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ClaimLedgerTable" displayName="ClaimLedgerTable" ref="A1:H31" headerRowCount="1">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="ClaimLedgerTable" displayName="ClaimLedgerTable" ref="A1:H31" headerRowCount="1">
   <autoFilter ref="A1:H31"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Claim_ID"/>
@@ -405,8 +433,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="AIUsageTable" displayName="AIUsageTable" ref="A1:J41" headerRowCount="1">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="AIUsageTable" displayName="AIUsageTable" ref="A1:J41" headerRowCount="1">
   <autoFilter ref="A1:J41"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Entry_ID"/>
@@ -424,8 +452,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="EthicsTable" displayName="EthicsTable" ref="A1:H31" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="EthicsTable" displayName="EthicsTable" ref="A1:H31" headerRowCount="1">
   <autoFilter ref="A1:H31"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Note_ID"/>
@@ -438,6 +466,160 @@
     <tableColumn id="8" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="GroupingStrategyTable" displayName="GroupingStrategyTable" ref="A1:O41" headerRowCount="1">
+  <autoFilter ref="A1:O41"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="Grouping_Strategy_ID"/>
+    <tableColumn id="2" name="Strategy_Name"/>
+    <tableColumn id="3" name="Split_Family"/>
+    <tableColumn id="4" name="Train_Group_Unit"/>
+    <tableColumn id="5" name="Test_Group_Unit"/>
+    <tableColumn id="6" name="Grouping_Level"/>
+    <tableColumn id="7" name="Train_Rule"/>
+    <tableColumn id="8" name="Test_Rule"/>
+    <tableColumn id="9" name="Leakage_Safeguard"/>
+    <tableColumn id="10" name="Suitable_For"/>
+    <tableColumn id="11" name="Not_Suitable_For"/>
+    <tableColumn id="12" name="Interpretation_Boundary"/>
+    <tableColumn id="13" name="Typical_Experiments"/>
+    <tableColumn id="14" name="Thesis_Section"/>
+    <tableColumn id="15" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ProfileSubjectTable" displayName="ProfileSubjectTable" ref="A12:E20" headerRowCount="1">
+  <autoFilter ref="A12:E20"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Subject_ID"/>
+    <tableColumn id="2" name="Count"/>
+    <tableColumn id="3" name="Share_of_Block"/>
+    <tableColumn id="4" name="Flag"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ProfileSessionTable" displayName="ProfileSessionTable" ref="A24:E34" headerRowCount="1">
+  <autoFilter ref="A24:E34"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Session_ID"/>
+    <tableColumn id="2" name="Count"/>
+    <tableColumn id="3" name="Share_of_Block"/>
+    <tableColumn id="4" name="Flag"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ProfileTaskTable" displayName="ProfileTaskTable" ref="A38:E45" headerRowCount="1">
+  <autoFilter ref="A38:E45"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Task_ID"/>
+    <tableColumn id="2" name="Count"/>
+    <tableColumn id="3" name="Share_of_Block"/>
+    <tableColumn id="4" name="Flag"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="ProfileModalityTable" displayName="ProfileModalityTable" ref="A49:E55" headerRowCount="1">
+  <autoFilter ref="A49:E55"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Modality_ID"/>
+    <tableColumn id="2" name="Count"/>
+    <tableColumn id="3" name="Share_of_Block"/>
+    <tableColumn id="4" name="Flag"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ProfileTargetClassTable" displayName="ProfileTargetClassTable" ref="A59:E65" headerRowCount="1">
+  <autoFilter ref="A59:E65"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Target_or_Class_ID"/>
+    <tableColumn id="2" name="Count"/>
+    <tableColumn id="3" name="Share_of_Block"/>
+    <tableColumn id="4" name="Flag"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ProfileDataSliceTable" displayName="ProfileDataSliceTable" ref="A70:E80" headerRowCount="1">
+  <autoFilter ref="A70:E80"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Data_Slice_ID"/>
+    <tableColumn id="2" name="Count"/>
+    <tableColumn id="3" name="Share_of_Block"/>
+    <tableColumn id="4" name="Flag"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="RunLogTable" displayName="RunLogTable" ref="A1:AK41" headerRowCount="1">
+  <autoFilter ref="A1:AK41"/>
+  <tableColumns count="37">
+    <tableColumn id="1" name="Run_ID"/>
+    <tableColumn id="2" name="Experiment_ID"/>
+    <tableColumn id="3" name="Run_Date"/>
+    <tableColumn id="4" name="Dataset_Name"/>
+    <tableColumn id="5" name="Data_Subset"/>
+    <tableColumn id="6" name="Data_Slice_ID"/>
+    <tableColumn id="7" name="Grouping_Strategy_ID"/>
+    <tableColumn id="8" name="Code_Commit_or_Version"/>
+    <tableColumn id="9" name="Config_File_or_Path"/>
+    <tableColumn id="10" name="Random_Seed"/>
+    <tableColumn id="11" name="Target"/>
+    <tableColumn id="12" name="Split_ID_or_Fold_Definition"/>
+    <tableColumn id="13" name="Train_Group_Rule"/>
+    <tableColumn id="14" name="Test_Group_Rule"/>
+    <tableColumn id="15" name="Transfer_Direction"/>
+    <tableColumn id="16" name="Session_Coverage"/>
+    <tableColumn id="17" name="Task_Coverage"/>
+    <tableColumn id="18" name="Modality_Coverage"/>
+    <tableColumn id="19" name="Model"/>
+    <tableColumn id="20" name="Feature_Set"/>
+    <tableColumn id="21" name="Run_Type"/>
+    <tableColumn id="22" name="Affects_Frozen_Pipeline"/>
+    <tableColumn id="23" name="Eligible_for_Method_Decision"/>
+    <tableColumn id="24" name="Sample_Count"/>
+    <tableColumn id="25" name="Class_Counts"/>
+    <tableColumn id="26" name="Imbalance_Status"/>
+    <tableColumn id="27" name="Leakage_Check_Status"/>
+    <tableColumn id="28" name="Primary_Metric_Value"/>
+    <tableColumn id="29" name="Secondary_Metric_1"/>
+    <tableColumn id="30" name="Secondary_Metric_2"/>
+    <tableColumn id="31" name="Robustness_Output_Summary"/>
+    <tableColumn id="32" name="Result_Summary"/>
+    <tableColumn id="33" name="Preliminary_Interpretation"/>
+    <tableColumn id="34" name="Reviewed"/>
+    <tableColumn id="35" name="Used_in_Thesis"/>
+    <tableColumn id="36" name="Artifact_Path"/>
+    <tableColumn id="37" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -730,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -784,12 +966,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Evidence tiers</t>
+          <t>Governance layers</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Primary confirmatory; Primary-supporting robustness; Secondary decision-support; Exploratory extension. Each tier has explicit interpretation boundaries.</t>
+          <t>Experiment governance documents what each experiment is allowed to conclude. Data-slice governance documents what subset policy and grouping strategy were used in each run and what claims they can support.</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -814,12 +996,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Stage system</t>
+          <t>Evidence tiers</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Stage 1 Target lock -&gt; Stage 2 Split lock -&gt; Stage 3 Model lock -&gt; Stage 4 Feature/preprocessing lock -&gt; Stage 5 Confirmatory analysis -&gt; Stage 6 Robustness analysis -&gt; Stage 7 Exploratory extension.</t>
+          <t>Primary confirmatory; Primary-supporting robustness; Secondary decision-support; Exploratory extension. Each tier has explicit interpretation boundaries.</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -844,12 +1026,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Freeze policy</t>
+          <t>Stage system</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Confirmatory eligibility requires D01-D07 locked in Decision_Log. Chapter 4 readiness additionally requires required confirmatory/supporting items completed and marked Ready_for_Chapter_4=YES.</t>
+          <t>Stage 1 Target lock -&gt; Stage 2 Split lock -&gt; Stage 3 Model lock -&gt; Stage 4 Feature/preprocessing lock -&gt; Stage 5 Confirmatory analysis -&gt; Stage 6 Robustness analysis -&gt; Stage 7 Exploratory extension.</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -874,12 +1056,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Governance additions</t>
+          <t>Freeze policy</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Claim_Ledger enforces claim discipline. AI_Usage_Log supports tool transparency and human verification traceability. Ethics_Governance_Notes supports risk/mitigation accountability.</t>
+          <t>Confirmatory eligibility requires D01-D07 locked in Decision_Log. Chapter 4 readiness additionally requires required confirmatory/supporting items completed and marked Ready_for_Chapter_4=YES.</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -904,12 +1086,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Workflow</t>
+          <t>Data_Selection_Design</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Master_Experiments -&gt; Run_Log -&gt; Decision_Log -&gt; Confirmatory_Set -&gt; Claim_Ledger/AI_Usage_Log/Ethics_Governance_Notes -&gt; Thesis_Map -&gt; Dashboard.</t>
+          <t>Defines allowed data slices (subject/session/task/modality/target scope, inclusion/exclusion, class-balance policy, leakage risk, and thesis-use boundary).</t>
         </is>
       </c>
       <c r="C18" s="4" t="n"/>
@@ -931,37 +1113,2572 @@
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Grouping_Strategy_Map</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Defines split family, train/test grouping units, leakage safeguards, and interpretation boundaries for each grouping strategy identifier.</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>This workbook is aligned to thesis method-choice/method-application workflow and reporting governance requirements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Data_Profile</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Structured worksheet for manual or imported descriptive counts by subject/session/task/modality/target/class and by Data_Slice_ID, with formula-based sparsity/imbalance flags.</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Claim boundaries</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Within-person held-out-session claims and cross-person transfer claims are different scientific claims and must not be interpreted interchangeably.</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Weak-split policy</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Weak split results are allowed only as inflation demonstrations and diagnostic contrast. They are not confirmatory evidence.</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Governance additions</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Claim_Ledger enforces claim discipline. AI_Usage_Log supports tool transparency and human verification traceability. Ethics_Governance_Notes supports risk/mitigation accountability.</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Master_Experiments + Data_Selection_Design + Grouping_Strategy_Map -&gt; Run_Log -&gt; Decision_Log -&gt; Confirmatory_Set -&gt; Claim_Ledger/AI_Usage_Log/Ethics_Governance_Notes -&gt; Thesis_Map -&gt; Dashboard.</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>This workbook is aligned to thesis method-choice/method-application workflow, data-slice/grouping governance, and leakage-aware reporting requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Generated by create_thesis_experiment_workbook.py (v2)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
     <mergeCell ref="B9:I10"/>
     <mergeCell ref="B12:I13"/>
     <mergeCell ref="B18:I19"/>
     <mergeCell ref="B3:I4"/>
+    <mergeCell ref="B36:I37"/>
+    <mergeCell ref="B33:I34"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B6:I7"/>
+    <mergeCell ref="B21:I22"/>
     <mergeCell ref="B15:I16"/>
-    <mergeCell ref="A22:I23"/>
+    <mergeCell ref="A39:I40"/>
+    <mergeCell ref="B24:I25"/>
+    <mergeCell ref="B30:I31"/>
+    <mergeCell ref="B27:I28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AL15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
+    <col width="84" customWidth="1" min="38" max="38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Controlled vocabularies (drives dropdown validation)</t>
+        </is>
+      </c>
+      <c r="AK1" s="13" t="inlineStr">
+        <is>
+          <t>Term definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Evidential_Role</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Reporting_Destination</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Used_in_Thesis</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>Freeze_Status</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>Run_Type</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>Affects_Frozen_Pipeline</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>Eligible_for_Method_Decision</t>
+        </is>
+      </c>
+      <c r="M2" s="14" t="inlineStr">
+        <is>
+          <t>Claim_Type</t>
+        </is>
+      </c>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>Evidence_Status</t>
+        </is>
+      </c>
+      <c r="O2" s="14" t="inlineStr">
+        <is>
+          <t>Writing_Location</t>
+        </is>
+      </c>
+      <c r="P2" s="14" t="inlineStr">
+        <is>
+          <t>Human_Verification_Status</t>
+        </is>
+      </c>
+      <c r="Q2" s="14" t="inlineStr">
+        <is>
+          <t>Ethics_Status</t>
+        </is>
+      </c>
+      <c r="R2" s="14" t="inlineStr">
+        <is>
+          <t>Ethics_Topic</t>
+        </is>
+      </c>
+      <c r="S2" s="14" t="inlineStr">
+        <is>
+          <t>Required_for_Main_Claim</t>
+        </is>
+      </c>
+      <c r="T2" s="14" t="inlineStr">
+        <is>
+          <t>Ready_for_Chapter_4</t>
+        </is>
+      </c>
+      <c r="U2" s="14" t="inlineStr">
+        <is>
+          <t>YesNo</t>
+        </is>
+      </c>
+      <c r="V2" s="14" t="inlineStr">
+        <is>
+          <t>Subject_Scope</t>
+        </is>
+      </c>
+      <c r="W2" s="14" t="inlineStr">
+        <is>
+          <t>Session_Scope</t>
+        </is>
+      </c>
+      <c r="X2" s="14" t="inlineStr">
+        <is>
+          <t>Task_Scope</t>
+        </is>
+      </c>
+      <c r="Y2" s="14" t="inlineStr">
+        <is>
+          <t>Modality_Scope</t>
+        </is>
+      </c>
+      <c r="Z2" s="14" t="inlineStr">
+        <is>
+          <t>Class_Balance_Policy</t>
+        </is>
+      </c>
+      <c r="AA2" s="14" t="inlineStr">
+        <is>
+          <t>Split_Family</t>
+        </is>
+      </c>
+      <c r="AB2" s="14" t="inlineStr">
+        <is>
+          <t>Imbalance_Status</t>
+        </is>
+      </c>
+      <c r="AC2" s="14" t="inlineStr">
+        <is>
+          <t>Leakage_Check_Status</t>
+        </is>
+      </c>
+      <c r="AD2" s="14" t="inlineStr">
+        <is>
+          <t>Thesis_Use_Tag</t>
+        </is>
+      </c>
+      <c r="AE2" s="14" t="inlineStr">
+        <is>
+          <t>Use_Case</t>
+        </is>
+      </c>
+      <c r="AF2" s="14" t="inlineStr">
+        <is>
+          <t>Group_Unit</t>
+        </is>
+      </c>
+      <c r="AG2" s="14" t="inlineStr">
+        <is>
+          <t>Grouping_Level</t>
+        </is>
+      </c>
+      <c r="AH2" s="14" t="inlineStr">
+        <is>
+          <t>Transfer_Direction</t>
+        </is>
+      </c>
+      <c r="AI2" s="14" t="inlineStr">
+        <is>
+          <t>Leakage_Risk_Level</t>
+        </is>
+      </c>
+      <c r="AJ2" s="14" t="inlineStr">
+        <is>
+          <t>Target_Type</t>
+        </is>
+      </c>
+      <c r="AK2" s="14" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="AL2" s="14" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Target-definition</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Primary confirmatory</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Stage 1 - Target lock</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 3 Method choice</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Method-choice</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Not reviewed</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Data governance</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>within_subject</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>not_checked</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>within_subject</t>
+        </is>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>none_or_within_subject</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="AK3" s="4" t="inlineStr">
+        <is>
+          <t>confirmatory</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Pre-specified, locked-pipeline evidence analysis supporting main thesis claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Split-design</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Primary-supporting robustness</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Stage 2 - Split lock</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Chapter 4 Main results</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Decision-support</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>Confirmatory finding</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Chapter 4</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>Partially verified</t>
+        </is>
+      </c>
+      <c r="Q4" s="11" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>Bias/fairness</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V4" s="11" t="inlineStr">
+        <is>
+          <t>single_subject</t>
+        </is>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>early_only</t>
+        </is>
+      </c>
+      <c r="X4" s="11" t="inlineStr">
+        <is>
+          <t>passive_only</t>
+        </is>
+      </c>
+      <c r="Y4" s="11" t="inlineStr">
+        <is>
+          <t>audio_only</t>
+        </is>
+      </c>
+      <c r="Z4" s="11" t="inlineStr">
+        <is>
+          <t>balanced_subset</t>
+        </is>
+      </c>
+      <c r="AA4" s="11" t="inlineStr">
+        <is>
+          <t>cross_person</t>
+        </is>
+      </c>
+      <c r="AB4" s="11" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="AC4" s="11" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="AD4" s="11" t="inlineStr">
+        <is>
+          <t>main_confirmatory</t>
+        </is>
+      </c>
+      <c r="AE4" s="11" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="AF4" s="11" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="AG4" s="11" t="inlineStr">
+        <is>
+          <t>across_subject</t>
+        </is>
+      </c>
+      <c r="AH4" s="11" t="inlineStr">
+        <is>
+          <t>A_to_B</t>
+        </is>
+      </c>
+      <c r="AI4" s="11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AJ4" s="11" t="inlineStr">
+        <is>
+          <t>binary_valence_like</t>
+        </is>
+      </c>
+      <c r="AK4" s="11" t="inlineStr">
+        <is>
+          <t>decision-support</t>
+        </is>
+      </c>
+      <c r="AL4" s="8" t="inlineStr">
+        <is>
+          <t>Method-choice analysis performed before locking confirmatory settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Model-comparison</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Secondary decision-support</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Stage 3 - Model lock</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Running</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 4 Supporting robustness</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Robustness support</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>Chapter 5</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>Interpretation limits</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>cross_person_transfer</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>late_only</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>emo_only</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>video_only</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>weighted_only</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>temporal</t>
+        </is>
+      </c>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>mild_imbalance</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>supporting_robustness</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>confirmatory_cross_person_transfer</t>
+        </is>
+      </c>
+      <c r="AF5" s="4" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="AG5" s="4" t="inlineStr">
+        <is>
+          <t>session_level</t>
+        </is>
+      </c>
+      <c r="AH5" s="4" t="inlineStr">
+        <is>
+          <t>B_to_A</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
+        <is>
+          <t>fine_emotion</t>
+        </is>
+      </c>
+      <c r="AK5" s="4" t="inlineStr">
+        <is>
+          <t>exploratory</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Hypothesis-generating extension outside confirmatory core.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Preprocessing-feature</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Secondary decision-support / robustness</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Stage 4 - Feature/preprocessing lock</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Chapter 5 Discussion</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>Exploratory observation</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="R6" s="11" t="inlineStr">
+        <is>
+          <t>AI/tool transparency</t>
+        </is>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>held_out_session</t>
+        </is>
+      </c>
+      <c r="X6" s="11" t="inlineStr">
+        <is>
+          <t>rating_only</t>
+        </is>
+      </c>
+      <c r="Y6" s="11" t="inlineStr">
+        <is>
+          <t>audiovisual_only</t>
+        </is>
+      </c>
+      <c r="Z6" s="11" t="inlineStr">
+        <is>
+          <t>min_count_threshold</t>
+        </is>
+      </c>
+      <c r="AA6" s="11" t="inlineStr">
+        <is>
+          <t>weak_split_demo</t>
+        </is>
+      </c>
+      <c r="AB6" s="11" t="inlineStr">
+        <is>
+          <t>severe_imbalance</t>
+        </is>
+      </c>
+      <c r="AC6" s="11" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="AD6" s="11" t="inlineStr">
+        <is>
+          <t>discussion_limitations</t>
+        </is>
+      </c>
+      <c r="AE6" s="11" t="inlineStr">
+        <is>
+          <t>robustness_support</t>
+        </is>
+      </c>
+      <c r="AF6" s="11" t="inlineStr">
+        <is>
+          <t>modality</t>
+        </is>
+      </c>
+      <c r="AG6" s="11" t="inlineStr">
+        <is>
+          <t>task_level</t>
+        </is>
+      </c>
+      <c r="AH6" s="11" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="AI6" s="11" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="AJ6" s="11" t="inlineStr">
+        <is>
+          <t>custom_target</t>
+        </is>
+      </c>
+      <c r="AK6" s="11" t="inlineStr">
+        <is>
+          <t>data slice</t>
+        </is>
+      </c>
+      <c r="AL6" s="8" t="inlineStr">
+        <is>
+          <t>Explicit subset policy over subjects/sessions/tasks/modalities/labels used by runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Exploratory extension</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Stage 5 - Confirmatory analysis</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>On hold</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Exploratory</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>Reproducibility</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>custom_window</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>task_specific_other</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>appendix_exploratory</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>weak_split_demo_only</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr">
+        <is>
+          <t>subject_session</t>
+        </is>
+      </c>
+      <c r="AG7" s="4" t="inlineStr">
+        <is>
+          <t>modality_level</t>
+        </is>
+      </c>
+      <c r="AH7" s="4" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="AK7" s="4" t="inlineStr">
+        <is>
+          <t>grouping strategy</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Explicit train/test grouping logic and split family for claim-matched evaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Confirmatory core</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Stage 6 - Robustness analysis</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Dropped</t>
+        </is>
+      </c>
+      <c r="R8" s="11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AE8" s="11" t="inlineStr">
+        <is>
+          <t>diagnostic_only</t>
+        </is>
+      </c>
+      <c r="AF8" s="11" t="inlineStr">
+        <is>
+          <t>task_modality</t>
+        </is>
+      </c>
+      <c r="AG8" s="11" t="inlineStr">
+        <is>
+          <t>task_modality_level</t>
+        </is>
+      </c>
+      <c r="AK8" s="11" t="inlineStr">
+        <is>
+          <t>weak split demo</t>
+        </is>
+      </c>
+      <c r="AL8" s="8" t="inlineStr">
+        <is>
+          <t>Intentionally weak split used only to demonstrate inflation risk; not confirmatory evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>External exploratory</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Stage 7 - Exploratory extension</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>exploratory_only</t>
+        </is>
+      </c>
+      <c r="AF9" s="4" t="inlineStr">
+        <is>
+          <t>custom_group</t>
+        </is>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>mixed_level</t>
+        </is>
+      </c>
+      <c r="AK9" s="4" t="inlineStr">
+        <is>
+          <t>construct validity</t>
+        </is>
+      </c>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>How well labels/features operationalize intended constructs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="AK10" s="11" t="inlineStr">
+        <is>
+          <t>internal validity</t>
+        </is>
+      </c>
+      <c r="AL10" s="8" t="inlineStr">
+        <is>
+          <t>Protection against confounds and leakage in design and execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="AK11" s="4" t="inlineStr">
+        <is>
+          <t>statistical conclusion validity</t>
+        </is>
+      </c>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Reliability of metric-based inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="AK12" s="11" t="inlineStr">
+        <is>
+          <t>external validity</t>
+        </is>
+      </c>
+      <c r="AL12" s="8" t="inlineStr">
+        <is>
+          <t>Extent findings transfer to other data contexts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="AK13" s="4" t="inlineStr">
+        <is>
+          <t>leakage</t>
+        </is>
+      </c>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Train-test information contamination that inflates apparent performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="AK14" s="11" t="inlineStr">
+        <is>
+          <t>domain shift</t>
+        </is>
+      </c>
+      <c r="AL14" s="8" t="inlineStr">
+        <is>
+          <t>Distribution shift between train and test domains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="AK15" s="4" t="inlineStr">
+        <is>
+          <t>interpretability stability</t>
+        </is>
+      </c>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Consistency of model-behavior explanation signals across folds.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="A1:AJ1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Thesis Experiment Program Dashboard (v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Program state summary</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Experiments by category</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>Experiments by evidential role</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>Experiments by data slice</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>Experiments by grouping strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Total number of experiments</t>
+        </is>
+      </c>
+      <c r="B4" s="11">
+        <f>COUNTA(Master_Experiments!$A$2:$A$500)</f>
+        <v/>
+      </c>
+      <c r="D4" s="4">
+        <f>Dictionary_Validation!A3</f>
+        <v/>
+      </c>
+      <c r="E4" s="4">
+        <f>COUNTIF(Master_Experiments!$C:$C,D4)</f>
+        <v/>
+      </c>
+      <c r="G4" s="17">
+        <f>Dictionary_Validation!B3</f>
+        <v/>
+      </c>
+      <c r="H4" s="4">
+        <f>COUNTIF(Master_Experiments!$D:$D,G4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="4">
+        <f>IFERROR(Data_Selection_Design!$A2,"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="4">
+        <f>IF(J4="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J4)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J4,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M4" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A2,"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="4">
+        <f>IF(M4="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M4)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M4,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Completed experiments</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>COUNTIF(Master_Experiments!$AA$2:$AA$500,"Completed")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>Dictionary_Validation!A4</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>COUNTIF(Master_Experiments!$C:$C,D5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="17">
+        <f>Dictionary_Validation!B4</f>
+        <v/>
+      </c>
+      <c r="H5" s="4">
+        <f>COUNTIF(Master_Experiments!$D:$D,G5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="4">
+        <f>IFERROR(Data_Selection_Design!$A3,"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>IF(J5="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J5)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J5,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M5" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A3,"")</f>
+        <v/>
+      </c>
+      <c r="N5" s="4">
+        <f>IF(M5="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M5)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M5,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Critical experiments completed</t>
+        </is>
+      </c>
+      <c r="B6" s="11">
+        <f>COUNTIFS(Master_Experiments!$F$2:$F$500,"Critical",Master_Experiments!$AA$2:$AA$500,"Completed")</f>
+        <v/>
+      </c>
+      <c r="D6" s="4">
+        <f>Dictionary_Validation!A5</f>
+        <v/>
+      </c>
+      <c r="E6" s="4">
+        <f>COUNTIF(Master_Experiments!$C:$C,D6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>Dictionary_Validation!B5</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>COUNTIF(Master_Experiments!$D:$D,G6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="4">
+        <f>IFERROR(Data_Selection_Design!$A4,"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="4">
+        <f>IF(J6="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J6)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J6,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M6" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A4,"")</f>
+        <v/>
+      </c>
+      <c r="N6" s="4">
+        <f>IF(M6="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M6)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M6,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Open decisions</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>COUNTIF(Decision_Log!$M$2:$M$500,"Open")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>Dictionary_Validation!A6</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>COUNTIF(Master_Experiments!$C:$C,D7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>Dictionary_Validation!B6</f>
+        <v/>
+      </c>
+      <c r="H7" s="4">
+        <f>COUNTIF(Master_Experiments!$D:$D,G7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="4">
+        <f>IFERROR(Data_Selection_Design!$A5,"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="4">
+        <f>IF(J7="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J7)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J7,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M7" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A5,"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="4">
+        <f>IF(M7="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M7)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M7,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Locked decisions</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>COUNTIF(Decision_Log!$M$2:$M$500,"Locked")</f>
+        <v/>
+      </c>
+      <c r="D8" s="4">
+        <f>Dictionary_Validation!A7</f>
+        <v/>
+      </c>
+      <c r="E8" s="4">
+        <f>COUNTIF(Master_Experiments!$C:$C,D8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>Dictionary_Validation!B7</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(Master_Experiments!$D:$D,G8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="4">
+        <f>IFERROR(Data_Selection_Design!$A6,"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="4">
+        <f>IF(J8="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J8)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J8,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M8" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A6,"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="4">
+        <f>IF(M8="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M8)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M8,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Target locked?</t>
+        </is>
+      </c>
+      <c r="B9" s="4">
+        <f>IF(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$M:$M,"Locked")&gt;0,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="D9" s="4">
+        <f>Dictionary_Validation!A8</f>
+        <v/>
+      </c>
+      <c r="E9" s="4">
+        <f>COUNTIF(Master_Experiments!$C:$C,D9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="4">
+        <f>IFERROR(Data_Selection_Design!$A7,"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="4">
+        <f>IF(J9="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J9)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J9,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M9" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A7,"")</f>
+        <v/>
+      </c>
+      <c r="N9" s="4">
+        <f>IF(M9="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M9)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M9,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Split locked?</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>IF(COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$M:$M,"Locked")&gt;0,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>Dictionary_Validation!A9</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>COUNTIF(Master_Experiments!$C:$C,D10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="4">
+        <f>IFERROR(Data_Selection_Design!$A8,"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="4">
+        <f>IF(J10="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J10)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J10,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A8,"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="4">
+        <f>IF(M10="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M10)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M10,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Model locked?</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="J11" s="4">
+        <f>IFERROR(Data_Selection_Design!$A9,"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="4">
+        <f>IF(J11="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J11)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J11,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A9,"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="4">
+        <f>IF(M11="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M11)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M11,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Feature/preprocessing locked?</t>
+        </is>
+      </c>
+      <c r="B12" s="11">
+        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="J12" s="4">
+        <f>IFERROR(Data_Selection_Design!$A10,"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>IF(J12="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J12)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J12,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A10,"")</f>
+        <v/>
+      </c>
+      <c r="N12" s="4">
+        <f>IF(M12="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M12)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M12,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Confirmatory eligibility achieved?</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
+        <f>IF(COUNTIFS(Confirmatory_Set!$J:$J,"YES")=COUNTIFS(Confirmatory_Set!$A:$A,"&lt;&gt;"),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="J13" s="4">
+        <f>IFERROR(Data_Selection_Design!$A11,"")</f>
+        <v/>
+      </c>
+      <c r="K13" s="4">
+        <f>IF(J13="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J13)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J13,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M13" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A11,"")</f>
+        <v/>
+      </c>
+      <c r="N13" s="4">
+        <f>IF(M13="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M13)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M13,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Confirmatory ready for Chapter 4?</t>
+        </is>
+      </c>
+      <c r="B14" s="11">
+        <f>IF(AND(B13="YES",COUNTIFS(Confirmatory_Set!$H:$H,"YES",Confirmatory_Set!$G:$G,"YES",Confirmatory_Set!$I:$I,"YES")=COUNTIFS(Confirmatory_Set!$H:$H,"YES")),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="J14" s="4">
+        <f>IFERROR(Data_Selection_Design!$A12,"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="4">
+        <f>IF(J14="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J14)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J14,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M14" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A12,"")</f>
+        <v/>
+      </c>
+      <c r="N14" s="4">
+        <f>IF(M14="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M14)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M14,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Experiments mapped to Chapter 4 main results</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <f>COUNTIFS(Thesis_Map!$B$2:$B$500,"Chapter 4",Thesis_Map!$E$2:$E$500,"Main")</f>
+        <v/>
+      </c>
+      <c r="J15" s="4">
+        <f>IFERROR(Data_Selection_Design!$A13,"")</f>
+        <v/>
+      </c>
+      <c r="K15" s="4">
+        <f>IF(J15="","",SUMPRODUCT((Run_Log!$F$2:$F$2000=J15)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$F$2:$F$2000,J15,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+      <c r="M15" s="4">
+        <f>IFERROR(Grouping_Strategy_Map!$A13,"")</f>
+        <v/>
+      </c>
+      <c r="N15" s="4">
+        <f>IF(M15="","",SUMPRODUCT((Run_Log!$G$2:$G$2000=M15)*(Run_Log!$B$2:$B$2000&lt;&gt;"")/IFERROR(COUNTIFS(Run_Log!$G$2:$G$2000,M15,Run_Log!$B$2:$B$2000,Run_Log!$B$2:$B$2000),1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Experiments mapped only to Appendix</t>
+        </is>
+      </c>
+      <c r="B16" s="11">
+        <f>COUNTIF(Thesis_Map!$B$2:$B$500,"Appendix")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Claims with Evidence_Status = supported</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <f>COUNTIF(Claim_Ledger!$E$2:$E$500,"supported")</f>
+        <v/>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Quick comparison counts (run-level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Claims with Evidence_Status = partial</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
+        <f>COUNTIF(Claim_Ledger!$E$2:$E$500,"partial")</f>
+        <v/>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Pooled task runs</t>
+        </is>
+      </c>
+      <c r="E18" s="11">
+        <f>COUNTIF(Run_Log!$Q$2:$Q$2000,"pooled_all_tasks")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Claims with Evidence_Status = open</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <f>COUNTIF(Claim_Ledger!$E$2:$E$500,"open")</f>
+        <v/>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Task-specific runs</t>
+        </is>
+      </c>
+      <c r="E19" s="4">
+        <f>COUNTIFS(Run_Log!$Q$2:$Q$2000,"&lt;&gt;",Run_Log!$Q$2:$Q$2000,"&lt;&gt;pooled_all_tasks")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>AI log entries</t>
+        </is>
+      </c>
+      <c r="B20" s="11">
+        <f>COUNTA(AI_Usage_Log!$A$2:$A$500)</f>
+        <v/>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Pooled modality runs</t>
+        </is>
+      </c>
+      <c r="E20" s="11">
+        <f>COUNTIF(Run_Log!$R$2:$R$2000,"pooled_all_modalities")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Open ethics/governance notes</t>
+        </is>
+      </c>
+      <c r="B21" s="4">
+        <f>COUNTIF(Ethics_Governance_Notes!$G$2:$G$500,"Open")</f>
+        <v/>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Modality-specific runs</t>
+        </is>
+      </c>
+      <c r="E21" s="4">
+        <f>COUNTIFS(Run_Log!$R$2:$R$2000,"&lt;&gt;",Run_Log!$R$2:$R$2000,"&lt;&gt;pooled_all_modalities")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Runs flagged with imbalance warning</t>
+        </is>
+      </c>
+      <c r="B22" s="11">
+        <f>COUNTIFS(Run_Log!$Z$2:$Z$2000,"mild_imbalance")+COUNTIFS(Run_Log!$Z$2:$Z$2000,"severe_imbalance")</f>
+        <v/>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Within-person runs</t>
+        </is>
+      </c>
+      <c r="E22" s="11">
+        <f>SUMPRODUCT((Grouping_Strategy_Map!$C$2:$C$200="within_subject")*COUNTIF(Run_Log!$G$2:$G$2000,Grouping_Strategy_Map!$A$2:$A$200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Runs flagged with leakage warning/fail</t>
+        </is>
+      </c>
+      <c r="B23" s="4">
+        <f>COUNTIFS(Run_Log!$AA$2:$AA$2000,"warning")+COUNTIFS(Run_Log!$AA$2:$AA$2000,"failed")</f>
+        <v/>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Cross-person runs</t>
+        </is>
+      </c>
+      <c r="E23" s="4">
+        <f>SUMPRODUCT((Grouping_Strategy_Map!$C$2:$C$200="cross_person")*COUNTIF(Run_Log!$G$2:$G$2000,Grouping_Strategy_Map!$A$2:$A$200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Distinct data slices used in Run_Log</t>
+        </is>
+      </c>
+      <c r="B24" s="11">
+        <f>SUMPRODUCT((Run_Log!$F$2:$F$2000&lt;&gt;"")/COUNTIF(Run_Log!$F$2:$F$2000,Run_Log!$F$2:$F$2000&amp;""))</f>
+        <v/>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Temporal split runs</t>
+        </is>
+      </c>
+      <c r="E24" s="11">
+        <f>SUMPRODUCT((Grouping_Strategy_Map!$C$2:$C$200="temporal")*COUNTIF(Run_Log!$G$2:$G$2000,Grouping_Strategy_Map!$A$2:$A$200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Distinct grouping strategies used in Run_Log</t>
+        </is>
+      </c>
+      <c r="B25" s="4">
+        <f>SUMPRODUCT((Run_Log!$G$2:$G$2000&lt;&gt;"")/COUNTIF(Run_Log!$G$2:$G$2000,Run_Log!$G$2:$G$2000&amp;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Runs with Data_Slice_ID recorded</t>
+        </is>
+      </c>
+      <c r="B26" s="11">
+        <f>COUNTIF(Run_Log!$F$2:$F$2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Runs with Grouping_Strategy_ID recorded</t>
+        </is>
+      </c>
+      <c r="B27" s="4">
+        <f>COUNTIF(Run_Log!$G$2:$G$2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B9:B14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>B9="YES"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="4">
+      <formula>B9="NO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Claim_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Claim_Text</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Claim_Type</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Supported_By_Experiments</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Evidence_Status</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Writing_Location</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Interpretation_Limit</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Primary within-person held-out-session decoding demonstrates meaningful generalization under locked pipeline.</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Confirmatory finding</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>E16,E12,E13,E14</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 4</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Interpret only within claim-matched split and current dataset scope.</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Frozen directional cross-person transfer indicates cross-case portability under domain shift.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Confirmatory finding</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>E17,E12,E13</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Chapter 4</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Not a population-level generalization claim.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Method lock decisions reduce leakage risk and interpretation drift.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Method-choice</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>E01,E04,E05,E06,E09,E11</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Governance claim; not a performance claim.</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H31"/>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Claim_Type</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Evidence_Status</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Writing_Location</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1551,7 +4268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5070,34 +7787,4052 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y41"/>
+  <dimension ref="A1:R41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Data_Slice_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Slice_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Subject_Scope</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Session_Scope</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Time_Window</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Task_Scope</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Modality_Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Target_Type</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Label_Set</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Inclusion_Rule</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion_Rule</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>Class_Balance_Policy</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Minimum_Samples_Rule</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Leakage_Risk</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Valid_Use_Case</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Thesis_Use</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>DS01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>All subjects, all sessions, pooled task, pooled modality, coarse_affect</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Global baseline for target/split/model method-choice comparisons.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>All QC-passed repeated-session beta maps with valid labels.</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>Drop failed-preprocessing rows and missing targets.</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>Prefer &gt;=20 per class before claim-level interpretation.</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P2" s="8" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>DS02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Subject-specific pooled-task pooled-modality</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Primary within-person held-out-session claim support.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>single_subject</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>held_out_session</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>One subject at a time with all eligible sessions.</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>No cross-subject pooling inside fold-level fit.</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>weighted_only</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Per-class floor checked per subject.</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>main_confirmatory</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Matches held-out-session inference boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>DS03</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Task-specific pooled-modality</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Task pooling vs task-specific method-choice and diagnostics.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>task_specific_other</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect by task</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Restrict each run to one task family.</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Exclude off-task records for that run.</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>Minimum counts checked per task-specific slice.</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>DS04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Modality-specific pooled-task</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Modality pooling vs modality-specific method-choice checks.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>audio_only</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>One modality family per run (audio/video/audiovisual variants).</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Exclude other modalities in each modality-specific run.</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Check sample sufficiency per modality variant.</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Seed modality is audio_only; clone row for other modalities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>DS05</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Subject-specific task x modality subset</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Fine-grained diagnostic sensitivity slices.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>single_subject</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>task_specific_other</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>audiovisual_only</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Single subject + selected task + selected modality combination.</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Exclude all records outside the chosen intersection.</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>min_count_threshold</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>Hard floor required before reporting.</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>diagnostic_only</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>discussion_limitations</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DS06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Early sessions only</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Temporal drift checks and early-to-late transfer design.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>early_only</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>early_window</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Use sessions pre-registered as early window.</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Exclude late-window sessions.</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Check class floor by temporal window.</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>robustness_support</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>supporting_robustness</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>DS07</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Late sessions only</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Temporal drift checks and early-to-late transfer design.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>late_only</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>late_window</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Use sessions pre-registered as late window.</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Exclude early-window sessions.</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>Check class floor by temporal window.</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>robustness_support</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>supporting_robustness</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>DS08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Balanced subset only</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Imbalance-aware sensitivity diagnostics.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Only include rows passing balancing policy.</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Exclude classes below predefined minimum count floor.</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>balanced_subset</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Set explicit class floor in analysis config.</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>robustness_support</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>supporting_robustness</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>Do not replace confirmatory as-is evidence with this slice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="8" t="n"/>
+      <c r="P18" s="8" t="n"/>
+      <c r="Q18" s="8" t="n"/>
+      <c r="R18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
+      <c r="R19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
+      <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="8" t="n"/>
+      <c r="R22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n"/>
+      <c r="Q25" s="3" t="n"/>
+      <c r="R25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="8" t="n"/>
+      <c r="O26" s="8" t="n"/>
+      <c r="P26" s="8" t="n"/>
+      <c r="Q26" s="8" t="n"/>
+      <c r="R26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="n"/>
+      <c r="P28" s="8" t="n"/>
+      <c r="Q28" s="8" t="n"/>
+      <c r="R28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n"/>
+      <c r="R29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="8" t="n"/>
+      <c r="O30" s="8" t="n"/>
+      <c r="P30" s="8" t="n"/>
+      <c r="Q30" s="8" t="n"/>
+      <c r="R30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="3" t="n"/>
+      <c r="Q31" s="3" t="n"/>
+      <c r="R31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="8" t="n"/>
+      <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="8" t="n"/>
+      <c r="R32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
+      <c r="R33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
+      <c r="O34" s="8" t="n"/>
+      <c r="P34" s="8" t="n"/>
+      <c r="Q34" s="8" t="n"/>
+      <c r="R34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="n"/>
+      <c r="Q35" s="3" t="n"/>
+      <c r="R35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="8" t="n"/>
+      <c r="O36" s="8" t="n"/>
+      <c r="P36" s="8" t="n"/>
+      <c r="Q36" s="8" t="n"/>
+      <c r="R36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="3" t="n"/>
+      <c r="Q37" s="3" t="n"/>
+      <c r="R37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="8" t="n"/>
+      <c r="O38" s="8" t="n"/>
+      <c r="P38" s="8" t="n"/>
+      <c r="Q38" s="8" t="n"/>
+      <c r="R38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
+      <c r="R39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="8" t="n"/>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="8" t="n"/>
+      <c r="R40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="n"/>
+      <c r="Q41" s="3" t="n"/>
+      <c r="R41" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R41"/>
+  <dataValidations count="9">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Subject_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Session_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Task_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Modality_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Target_Type</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Class_Balance_Policy</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Leakage_Risk_Level</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Use_Case</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Thesis_Use_Tag</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Grouping_Strategy_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Strategy_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Split_Family</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Train_Group_Unit</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Test_Group_Unit</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Grouping_Level</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Train_Rule</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Test_Rule</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Leakage_Safeguard</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Suitable_For</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Not_Suitable_For</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Interpretation_Boundary</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>Typical_Experiments</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Thesis_Section</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>GS01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>within-subject LOSO-session</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>within_subject</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>subject_session</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>within_subject</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Per subject: train on all but one session.</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Per subject: test on held-out session.</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>No held-out session rows in any train-side fit/tune stage.</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>confirmatory_cross_person_transfer</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>Supports within-person held-out-session claim only.</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>E04,E16</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 4 Main results</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>GS02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>pooled-task within-subject LOSO-session</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>within_subject</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>subject_session</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>within_subject</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Within each subject, pool tasks and hold out one session.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Evaluate on held-out session with pooled task scope.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>No test-session information in pooled train transforms.</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>confirmatory_cross_person_transfer</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Within-person conclusion under pooled task policy.</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>E02,E16</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Chapter 3 Method choice</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>GS03</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>task-specific within-subject LOSO-session</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>within_subject</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>subject_session</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>task_level</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Within each subject/task, hold out one session.</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Test on same-task held-out session.</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Task-specific split manifests and train-only preprocessing.</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>confirmatory_cross_person_transfer</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Task-conditioned within-person evidence only.</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>E02,E15</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 3 Method choice</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>GS04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>modality-specific within-subject LOSO-session</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>within_subject</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>subject_session</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>modality_level</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Within each subject/modality, hold out one session.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Test on same-modality held-out session.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Modality-specific fold manifests with strict train-only fit.</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>confirmatory_cross_person_transfer</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Modality-conditioned within-person evidence only.</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>E03,E15</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Chapter 3 Method choice</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>GS05</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>early-train late-test</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>temporal</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>session_level</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Train on pre-defined early sessions.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Test on disjoint late sessions.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Fixed temporal boundary and no late-session tuning.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>robustness_support</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Temporal transfer sensitivity, not the primary confirmatory claim.</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>E04,E15</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 4 Supporting robustness</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>GS06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>frozen cross-person transfer A-&gt;B</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>cross_person</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>across_subject</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Fit on subject A only (frozen pipeline).</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Evaluate on subject B without refit/re-tune.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>No test-subject fitting; strict direction lock.</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>confirmatory_cross_person_transfer</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Directional transfer under domain shift only.</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>E05,E17</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Chapter 4 Main results</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>GS07</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>frozen cross-person transfer B-&gt;A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>cross_person</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>across_subject</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Fit on subject B only (frozen pipeline).</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Evaluate on subject A without refit/re-tune.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>No test-subject fitting; strict direction lock.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>confirmatory_cross_person_transfer</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Directional transfer under domain shift only.</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>E05,E17</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 4 Main results</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>GS08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>weak split inflation demo</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>weak_split_demo</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>custom_group</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>custom_group</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>mixed_level</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Use intentionally weaker split variant for contrast.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Evaluate inflation magnitude vs strict split.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Tag as weak split and exclude from confirmatory claims.</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>weak_split_demo_only</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Inflation demonstration only; non-confirmatory.</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Chapter 3 Method choice</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>Permitted only as cautionary demonstration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>GS09</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>task x modality diagnostic split</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>task_modality</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>task_modality</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>task_modality_level</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Train within selected task/modality intersections.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Test on matched or held-out intersections per protocol.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Pre-registered intersection mapping and no adaptive relabeling.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>diagnostic_only</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Diagnostic sensitivity only; not core evidence.</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 5 Discussion</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="8" t="n"/>
+      <c r="O26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+      <c r="O29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="8" t="n"/>
+      <c r="O30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
+      <c r="O34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="8" t="n"/>
+      <c r="O36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="8" t="n"/>
+      <c r="O38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O41"/>
+  <dataValidations count="7">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Split_Family</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Group_Unit</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Group_Unit</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Grouping_Level</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Use_Case</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Use_Case</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Reporting_Destination</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Data Profile and Imbalance Diagnostics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>How to use</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Paste exported counts into Count columns (or maintain manually). Formulas compute shares, imbalance flags, and sparsity flags.</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Threshold controls</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Profile summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Sparse count threshold</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Total_subject_samples</t>
+        </is>
+      </c>
+      <c r="G7" s="4">
+        <f>SUM(B13:B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Mild imbalance ratio (max/min)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Total_session_samples</t>
+        </is>
+      </c>
+      <c r="G8" s="11">
+        <f>SUM(B25:B34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Severe imbalance ratio (max/min)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Total_task_samples</t>
+        </is>
+      </c>
+      <c r="G9" s="4">
+        <f>SUM(B39:B45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Total_modality_samples</t>
+        </is>
+      </c>
+      <c r="G10" s="11">
+        <f>SUM(B50:B55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Counts by subject</t>
+        </is>
+      </c>
+      <c r="G11" s="4">
+        <f>SUM(B60:B65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Subject_ID</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Share_of_Block</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="G12" s="11">
+        <f>IFERROR(MAX(B60:B65)/MIN(B60:B65),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>sub-001</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3">
+        <f>IFERROR(B13/SUM($B$13:$B$20),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>IF(B13="","",IF(B13&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="G13" s="4">
+        <f>IF(B60="","",IF(OR(MIN(B60:B65)=0,G12&gt;$B$9),"SEVERE_IMBALANCE",IF(G12&gt;$B$8,"MILD_IMBALANCE","BALANCED")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>sub-002</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8">
+        <f>IFERROR(B14/SUM($B$13:$B$20),0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="8">
+        <f>IF(B14="","",IF(B14&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>sub-003</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3">
+        <f>IFERROR(B15/SUM($B$13:$B$20),0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>IF(B15="","",IF(B15&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>sub-004</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8">
+        <f>IFERROR(B16/SUM($B$13:$B$20),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="8">
+        <f>IF(B16="","",IF(B16&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>sub-005</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3">
+        <f>IFERROR(B17/SUM($B$13:$B$20),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="3">
+        <f>IF(B17="","",IF(B17&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>sub-006</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8">
+        <f>IFERROR(B18/SUM($B$13:$B$20),0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="8">
+        <f>IF(B18="","",IF(B18&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>sub-007</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3">
+        <f>IFERROR(B19/SUM($B$13:$B$20),0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>IF(B19="","",IF(B19&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>sub-008</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8">
+        <f>IFERROR(B20/SUM($B$13:$B$20),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>IF(B20="","",IF(B20&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E20" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Counts by session</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Session_ID</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Share_of_Block</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ses-01</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3">
+        <f>IFERROR(B25/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="3">
+        <f>IF(B25="","",IF(B25&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>ses-02</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8">
+        <f>IFERROR(B26/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="8">
+        <f>IF(B26="","",IF(B26&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ses-03</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3">
+        <f>IFERROR(B27/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D27" s="3">
+        <f>IF(B27="","",IF(B27&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>ses-04</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8">
+        <f>IFERROR(B28/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D28" s="8">
+        <f>IF(B28="","",IF(B28&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ses-05</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3">
+        <f>IFERROR(B29/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="3">
+        <f>IF(B29="","",IF(B29&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>ses-06</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8">
+        <f>IFERROR(B30/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D30" s="8">
+        <f>IF(B30="","",IF(B30&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>ses-07</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3">
+        <f>IFERROR(B31/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D31" s="3">
+        <f>IF(B31="","",IF(B31&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>ses-08</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8">
+        <f>IFERROR(B32/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D32" s="8">
+        <f>IF(B32="","",IF(B32&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>ses-09</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3">
+        <f>IFERROR(B33/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D33" s="3">
+        <f>IF(B33="","",IF(B33&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>ses-10</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8">
+        <f>IFERROR(B34/SUM($B$25:$B$34),0)</f>
+        <v/>
+      </c>
+      <c r="D34" s="8">
+        <f>IF(B34="","",IF(B34&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E34" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Counts by task</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Task_ID</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Share_of_Block</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3">
+        <f>IFERROR(B39/SUM($B$39:$B$45),0)</f>
+        <v/>
+      </c>
+      <c r="D39" s="3">
+        <f>IF(B39="","",IF(B39&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>passive_only</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8">
+        <f>IFERROR(B40/SUM($B$39:$B$45),0)</f>
+        <v/>
+      </c>
+      <c r="D40" s="8">
+        <f>IF(B40="","",IF(B40&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>emo_only</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3">
+        <f>IFERROR(B41/SUM($B$39:$B$45),0)</f>
+        <v/>
+      </c>
+      <c r="D41" s="3">
+        <f>IF(B41="","",IF(B41&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>rating_only</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8">
+        <f>IFERROR(B42/SUM($B$39:$B$45),0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="8">
+        <f>IF(B42="","",IF(B42&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>task_specific_other</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3">
+        <f>IFERROR(B43/SUM($B$39:$B$45),0)</f>
+        <v/>
+      </c>
+      <c r="D43" s="3">
+        <f>IF(B43="","",IF(B43&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>custom_task_1</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8">
+        <f>IFERROR(B44/SUM($B$39:$B$45),0)</f>
+        <v/>
+      </c>
+      <c r="D44" s="8">
+        <f>IF(B44="","",IF(B44&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>custom_task_2</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3">
+        <f>IFERROR(B45/SUM($B$39:$B$45),0)</f>
+        <v/>
+      </c>
+      <c r="D45" s="3">
+        <f>IF(B45="","",IF(B45&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E45" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Counts by modality</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Modality_ID</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Share_of_Block</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8">
+        <f>IFERROR(B50/SUM($B$50:$B$55),0)</f>
+        <v/>
+      </c>
+      <c r="D50" s="8">
+        <f>IF(B50="","",IF(B50&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>audio_only</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3">
+        <f>IFERROR(B51/SUM($B$50:$B$55),0)</f>
+        <v/>
+      </c>
+      <c r="D51" s="3">
+        <f>IF(B51="","",IF(B51&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>video_only</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8">
+        <f>IFERROR(B52/SUM($B$50:$B$55),0)</f>
+        <v/>
+      </c>
+      <c r="D52" s="8">
+        <f>IF(B52="","",IF(B52&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>audiovisual_only</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3">
+        <f>IFERROR(B53/SUM($B$50:$B$55),0)</f>
+        <v/>
+      </c>
+      <c r="D53" s="3">
+        <f>IF(B53="","",IF(B53&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>custom_modality_1</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8">
+        <f>IFERROR(B54/SUM($B$50:$B$55),0)</f>
+        <v/>
+      </c>
+      <c r="D54" s="8">
+        <f>IF(B54="","",IF(B54&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>custom_modality_2</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3">
+        <f>IFERROR(B55/SUM($B$50:$B$55),0)</f>
+        <v/>
+      </c>
+      <c r="D55" s="3">
+        <f>IF(B55="","",IF(B55&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E55" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Counts by target/class</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Target_or_Class_ID</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Share_of_Block</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect_neg</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8">
+        <f>IFERROR(B60/SUM($B$60:$B$65),0)</f>
+        <v/>
+      </c>
+      <c r="D60" s="8">
+        <f>IF(B60="","",IF(OR(MIN($B$60:$B$65)=0,MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$9),"SEVERE_IMBALANCE",IF(MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$8,"MILD_IMBALANCE","BALANCED")))</f>
+        <v/>
+      </c>
+      <c r="E60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect_neu</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3">
+        <f>IFERROR(B61/SUM($B$60:$B$65),0)</f>
+        <v/>
+      </c>
+      <c r="D61" s="3">
+        <f>IF(B61="","",IF(OR(MIN($B$60:$B$65)=0,MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$9),"SEVERE_IMBALANCE",IF(MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$8,"MILD_IMBALANCE","BALANCED")))</f>
+        <v/>
+      </c>
+      <c r="E61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect_pos</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8">
+        <f>IFERROR(B62/SUM($B$60:$B$65),0)</f>
+        <v/>
+      </c>
+      <c r="D62" s="8">
+        <f>IF(B62="","",IF(OR(MIN($B$60:$B$65)=0,MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$9),"SEVERE_IMBALANCE",IF(MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$8,"MILD_IMBALANCE","BALANCED")))</f>
+        <v/>
+      </c>
+      <c r="E62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>binary_neg</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3">
+        <f>IFERROR(B63/SUM($B$60:$B$65),0)</f>
+        <v/>
+      </c>
+      <c r="D63" s="3">
+        <f>IF(B63="","",IF(OR(MIN($B$60:$B$65)=0,MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$9),"SEVERE_IMBALANCE",IF(MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$8,"MILD_IMBALANCE","BALANCED")))</f>
+        <v/>
+      </c>
+      <c r="E63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>binary_pos</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8">
+        <f>IFERROR(B64/SUM($B$60:$B$65),0)</f>
+        <v/>
+      </c>
+      <c r="D64" s="8">
+        <f>IF(B64="","",IF(OR(MIN($B$60:$B$65)=0,MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$9),"SEVERE_IMBALANCE",IF(MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$8,"MILD_IMBALANCE","BALANCED")))</f>
+        <v/>
+      </c>
+      <c r="E64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>custom_class_1</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3">
+        <f>IFERROR(B65/SUM($B$60:$B$65),0)</f>
+        <v/>
+      </c>
+      <c r="D65" s="3">
+        <f>IF(B65="","",IF(OR(MIN($B$60:$B$65)=0,MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$9),"SEVERE_IMBALANCE",IF(MAX($B$60:$B$65)/MIN($B$60:$B$65)&gt;$B$8,"MILD_IMBALANCE","BALANCED")))</f>
+        <v/>
+      </c>
+      <c r="E65" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>Counts by Data_Slice_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Data_Slice_ID</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Share_of_Block</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3">
+        <f>IFERROR(Data_Selection_Design!$A2,"")</f>
+        <v/>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3">
+        <f>IFERROR(B71/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D71" s="3">
+        <f>IF(B71="","",IF(B71&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8">
+        <f>IFERROR(Data_Selection_Design!$A3,"")</f>
+        <v/>
+      </c>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8">
+        <f>IFERROR(B72/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D72" s="8">
+        <f>IF(B72="","",IF(B72&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3">
+        <f>IFERROR(Data_Selection_Design!$A4,"")</f>
+        <v/>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3">
+        <f>IFERROR(B73/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D73" s="3">
+        <f>IF(B73="","",IF(B73&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8">
+        <f>IFERROR(Data_Selection_Design!$A5,"")</f>
+        <v/>
+      </c>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="8">
+        <f>IFERROR(B74/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D74" s="8">
+        <f>IF(B74="","",IF(B74&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3">
+        <f>IFERROR(Data_Selection_Design!$A6,"")</f>
+        <v/>
+      </c>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3">
+        <f>IFERROR(B75/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D75" s="3">
+        <f>IF(B75="","",IF(B75&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8">
+        <f>IFERROR(Data_Selection_Design!$A7,"")</f>
+        <v/>
+      </c>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="8">
+        <f>IFERROR(B76/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D76" s="8">
+        <f>IF(B76="","",IF(B76&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3">
+        <f>IFERROR(Data_Selection_Design!$A8,"")</f>
+        <v/>
+      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3">
+        <f>IFERROR(B77/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D77" s="3">
+        <f>IF(B77="","",IF(B77&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8">
+        <f>IFERROR(Data_Selection_Design!$A9,"")</f>
+        <v/>
+      </c>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="8">
+        <f>IFERROR(B78/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D78" s="8">
+        <f>IF(B78="","",IF(B78&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E78" s="8" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3">
+        <f>IFERROR(Data_Selection_Design!$A10,"")</f>
+        <v/>
+      </c>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3">
+        <f>IFERROR(B79/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D79" s="3">
+        <f>IF(B79="","",IF(B79&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8">
+        <f>IFERROR(Data_Selection_Design!$A11,"")</f>
+        <v/>
+      </c>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="8">
+        <f>IFERROR(B80/SUM($B$71:$B$80),0)</f>
+        <v/>
+      </c>
+      <c r="D80" s="8">
+        <f>IF(B80="","",IF(B80&lt;$B$7,"SPARSE","OK"))</f>
+        <v/>
+      </c>
+      <c r="E80" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B3:J4"/>
+    <mergeCell ref="A58:E58"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="6">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AK41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="36" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="30" customWidth="1" min="31" max="31"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="34" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="36" customWidth="1" min="36" max="36"/>
+    <col width="28" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5128,100 +11863,160 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Data_Slice_ID</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Grouping_Strategy_ID</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
           <t>Code_Commit_or_Version</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Config_File_or_Path</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Random_Seed</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Split_ID_or_Fold_Definition</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>Train_Group_Rule</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Test_Group_Rule</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Transfer_Direction</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Session_Coverage</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Task_Coverage</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Modality_Coverage</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>Feature_Set</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>Run_Type</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>Affects_Frozen_Pipeline</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>Eligible_for_Method_Decision</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="X1" s="7" t="inlineStr">
+        <is>
+          <t>Sample_Count</t>
+        </is>
+      </c>
+      <c r="Y1" s="7" t="inlineStr">
+        <is>
+          <t>Class_Counts</t>
+        </is>
+      </c>
+      <c r="Z1" s="7" t="inlineStr">
+        <is>
+          <t>Imbalance_Status</t>
+        </is>
+      </c>
+      <c r="AA1" s="7" t="inlineStr">
+        <is>
+          <t>Leakage_Check_Status</t>
+        </is>
+      </c>
+      <c r="AB1" s="7" t="inlineStr">
         <is>
           <t>Primary_Metric_Value</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="AC1" s="7" t="inlineStr">
         <is>
           <t>Secondary_Metric_1</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="AD1" s="7" t="inlineStr">
         <is>
           <t>Secondary_Metric_2</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="AE1" s="7" t="inlineStr">
         <is>
           <t>Robustness_Output_Summary</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="AF1" s="7" t="inlineStr">
         <is>
           <t>Result_Summary</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="AG1" s="7" t="inlineStr">
         <is>
           <t>Preliminary_Interpretation</t>
         </is>
       </c>
-      <c r="V1" s="7" t="inlineStr">
+      <c r="AH1" s="7" t="inlineStr">
         <is>
           <t>Reviewed</t>
         </is>
       </c>
-      <c r="W1" s="7" t="inlineStr">
+      <c r="AI1" s="7" t="inlineStr">
         <is>
           <t>Used_in_Thesis</t>
         </is>
       </c>
-      <c r="X1" s="7" t="inlineStr">
+      <c r="AJ1" s="7" t="inlineStr">
         <is>
           <t>Artifact_Path</t>
         </is>
       </c>
-      <c r="Y1" s="7" t="inlineStr">
+      <c r="AK1" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5253,6 +12048,18 @@
       <c r="W2" s="8" t="n"/>
       <c r="X2" s="8" t="n"/>
       <c r="Y2" s="8" t="n"/>
+      <c r="Z2" s="8" t="n"/>
+      <c r="AA2" s="8" t="n"/>
+      <c r="AB2" s="8" t="n"/>
+      <c r="AC2" s="8" t="n"/>
+      <c r="AD2" s="8" t="n"/>
+      <c r="AE2" s="8" t="n"/>
+      <c r="AF2" s="8" t="n"/>
+      <c r="AG2" s="8" t="n"/>
+      <c r="AH2" s="8" t="n"/>
+      <c r="AI2" s="8" t="n"/>
+      <c r="AJ2" s="8" t="n"/>
+      <c r="AK2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -5280,6 +12087,18 @@
       <c r="W3" s="3" t="n"/>
       <c r="X3" s="3" t="n"/>
       <c r="Y3" s="3" t="n"/>
+      <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
+      <c r="AB3" s="3" t="n"/>
+      <c r="AC3" s="3" t="n"/>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="3" t="n"/>
+      <c r="AF3" s="3" t="n"/>
+      <c r="AG3" s="3" t="n"/>
+      <c r="AH3" s="3" t="n"/>
+      <c r="AI3" s="3" t="n"/>
+      <c r="AJ3" s="3" t="n"/>
+      <c r="AK3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n"/>
@@ -5307,6 +12126,18 @@
       <c r="W4" s="8" t="n"/>
       <c r="X4" s="8" t="n"/>
       <c r="Y4" s="8" t="n"/>
+      <c r="Z4" s="8" t="n"/>
+      <c r="AA4" s="8" t="n"/>
+      <c r="AB4" s="8" t="n"/>
+      <c r="AC4" s="8" t="n"/>
+      <c r="AD4" s="8" t="n"/>
+      <c r="AE4" s="8" t="n"/>
+      <c r="AF4" s="8" t="n"/>
+      <c r="AG4" s="8" t="n"/>
+      <c r="AH4" s="8" t="n"/>
+      <c r="AI4" s="8" t="n"/>
+      <c r="AJ4" s="8" t="n"/>
+      <c r="AK4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -5334,6 +12165,18 @@
       <c r="W5" s="3" t="n"/>
       <c r="X5" s="3" t="n"/>
       <c r="Y5" s="3" t="n"/>
+      <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="3" t="n"/>
+      <c r="AE5" s="3" t="n"/>
+      <c r="AF5" s="3" t="n"/>
+      <c r="AG5" s="3" t="n"/>
+      <c r="AH5" s="3" t="n"/>
+      <c r="AI5" s="3" t="n"/>
+      <c r="AJ5" s="3" t="n"/>
+      <c r="AK5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -5361,6 +12204,18 @@
       <c r="W6" s="8" t="n"/>
       <c r="X6" s="8" t="n"/>
       <c r="Y6" s="8" t="n"/>
+      <c r="Z6" s="8" t="n"/>
+      <c r="AA6" s="8" t="n"/>
+      <c r="AB6" s="8" t="n"/>
+      <c r="AC6" s="8" t="n"/>
+      <c r="AD6" s="8" t="n"/>
+      <c r="AE6" s="8" t="n"/>
+      <c r="AF6" s="8" t="n"/>
+      <c r="AG6" s="8" t="n"/>
+      <c r="AH6" s="8" t="n"/>
+      <c r="AI6" s="8" t="n"/>
+      <c r="AJ6" s="8" t="n"/>
+      <c r="AK6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -5388,6 +12243,18 @@
       <c r="W7" s="3" t="n"/>
       <c r="X7" s="3" t="n"/>
       <c r="Y7" s="3" t="n"/>
+      <c r="Z7" s="3" t="n"/>
+      <c r="AA7" s="3" t="n"/>
+      <c r="AB7" s="3" t="n"/>
+      <c r="AC7" s="3" t="n"/>
+      <c r="AD7" s="3" t="n"/>
+      <c r="AE7" s="3" t="n"/>
+      <c r="AF7" s="3" t="n"/>
+      <c r="AG7" s="3" t="n"/>
+      <c r="AH7" s="3" t="n"/>
+      <c r="AI7" s="3" t="n"/>
+      <c r="AJ7" s="3" t="n"/>
+      <c r="AK7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n"/>
@@ -5415,6 +12282,18 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
       <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8" t="n"/>
+      <c r="AI8" s="8" t="n"/>
+      <c r="AJ8" s="8" t="n"/>
+      <c r="AK8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -5442,6 +12321,18 @@
       <c r="W9" s="3" t="n"/>
       <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="n"/>
+      <c r="Z9" s="3" t="n"/>
+      <c r="AA9" s="3" t="n"/>
+      <c r="AB9" s="3" t="n"/>
+      <c r="AC9" s="3" t="n"/>
+      <c r="AD9" s="3" t="n"/>
+      <c r="AE9" s="3" t="n"/>
+      <c r="AF9" s="3" t="n"/>
+      <c r="AG9" s="3" t="n"/>
+      <c r="AH9" s="3" t="n"/>
+      <c r="AI9" s="3" t="n"/>
+      <c r="AJ9" s="3" t="n"/>
+      <c r="AK9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
@@ -5469,6 +12360,18 @@
       <c r="W10" s="8" t="n"/>
       <c r="X10" s="8" t="n"/>
       <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8" t="n"/>
+      <c r="AI10" s="8" t="n"/>
+      <c r="AJ10" s="8" t="n"/>
+      <c r="AK10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -5496,6 +12399,18 @@
       <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
+      <c r="AB11" s="3" t="n"/>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="3" t="n"/>
+      <c r="AE11" s="3" t="n"/>
+      <c r="AF11" s="3" t="n"/>
+      <c r="AG11" s="3" t="n"/>
+      <c r="AH11" s="3" t="n"/>
+      <c r="AI11" s="3" t="n"/>
+      <c r="AJ11" s="3" t="n"/>
+      <c r="AK11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
@@ -5523,6 +12438,18 @@
       <c r="W12" s="8" t="n"/>
       <c r="X12" s="8" t="n"/>
       <c r="Y12" s="8" t="n"/>
+      <c r="Z12" s="8" t="n"/>
+      <c r="AA12" s="8" t="n"/>
+      <c r="AB12" s="8" t="n"/>
+      <c r="AC12" s="8" t="n"/>
+      <c r="AD12" s="8" t="n"/>
+      <c r="AE12" s="8" t="n"/>
+      <c r="AF12" s="8" t="n"/>
+      <c r="AG12" s="8" t="n"/>
+      <c r="AH12" s="8" t="n"/>
+      <c r="AI12" s="8" t="n"/>
+      <c r="AJ12" s="8" t="n"/>
+      <c r="AK12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -5550,6 +12477,18 @@
       <c r="W13" s="3" t="n"/>
       <c r="X13" s="3" t="n"/>
       <c r="Y13" s="3" t="n"/>
+      <c r="Z13" s="3" t="n"/>
+      <c r="AA13" s="3" t="n"/>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" s="3" t="n"/>
+      <c r="AD13" s="3" t="n"/>
+      <c r="AE13" s="3" t="n"/>
+      <c r="AF13" s="3" t="n"/>
+      <c r="AG13" s="3" t="n"/>
+      <c r="AH13" s="3" t="n"/>
+      <c r="AI13" s="3" t="n"/>
+      <c r="AJ13" s="3" t="n"/>
+      <c r="AK13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
@@ -5577,6 +12516,18 @@
       <c r="W14" s="8" t="n"/>
       <c r="X14" s="8" t="n"/>
       <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8" t="n"/>
+      <c r="AI14" s="8" t="n"/>
+      <c r="AJ14" s="8" t="n"/>
+      <c r="AK14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -5604,6 +12555,18 @@
       <c r="W15" s="3" t="n"/>
       <c r="X15" s="3" t="n"/>
       <c r="Y15" s="3" t="n"/>
+      <c r="Z15" s="3" t="n"/>
+      <c r="AA15" s="3" t="n"/>
+      <c r="AB15" s="3" t="n"/>
+      <c r="AC15" s="3" t="n"/>
+      <c r="AD15" s="3" t="n"/>
+      <c r="AE15" s="3" t="n"/>
+      <c r="AF15" s="3" t="n"/>
+      <c r="AG15" s="3" t="n"/>
+      <c r="AH15" s="3" t="n"/>
+      <c r="AI15" s="3" t="n"/>
+      <c r="AJ15" s="3" t="n"/>
+      <c r="AK15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
@@ -5631,6 +12594,18 @@
       <c r="W16" s="8" t="n"/>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8" t="n"/>
+      <c r="AI16" s="8" t="n"/>
+      <c r="AJ16" s="8" t="n"/>
+      <c r="AK16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -5658,6 +12633,18 @@
       <c r="W17" s="3" t="n"/>
       <c r="X17" s="3" t="n"/>
       <c r="Y17" s="3" t="n"/>
+      <c r="Z17" s="3" t="n"/>
+      <c r="AA17" s="3" t="n"/>
+      <c r="AB17" s="3" t="n"/>
+      <c r="AC17" s="3" t="n"/>
+      <c r="AD17" s="3" t="n"/>
+      <c r="AE17" s="3" t="n"/>
+      <c r="AF17" s="3" t="n"/>
+      <c r="AG17" s="3" t="n"/>
+      <c r="AH17" s="3" t="n"/>
+      <c r="AI17" s="3" t="n"/>
+      <c r="AJ17" s="3" t="n"/>
+      <c r="AK17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
@@ -5685,6 +12672,18 @@
       <c r="W18" s="8" t="n"/>
       <c r="X18" s="8" t="n"/>
       <c r="Y18" s="8" t="n"/>
+      <c r="Z18" s="8" t="n"/>
+      <c r="AA18" s="8" t="n"/>
+      <c r="AB18" s="8" t="n"/>
+      <c r="AC18" s="8" t="n"/>
+      <c r="AD18" s="8" t="n"/>
+      <c r="AE18" s="8" t="n"/>
+      <c r="AF18" s="8" t="n"/>
+      <c r="AG18" s="8" t="n"/>
+      <c r="AH18" s="8" t="n"/>
+      <c r="AI18" s="8" t="n"/>
+      <c r="AJ18" s="8" t="n"/>
+      <c r="AK18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -5712,6 +12711,18 @@
       <c r="W19" s="3" t="n"/>
       <c r="X19" s="3" t="n"/>
       <c r="Y19" s="3" t="n"/>
+      <c r="Z19" s="3" t="n"/>
+      <c r="AA19" s="3" t="n"/>
+      <c r="AB19" s="3" t="n"/>
+      <c r="AC19" s="3" t="n"/>
+      <c r="AD19" s="3" t="n"/>
+      <c r="AE19" s="3" t="n"/>
+      <c r="AF19" s="3" t="n"/>
+      <c r="AG19" s="3" t="n"/>
+      <c r="AH19" s="3" t="n"/>
+      <c r="AI19" s="3" t="n"/>
+      <c r="AJ19" s="3" t="n"/>
+      <c r="AK19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -5739,6 +12750,18 @@
       <c r="W20" s="8" t="n"/>
       <c r="X20" s="8" t="n"/>
       <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8" t="n"/>
+      <c r="AI20" s="8" t="n"/>
+      <c r="AJ20" s="8" t="n"/>
+      <c r="AK20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -5766,6 +12789,18 @@
       <c r="W21" s="3" t="n"/>
       <c r="X21" s="3" t="n"/>
       <c r="Y21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
+      <c r="AA21" s="3" t="n"/>
+      <c r="AB21" s="3" t="n"/>
+      <c r="AC21" s="3" t="n"/>
+      <c r="AD21" s="3" t="n"/>
+      <c r="AE21" s="3" t="n"/>
+      <c r="AF21" s="3" t="n"/>
+      <c r="AG21" s="3" t="n"/>
+      <c r="AH21" s="3" t="n"/>
+      <c r="AI21" s="3" t="n"/>
+      <c r="AJ21" s="3" t="n"/>
+      <c r="AK21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -5793,6 +12828,18 @@
       <c r="W22" s="8" t="n"/>
       <c r="X22" s="8" t="n"/>
       <c r="Y22" s="8" t="n"/>
+      <c r="Z22" s="8" t="n"/>
+      <c r="AA22" s="8" t="n"/>
+      <c r="AB22" s="8" t="n"/>
+      <c r="AC22" s="8" t="n"/>
+      <c r="AD22" s="8" t="n"/>
+      <c r="AE22" s="8" t="n"/>
+      <c r="AF22" s="8" t="n"/>
+      <c r="AG22" s="8" t="n"/>
+      <c r="AH22" s="8" t="n"/>
+      <c r="AI22" s="8" t="n"/>
+      <c r="AJ22" s="8" t="n"/>
+      <c r="AK22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -5820,6 +12867,18 @@
       <c r="W23" s="3" t="n"/>
       <c r="X23" s="3" t="n"/>
       <c r="Y23" s="3" t="n"/>
+      <c r="Z23" s="3" t="n"/>
+      <c r="AA23" s="3" t="n"/>
+      <c r="AB23" s="3" t="n"/>
+      <c r="AC23" s="3" t="n"/>
+      <c r="AD23" s="3" t="n"/>
+      <c r="AE23" s="3" t="n"/>
+      <c r="AF23" s="3" t="n"/>
+      <c r="AG23" s="3" t="n"/>
+      <c r="AH23" s="3" t="n"/>
+      <c r="AI23" s="3" t="n"/>
+      <c r="AJ23" s="3" t="n"/>
+      <c r="AK23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n"/>
@@ -5847,6 +12906,18 @@
       <c r="W24" s="8" t="n"/>
       <c r="X24" s="8" t="n"/>
       <c r="Y24" s="8" t="n"/>
+      <c r="Z24" s="8" t="n"/>
+      <c r="AA24" s="8" t="n"/>
+      <c r="AB24" s="8" t="n"/>
+      <c r="AC24" s="8" t="n"/>
+      <c r="AD24" s="8" t="n"/>
+      <c r="AE24" s="8" t="n"/>
+      <c r="AF24" s="8" t="n"/>
+      <c r="AG24" s="8" t="n"/>
+      <c r="AH24" s="8" t="n"/>
+      <c r="AI24" s="8" t="n"/>
+      <c r="AJ24" s="8" t="n"/>
+      <c r="AK24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -5874,6 +12945,18 @@
       <c r="W25" s="3" t="n"/>
       <c r="X25" s="3" t="n"/>
       <c r="Y25" s="3" t="n"/>
+      <c r="Z25" s="3" t="n"/>
+      <c r="AA25" s="3" t="n"/>
+      <c r="AB25" s="3" t="n"/>
+      <c r="AC25" s="3" t="n"/>
+      <c r="AD25" s="3" t="n"/>
+      <c r="AE25" s="3" t="n"/>
+      <c r="AF25" s="3" t="n"/>
+      <c r="AG25" s="3" t="n"/>
+      <c r="AH25" s="3" t="n"/>
+      <c r="AI25" s="3" t="n"/>
+      <c r="AJ25" s="3" t="n"/>
+      <c r="AK25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n"/>
@@ -5901,6 +12984,18 @@
       <c r="W26" s="8" t="n"/>
       <c r="X26" s="8" t="n"/>
       <c r="Y26" s="8" t="n"/>
+      <c r="Z26" s="8" t="n"/>
+      <c r="AA26" s="8" t="n"/>
+      <c r="AB26" s="8" t="n"/>
+      <c r="AC26" s="8" t="n"/>
+      <c r="AD26" s="8" t="n"/>
+      <c r="AE26" s="8" t="n"/>
+      <c r="AF26" s="8" t="n"/>
+      <c r="AG26" s="8" t="n"/>
+      <c r="AH26" s="8" t="n"/>
+      <c r="AI26" s="8" t="n"/>
+      <c r="AJ26" s="8" t="n"/>
+      <c r="AK26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -5928,6 +13023,18 @@
       <c r="W27" s="3" t="n"/>
       <c r="X27" s="3" t="n"/>
       <c r="Y27" s="3" t="n"/>
+      <c r="Z27" s="3" t="n"/>
+      <c r="AA27" s="3" t="n"/>
+      <c r="AB27" s="3" t="n"/>
+      <c r="AC27" s="3" t="n"/>
+      <c r="AD27" s="3" t="n"/>
+      <c r="AE27" s="3" t="n"/>
+      <c r="AF27" s="3" t="n"/>
+      <c r="AG27" s="3" t="n"/>
+      <c r="AH27" s="3" t="n"/>
+      <c r="AI27" s="3" t="n"/>
+      <c r="AJ27" s="3" t="n"/>
+      <c r="AK27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
@@ -5955,6 +13062,18 @@
       <c r="W28" s="8" t="n"/>
       <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
+      <c r="Z28" s="8" t="n"/>
+      <c r="AA28" s="8" t="n"/>
+      <c r="AB28" s="8" t="n"/>
+      <c r="AC28" s="8" t="n"/>
+      <c r="AD28" s="8" t="n"/>
+      <c r="AE28" s="8" t="n"/>
+      <c r="AF28" s="8" t="n"/>
+      <c r="AG28" s="8" t="n"/>
+      <c r="AH28" s="8" t="n"/>
+      <c r="AI28" s="8" t="n"/>
+      <c r="AJ28" s="8" t="n"/>
+      <c r="AK28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -5982,6 +13101,18 @@
       <c r="W29" s="3" t="n"/>
       <c r="X29" s="3" t="n"/>
       <c r="Y29" s="3" t="n"/>
+      <c r="Z29" s="3" t="n"/>
+      <c r="AA29" s="3" t="n"/>
+      <c r="AB29" s="3" t="n"/>
+      <c r="AC29" s="3" t="n"/>
+      <c r="AD29" s="3" t="n"/>
+      <c r="AE29" s="3" t="n"/>
+      <c r="AF29" s="3" t="n"/>
+      <c r="AG29" s="3" t="n"/>
+      <c r="AH29" s="3" t="n"/>
+      <c r="AI29" s="3" t="n"/>
+      <c r="AJ29" s="3" t="n"/>
+      <c r="AK29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
@@ -6009,6 +13140,18 @@
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
       <c r="Y30" s="8" t="n"/>
+      <c r="Z30" s="8" t="n"/>
+      <c r="AA30" s="8" t="n"/>
+      <c r="AB30" s="8" t="n"/>
+      <c r="AC30" s="8" t="n"/>
+      <c r="AD30" s="8" t="n"/>
+      <c r="AE30" s="8" t="n"/>
+      <c r="AF30" s="8" t="n"/>
+      <c r="AG30" s="8" t="n"/>
+      <c r="AH30" s="8" t="n"/>
+      <c r="AI30" s="8" t="n"/>
+      <c r="AJ30" s="8" t="n"/>
+      <c r="AK30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -6036,6 +13179,18 @@
       <c r="W31" s="3" t="n"/>
       <c r="X31" s="3" t="n"/>
       <c r="Y31" s="3" t="n"/>
+      <c r="Z31" s="3" t="n"/>
+      <c r="AA31" s="3" t="n"/>
+      <c r="AB31" s="3" t="n"/>
+      <c r="AC31" s="3" t="n"/>
+      <c r="AD31" s="3" t="n"/>
+      <c r="AE31" s="3" t="n"/>
+      <c r="AF31" s="3" t="n"/>
+      <c r="AG31" s="3" t="n"/>
+      <c r="AH31" s="3" t="n"/>
+      <c r="AI31" s="3" t="n"/>
+      <c r="AJ31" s="3" t="n"/>
+      <c r="AK31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
@@ -6063,6 +13218,18 @@
       <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="8" t="n"/>
+      <c r="Z32" s="8" t="n"/>
+      <c r="AA32" s="8" t="n"/>
+      <c r="AB32" s="8" t="n"/>
+      <c r="AC32" s="8" t="n"/>
+      <c r="AD32" s="8" t="n"/>
+      <c r="AE32" s="8" t="n"/>
+      <c r="AF32" s="8" t="n"/>
+      <c r="AG32" s="8" t="n"/>
+      <c r="AH32" s="8" t="n"/>
+      <c r="AI32" s="8" t="n"/>
+      <c r="AJ32" s="8" t="n"/>
+      <c r="AK32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -6090,6 +13257,18 @@
       <c r="W33" s="3" t="n"/>
       <c r="X33" s="3" t="n"/>
       <c r="Y33" s="3" t="n"/>
+      <c r="Z33" s="3" t="n"/>
+      <c r="AA33" s="3" t="n"/>
+      <c r="AB33" s="3" t="n"/>
+      <c r="AC33" s="3" t="n"/>
+      <c r="AD33" s="3" t="n"/>
+      <c r="AE33" s="3" t="n"/>
+      <c r="AF33" s="3" t="n"/>
+      <c r="AG33" s="3" t="n"/>
+      <c r="AH33" s="3" t="n"/>
+      <c r="AI33" s="3" t="n"/>
+      <c r="AJ33" s="3" t="n"/>
+      <c r="AK33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
@@ -6117,6 +13296,18 @@
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
       <c r="Y34" s="8" t="n"/>
+      <c r="Z34" s="8" t="n"/>
+      <c r="AA34" s="8" t="n"/>
+      <c r="AB34" s="8" t="n"/>
+      <c r="AC34" s="8" t="n"/>
+      <c r="AD34" s="8" t="n"/>
+      <c r="AE34" s="8" t="n"/>
+      <c r="AF34" s="8" t="n"/>
+      <c r="AG34" s="8" t="n"/>
+      <c r="AH34" s="8" t="n"/>
+      <c r="AI34" s="8" t="n"/>
+      <c r="AJ34" s="8" t="n"/>
+      <c r="AK34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -6144,6 +13335,18 @@
       <c r="W35" s="3" t="n"/>
       <c r="X35" s="3" t="n"/>
       <c r="Y35" s="3" t="n"/>
+      <c r="Z35" s="3" t="n"/>
+      <c r="AA35" s="3" t="n"/>
+      <c r="AB35" s="3" t="n"/>
+      <c r="AC35" s="3" t="n"/>
+      <c r="AD35" s="3" t="n"/>
+      <c r="AE35" s="3" t="n"/>
+      <c r="AF35" s="3" t="n"/>
+      <c r="AG35" s="3" t="n"/>
+      <c r="AH35" s="3" t="n"/>
+      <c r="AI35" s="3" t="n"/>
+      <c r="AJ35" s="3" t="n"/>
+      <c r="AK35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
@@ -6171,6 +13374,18 @@
       <c r="W36" s="8" t="n"/>
       <c r="X36" s="8" t="n"/>
       <c r="Y36" s="8" t="n"/>
+      <c r="Z36" s="8" t="n"/>
+      <c r="AA36" s="8" t="n"/>
+      <c r="AB36" s="8" t="n"/>
+      <c r="AC36" s="8" t="n"/>
+      <c r="AD36" s="8" t="n"/>
+      <c r="AE36" s="8" t="n"/>
+      <c r="AF36" s="8" t="n"/>
+      <c r="AG36" s="8" t="n"/>
+      <c r="AH36" s="8" t="n"/>
+      <c r="AI36" s="8" t="n"/>
+      <c r="AJ36" s="8" t="n"/>
+      <c r="AK36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -6198,6 +13413,18 @@
       <c r="W37" s="3" t="n"/>
       <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="n"/>
+      <c r="Z37" s="3" t="n"/>
+      <c r="AA37" s="3" t="n"/>
+      <c r="AB37" s="3" t="n"/>
+      <c r="AC37" s="3" t="n"/>
+      <c r="AD37" s="3" t="n"/>
+      <c r="AE37" s="3" t="n"/>
+      <c r="AF37" s="3" t="n"/>
+      <c r="AG37" s="3" t="n"/>
+      <c r="AH37" s="3" t="n"/>
+      <c r="AI37" s="3" t="n"/>
+      <c r="AJ37" s="3" t="n"/>
+      <c r="AK37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
@@ -6225,6 +13452,18 @@
       <c r="W38" s="8" t="n"/>
       <c r="X38" s="8" t="n"/>
       <c r="Y38" s="8" t="n"/>
+      <c r="Z38" s="8" t="n"/>
+      <c r="AA38" s="8" t="n"/>
+      <c r="AB38" s="8" t="n"/>
+      <c r="AC38" s="8" t="n"/>
+      <c r="AD38" s="8" t="n"/>
+      <c r="AE38" s="8" t="n"/>
+      <c r="AF38" s="8" t="n"/>
+      <c r="AG38" s="8" t="n"/>
+      <c r="AH38" s="8" t="n"/>
+      <c r="AI38" s="8" t="n"/>
+      <c r="AJ38" s="8" t="n"/>
+      <c r="AK38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -6252,6 +13491,18 @@
       <c r="W39" s="3" t="n"/>
       <c r="X39" s="3" t="n"/>
       <c r="Y39" s="3" t="n"/>
+      <c r="Z39" s="3" t="n"/>
+      <c r="AA39" s="3" t="n"/>
+      <c r="AB39" s="3" t="n"/>
+      <c r="AC39" s="3" t="n"/>
+      <c r="AD39" s="3" t="n"/>
+      <c r="AE39" s="3" t="n"/>
+      <c r="AF39" s="3" t="n"/>
+      <c r="AG39" s="3" t="n"/>
+      <c r="AH39" s="3" t="n"/>
+      <c r="AI39" s="3" t="n"/>
+      <c r="AJ39" s="3" t="n"/>
+      <c r="AK39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
@@ -6279,6 +13530,18 @@
       <c r="W40" s="8" t="n"/>
       <c r="X40" s="8" t="n"/>
       <c r="Y40" s="8" t="n"/>
+      <c r="Z40" s="8" t="n"/>
+      <c r="AA40" s="8" t="n"/>
+      <c r="AB40" s="8" t="n"/>
+      <c r="AC40" s="8" t="n"/>
+      <c r="AD40" s="8" t="n"/>
+      <c r="AE40" s="8" t="n"/>
+      <c r="AF40" s="8" t="n"/>
+      <c r="AG40" s="8" t="n"/>
+      <c r="AH40" s="8" t="n"/>
+      <c r="AI40" s="8" t="n"/>
+      <c r="AJ40" s="8" t="n"/>
+      <c r="AK40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -6306,23 +13569,59 @@
       <c r="W41" s="3" t="n"/>
       <c r="X41" s="3" t="n"/>
       <c r="Y41" s="3" t="n"/>
+      <c r="Z41" s="3" t="n"/>
+      <c r="AA41" s="3" t="n"/>
+      <c r="AB41" s="3" t="n"/>
+      <c r="AC41" s="3" t="n"/>
+      <c r="AD41" s="3" t="n"/>
+      <c r="AE41" s="3" t="n"/>
+      <c r="AF41" s="3" t="n"/>
+      <c r="AG41" s="3" t="n"/>
+      <c r="AH41" s="3" t="n"/>
+      <c r="AI41" s="3" t="n"/>
+      <c r="AJ41" s="3" t="n"/>
+      <c r="AK41" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y41"/>
-  <dataValidations count="5">
-    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <autoFilter ref="A1:AK41"/>
+  <dataValidations count="13">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Data_Slice_ID</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Grouping_Strategy_ID</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Transfer_Direction</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Session_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Task_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Modality_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="U2:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=List_Run_Type</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V2:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=List_Affects_Frozen_Pipeline</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=List_Eligible_for_Method_Decision</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Imbalance_Status</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Leakage_Check_Status</formula1>
+    </dataValidation>
+    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=List_Reviewed</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=List_Used_in_Thesis</formula1>
     </dataValidation>
   </dataValidations>
@@ -6333,7 +13632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6932,7 +14231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7345,7 +14644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8143,1508 +15442,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:W12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="84" customWidth="1" min="23" max="23"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Controlled vocabularies (drives dropdown validation)</t>
-        </is>
-      </c>
-      <c r="V1" s="9" t="inlineStr">
-        <is>
-          <t>Term definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Evidential_Role</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>Reporting_Destination</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>Used_in_Thesis</t>
-        </is>
-      </c>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>Freeze_Status</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>Run_Type</t>
-        </is>
-      </c>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>Affects_Frozen_Pipeline</t>
-        </is>
-      </c>
-      <c r="L2" s="10" t="inlineStr">
-        <is>
-          <t>Eligible_for_Method_Decision</t>
-        </is>
-      </c>
-      <c r="M2" s="10" t="inlineStr">
-        <is>
-          <t>Claim_Type</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>Evidence_Status</t>
-        </is>
-      </c>
-      <c r="O2" s="10" t="inlineStr">
-        <is>
-          <t>Writing_Location</t>
-        </is>
-      </c>
-      <c r="P2" s="10" t="inlineStr">
-        <is>
-          <t>Human_Verification_Status</t>
-        </is>
-      </c>
-      <c r="Q2" s="10" t="inlineStr">
-        <is>
-          <t>Ethics_Status</t>
-        </is>
-      </c>
-      <c r="R2" s="10" t="inlineStr">
-        <is>
-          <t>Ethics_Topic</t>
-        </is>
-      </c>
-      <c r="S2" s="10" t="inlineStr">
-        <is>
-          <t>Required_for_Main_Claim</t>
-        </is>
-      </c>
-      <c r="T2" s="10" t="inlineStr">
-        <is>
-          <t>Ready_for_Chapter_4</t>
-        </is>
-      </c>
-      <c r="U2" s="10" t="inlineStr">
-        <is>
-          <t>YesNo</t>
-        </is>
-      </c>
-      <c r="V2" s="10" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="W2" s="10" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Target-definition</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Primary confirmatory</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Stage 1 - Target lock</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Chapter 3 Method choice</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Pilot</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>Method-choice</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>Chapter 3</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>Data governance</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>confirmatory</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>Pre-specified, locked-pipeline evidence analysis supporting main thesis claims.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Split-design</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Primary-supporting robustness</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Stage 2 - Split lock</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Chapter 4 Main results</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>Decision-support</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr">
-        <is>
-          <t>Confirmatory finding</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>Chapter 4</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr">
-        <is>
-          <t>Partially verified</t>
-        </is>
-      </c>
-      <c r="Q4" s="11" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="R4" s="11" t="inlineStr">
-        <is>
-          <t>Bias/fairness</t>
-        </is>
-      </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U4" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V4" s="11" t="inlineStr">
-        <is>
-          <t>decision-support</t>
-        </is>
-      </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t>Method-choice analysis performed before locking confirmatory settings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Model-comparison</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Secondary decision-support</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Stage 3 - Model lock</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Chapter 4 Supporting robustness</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Confirmatory</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>Robustness support</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>Chapter 5</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>Interpretation limits</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>exploratory</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>Hypothesis-generating extension outside confirmatory core.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Preprocessing-feature</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Secondary decision-support / robustness</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Stage 4 - Feature/preprocessing lock</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Chapter 5 Discussion</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>Robustness</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>Exploratory observation</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>Appendix</t>
-        </is>
-      </c>
-      <c r="R6" s="11" t="inlineStr">
-        <is>
-          <t>AI/tool transparency</t>
-        </is>
-      </c>
-      <c r="V6" s="11" t="inlineStr">
-        <is>
-          <t>construct validity</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t>How well labels/features operationalize intended constructs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Robustness</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Exploratory extension</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Stage 5 - Confirmatory analysis</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>On hold</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Appendix</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Exploratory</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>Reproducibility</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>internal validity</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t>Protection against confounds and leakage in design and execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Confirmatory core</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Stage 6 - Robustness analysis</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Dropped</t>
-        </is>
-      </c>
-      <c r="R8" s="11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="V8" s="11" t="inlineStr">
-        <is>
-          <t>statistical conclusion validity</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>Reliability of metric-based inference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>External exploratory</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Stage 7 - Exploratory extension</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>external validity</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t>Extent findings transfer to other data contexts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>leakage</t>
-        </is>
-      </c>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t>Train-test information contamination that inflates apparent performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>domain shift</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t>Distribution shift between train and test domains.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="V12" s="11" t="inlineStr">
-        <is>
-          <t>interpretability stability</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>Consistency of model-behavior explanation signals across folds.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="V1:W1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="3" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="3" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Thesis Experiment Program Dashboard (v2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Program state summary</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>Experiments by category</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>Experiments by evidential role</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Total number of experiments</t>
-        </is>
-      </c>
-      <c r="B4" s="11">
-        <f>COUNTA(Master_Experiments!$A$2:$A$500)</f>
-        <v/>
-      </c>
-      <c r="D4" s="4">
-        <f>Dictionary_Validation!A3</f>
-        <v/>
-      </c>
-      <c r="E4" s="4">
-        <f>COUNTIF(Master_Experiments!$C:$C,D4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="14">
-        <f>Dictionary_Validation!B3</f>
-        <v/>
-      </c>
-      <c r="H4" s="4">
-        <f>COUNTIF(Master_Experiments!$D:$D,G4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Completed experiments</t>
-        </is>
-      </c>
-      <c r="B5" s="4">
-        <f>COUNTIF(Master_Experiments!$AA$2:$AA$500,"Completed")</f>
-        <v/>
-      </c>
-      <c r="D5" s="4">
-        <f>Dictionary_Validation!A4</f>
-        <v/>
-      </c>
-      <c r="E5" s="4">
-        <f>COUNTIF(Master_Experiments!$C:$C,D5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="14">
-        <f>Dictionary_Validation!B4</f>
-        <v/>
-      </c>
-      <c r="H5" s="4">
-        <f>COUNTIF(Master_Experiments!$D:$D,G5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Critical experiments completed</t>
-        </is>
-      </c>
-      <c r="B6" s="11">
-        <f>COUNTIFS(Master_Experiments!$F$2:$F$500,"Critical",Master_Experiments!$AA$2:$AA$500,"Completed")</f>
-        <v/>
-      </c>
-      <c r="D6" s="4">
-        <f>Dictionary_Validation!A5</f>
-        <v/>
-      </c>
-      <c r="E6" s="4">
-        <f>COUNTIF(Master_Experiments!$C:$C,D6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="14">
-        <f>Dictionary_Validation!B5</f>
-        <v/>
-      </c>
-      <c r="H6" s="4">
-        <f>COUNTIF(Master_Experiments!$D:$D,G6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Open decisions</t>
-        </is>
-      </c>
-      <c r="B7" s="4">
-        <f>COUNTIF(Decision_Log!$M$2:$M$500,"Open")</f>
-        <v/>
-      </c>
-      <c r="D7" s="4">
-        <f>Dictionary_Validation!A6</f>
-        <v/>
-      </c>
-      <c r="E7" s="4">
-        <f>COUNTIF(Master_Experiments!$C:$C,D7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="14">
-        <f>Dictionary_Validation!B6</f>
-        <v/>
-      </c>
-      <c r="H7" s="4">
-        <f>COUNTIF(Master_Experiments!$D:$D,G7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Locked decisions</t>
-        </is>
-      </c>
-      <c r="B8" s="11">
-        <f>COUNTIF(Decision_Log!$M$2:$M$500,"Locked")</f>
-        <v/>
-      </c>
-      <c r="D8" s="4">
-        <f>Dictionary_Validation!A7</f>
-        <v/>
-      </c>
-      <c r="E8" s="4">
-        <f>COUNTIF(Master_Experiments!$C:$C,D8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="14">
-        <f>Dictionary_Validation!B7</f>
-        <v/>
-      </c>
-      <c r="H8" s="4">
-        <f>COUNTIF(Master_Experiments!$D:$D,G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Target locked?</t>
-        </is>
-      </c>
-      <c r="B9" s="4">
-        <f>IF(COUNTIFS(Decision_Log!$A:$A,"D01",Decision_Log!$M:$M,"Locked")&gt;0,"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="D9" s="4">
-        <f>Dictionary_Validation!A8</f>
-        <v/>
-      </c>
-      <c r="E9" s="4">
-        <f>COUNTIF(Master_Experiments!$C:$C,D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Split locked?</t>
-        </is>
-      </c>
-      <c r="B10" s="11">
-        <f>IF(COUNTIFS(Decision_Log!$A:$A,"D02",Decision_Log!$M:$M,"Locked")&gt;0,"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="D10" s="4">
-        <f>Dictionary_Validation!A9</f>
-        <v/>
-      </c>
-      <c r="E10" s="4">
-        <f>COUNTIF(Master_Experiments!$C:$C,D10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Model locked?</t>
-        </is>
-      </c>
-      <c r="B11" s="4">
-        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D03",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D04",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D05",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Feature/preprocessing locked?</t>
-        </is>
-      </c>
-      <c r="B12" s="11">
-        <f>IF(AND(COUNTIFS(Decision_Log!$A:$A,"D06",Decision_Log!$M:$M,"Locked")&gt;0,COUNTIFS(Decision_Log!$A:$A,"D07",Decision_Log!$M:$M,"Locked")&gt;0),"YES","NO")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Confirmatory eligibility achieved?</t>
-        </is>
-      </c>
-      <c r="B13" s="4">
-        <f>IF(COUNTIFS(Confirmatory_Set!$J:$J,"YES")=COUNTIFS(Confirmatory_Set!$A:$A,"&lt;&gt;"),"YES","NO")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Confirmatory ready for Chapter 4?</t>
-        </is>
-      </c>
-      <c r="B14" s="11">
-        <f>IF(AND(B13="YES",COUNTIFS(Confirmatory_Set!$H:$H,"YES",Confirmatory_Set!$G:$G,"YES",Confirmatory_Set!$I:$I,"YES")=COUNTIFS(Confirmatory_Set!$H:$H,"YES")),"YES","NO")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Experiments mapped to Chapter 4 main results</t>
-        </is>
-      </c>
-      <c r="B15" s="4">
-        <f>COUNTIFS(Thesis_Map!$B$2:$B$500,"Chapter 4",Thesis_Map!$E$2:$E$500,"Main")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Experiments mapped only to Appendix</t>
-        </is>
-      </c>
-      <c r="B16" s="11">
-        <f>COUNTIF(Thesis_Map!$B$2:$B$500,"Appendix")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Claims with Evidence_Status = supported</t>
-        </is>
-      </c>
-      <c r="B17" s="4">
-        <f>COUNTIF(Claim_Ledger!$E$2:$E$500,"supported")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Claims with Evidence_Status = partial</t>
-        </is>
-      </c>
-      <c r="B18" s="11">
-        <f>COUNTIF(Claim_Ledger!$E$2:$E$500,"partial")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Claims with Evidence_Status = open</t>
-        </is>
-      </c>
-      <c r="B19" s="4">
-        <f>COUNTIF(Claim_Ledger!$E$2:$E$500,"open")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>AI log entries</t>
-        </is>
-      </c>
-      <c r="B20" s="11">
-        <f>COUNTA(AI_Usage_Log!$A$2:$A$500)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Open ethics/governance notes</t>
-        </is>
-      </c>
-      <c r="B21" s="4">
-        <f>COUNTIF(Ethics_Governance_Notes!$G$2:$G$500,"Open")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B9:B14">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B9="YES"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="4">
-      <formula>B9="NO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Claim_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Claim_Text</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Claim_Type</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>Supported_By_Experiments</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Evidence_Status</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Writing_Location</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Interpretation_Limit</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Primary within-person held-out-session decoding demonstrates meaningful generalization under locked pipeline.</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Confirmatory finding</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>E16,E12,E13,E14</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>Chapter 4</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>Interpret only within claim-matched split and current dataset scope.</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Frozen directional cross-person transfer indicates cross-case portability under domain shift.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Confirmatory finding</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>E17,E12,E13</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Chapter 4</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Not a population-level generalization claim.</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Method lock decisions reduce leakage risk and interpretation drift.</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Method-choice</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>E01,E04,E05,E06,E09,E11</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Chapter 3</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Governance claim; not a performance claim.</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H31"/>
-  <dataValidations count="3">
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Claim_Type</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Evidence_Status</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Writing_Location</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/thesis_experiment_program.xlsx
+++ b/thesis_experiment_program.xlsx
@@ -10,26 +10,29 @@
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Master_Experiments" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Experiment_Definitions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Artifact_Registry" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Fixed_Configs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Objectives" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Machine_Status" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Trial_Results" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Data_Selection_Design" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Grouping_Strategy_Map" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Data_Profile" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Run_Log" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Decision_Log" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Confirmatory_Set" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Thesis_Map" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Dictionary_Validation" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Dashboard" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Claim_Ledger" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="AI_Usage_Log" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Ethics_Governance_Notes" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Search_Spaces" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Artifact_Registry" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Fixed_Configs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Objectives" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Machine_Status" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Trial_Results" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Summary_Outputs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Data_Selection_Design" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Grouping_Strategy_Map" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Data_Profile" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Run_Log" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Decision_Log" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Confirmatory_Set" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Thesis_Map" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Dictionary_Validation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Dashboard" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Claim_Ledger" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="AI_Usage_Log" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Ethics_Governance_Notes" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="List_Experiment_ID">'Master_Experiments'!$A$2:INDEX('Master_Experiments'!$A:$A,MATCH("zzz",'Master_Experiments'!$A:$A))</definedName>
+    <definedName name="List_Search_Space_ID">'Search_Spaces'!$A$3:INDEX('Search_Spaces'!$A:$A,MATCH("zzz",'Search_Spaces'!$A:$A))</definedName>
     <definedName name="List_Data_Slice_ID">'Data_Selection_Design'!$A$2:INDEX('Data_Selection_Design'!$A:$A,MATCH("zzz",'Data_Selection_Design'!$A:$A))</definedName>
     <definedName name="List_Grouping_Strategy_ID">'Grouping_Strategy_Map'!$A$2:INDEX('Grouping_Strategy_Map'!$A:$A,MATCH("zzz",'Grouping_Strategy_Map'!$A:$A))</definedName>
     <definedName name="List_Category">'Dictionary_Validation'!$A$3:$A$9</definedName>
@@ -70,22 +73,26 @@
     <definedName name="List_Target_Type">'Dictionary_Validation'!$AJ$3:$AJ$6</definedName>
     <definedName name="List_Execution_Section">'Dictionary_Validation'!$AK$3:$AK$9</definedName>
     <definedName name="List_Reuse_Policy">'Dictionary_Validation'!$AL$3:$AL$5</definedName>
+    <definedName name="List_Search_Optimization_Mode">'Dictionary_Validation'!$AM$3:$AM$4</definedName>
+    <definedName name="List_Search_Parameter_Scope">'Dictionary_Validation'!$AN$3:$AN$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master_Experiments'!$A$1:$AF$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Experiment_Definitions'!$A$1:$N$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Artifact_Registry'!$A$2:$J$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fixed_Configs'!$A$2:$G$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Objectives'!$A$2:$H$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Machine_Status'!$A$2:$H$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Trial_Results'!$A$2:$J$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Data_Selection_Design'!$A$1:$R$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Grouping_Strategy_Map'!$A$1:$O$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Run_Log'!$A$1:$AK$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Decision_Log'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Confirmatory_Set'!$A$1:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Thesis_Map'!$A$1:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Claim_Ledger'!$A$1:$H$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'AI_Usage_Log'!$A$1:$J$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Ethics_Governance_Notes'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Experiment_Definitions'!$A$1:$O$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Search_Spaces'!$A$2:$I$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Artifact_Registry'!$A$2:$J$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fixed_Configs'!$A$2:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Objectives'!$A$2:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Machine_Status'!$A$2:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Trial_Results'!$A$2:$J$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Summary_Outputs'!$A$2:$N$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Data_Selection_Design'!$A$1:$R$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Grouping_Strategy_Map'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Run_Log'!$A$1:$AK$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Decision_Log'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Confirmatory_Set'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Thesis_Map'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Claim_Ledger'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'AI_Usage_Log'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Ethics_Governance_Notes'!$A$1:$H$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -347,9 +354,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentDefinitionsTable" displayName="ExperimentDefinitionsTable" ref="A1:N81" headerRowCount="1">
-  <autoFilter ref="A1:N81"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentDefinitionsTable" displayName="ExperimentDefinitionsTable" ref="A1:O81" headerRowCount="1">
+  <autoFilter ref="A1:O81"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="experiment_id"/>
     <tableColumn id="2" name="enabled"/>
     <tableColumn id="3" name="start_section"/>
@@ -364,13 +371,52 @@
     <tableColumn id="12" name="filter_task"/>
     <tableColumn id="13" name="filter_modality"/>
     <tableColumn id="14" name="reuse_policy"/>
+    <tableColumn id="15" name="search_space_id"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="ProfileSessionTable" displayName="ProfileSessionTable" ref="A24:E34" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="GroupingStrategyTable" displayName="GroupingStrategyTable" ref="A1:O41" headerRowCount="1">
+  <autoFilter ref="A1:O41"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="Grouping_Strategy_ID"/>
+    <tableColumn id="2" name="Strategy_Name"/>
+    <tableColumn id="3" name="Split_Family"/>
+    <tableColumn id="4" name="Train_Group_Unit"/>
+    <tableColumn id="5" name="Test_Group_Unit"/>
+    <tableColumn id="6" name="Grouping_Level"/>
+    <tableColumn id="7" name="Train_Rule"/>
+    <tableColumn id="8" name="Test_Rule"/>
+    <tableColumn id="9" name="Leakage_Safeguard"/>
+    <tableColumn id="10" name="Suitable_For"/>
+    <tableColumn id="11" name="Not_Suitable_For"/>
+    <tableColumn id="12" name="Interpretation_Boundary"/>
+    <tableColumn id="13" name="Typical_Experiments"/>
+    <tableColumn id="14" name="Thesis_Section"/>
+    <tableColumn id="15" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="ProfileSubjectTable" displayName="ProfileSubjectTable" ref="A12:E20" headerRowCount="1">
+  <autoFilter ref="A12:E20"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Subject_ID"/>
+    <tableColumn id="2" name="Count"/>
+    <tableColumn id="3" name="Share_of_Block"/>
+    <tableColumn id="4" name="Flag"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="ProfileSessionTable" displayName="ProfileSessionTable" ref="A24:E34" headerRowCount="1">
   <autoFilter ref="A24:E34"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Session_ID"/>
@@ -383,8 +429,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="ProfileTaskTable" displayName="ProfileTaskTable" ref="A38:E45" headerRowCount="1">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="ProfileTaskTable" displayName="ProfileTaskTable" ref="A38:E45" headerRowCount="1">
   <autoFilter ref="A38:E45"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Task_ID"/>
@@ -397,8 +443,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="ProfileModalityTable" displayName="ProfileModalityTable" ref="A49:E55" headerRowCount="1">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="ProfileModalityTable" displayName="ProfileModalityTable" ref="A49:E55" headerRowCount="1">
   <autoFilter ref="A49:E55"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Modality_ID"/>
@@ -411,8 +457,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="ProfileTargetClassTable" displayName="ProfileTargetClassTable" ref="A59:E65" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="ProfileTargetClassTable" displayName="ProfileTargetClassTable" ref="A59:E65" headerRowCount="1">
   <autoFilter ref="A59:E65"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Target_or_Class_ID"/>
@@ -425,8 +471,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="ProfileDataSliceTable" displayName="ProfileDataSliceTable" ref="A70:E80" headerRowCount="1">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="ProfileDataSliceTable" displayName="ProfileDataSliceTable" ref="A70:E80" headerRowCount="1">
   <autoFilter ref="A70:E80"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Data_Slice_ID"/>
@@ -439,8 +485,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="RunLogTable" displayName="RunLogTable" ref="A1:AK41" headerRowCount="1">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="RunLogTable" displayName="RunLogTable" ref="A1:AK41" headerRowCount="1">
   <autoFilter ref="A1:AK41"/>
   <tableColumns count="37">
     <tableColumn id="1" name="Run_ID"/>
@@ -485,8 +531,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:N9" headerRowCount="1">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="DecisionLogTable" displayName="DecisionLogTable" ref="A1:N9" headerRowCount="1">
   <autoFilter ref="A1:N9"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Decision_ID"/>
@@ -508,8 +554,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="ConfirmatoryTable" displayName="ConfirmatoryTable" ref="A1:L6" headerRowCount="1">
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ConfirmatoryTable" displayName="ConfirmatoryTable" ref="A1:L6" headerRowCount="1">
   <autoFilter ref="A1:L6"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Experiment_ID"/>
@@ -529,8 +575,26 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="ThesisMapTable" displayName="ThesisMapTable" ref="A1:H20" headerRowCount="1">
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SearchSpacesTable" displayName="SearchSpacesTable" ref="A2:I61" headerRowCount="1">
+  <autoFilter ref="A2:I61"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="search_space_id"/>
+    <tableColumn id="2" name="enabled"/>
+    <tableColumn id="3" name="optimization_mode"/>
+    <tableColumn id="4" name="parameter_name"/>
+    <tableColumn id="5" name="parameter_values"/>
+    <tableColumn id="6" name="parameter_scope"/>
+    <tableColumn id="7" name="objective_metric"/>
+    <tableColumn id="8" name="max_trials"/>
+    <tableColumn id="9" name="notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="ThesisMapTable" displayName="ThesisMapTable" ref="A1:H20" headerRowCount="1">
   <autoFilter ref="A1:H20"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Experiment_ID"/>
@@ -546,8 +610,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ClaimLedgerTable" displayName="ClaimLedgerTable" ref="A1:H31" headerRowCount="1">
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="ClaimLedgerTable" displayName="ClaimLedgerTable" ref="A1:H31" headerRowCount="1">
   <autoFilter ref="A1:H31"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Claim_ID"/>
@@ -563,8 +627,44 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WorkbookArtifactRegistryTable" displayName="WorkbookArtifactRegistryTable" ref="A2:J61" headerRowCount="1">
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="AIUsageTable" displayName="AIUsageTable" ref="A1:J41" headerRowCount="1">
+  <autoFilter ref="A1:J41"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Entry_ID"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="Task"/>
+    <tableColumn id="4" name="Tool"/>
+    <tableColumn id="5" name="Input_Summary"/>
+    <tableColumn id="6" name="Output_Summary"/>
+    <tableColumn id="7" name="What_Was_Adopted"/>
+    <tableColumn id="8" name="Human_Verification_Status"/>
+    <tableColumn id="9" name="Thesis_Use"/>
+    <tableColumn id="10" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="EthicsTable" displayName="EthicsTable" ref="A1:H31" headerRowCount="1">
+  <autoFilter ref="A1:H31"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Note_ID"/>
+    <tableColumn id="2" name="Experiment_ID_or_Decision_ID"/>
+    <tableColumn id="3" name="Topic"/>
+    <tableColumn id="4" name="Risk_or_Concern"/>
+    <tableColumn id="5" name="Mitigation_or_Response"/>
+    <tableColumn id="6" name="Thesis_Section"/>
+    <tableColumn id="7" name="Status"/>
+    <tableColumn id="8" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WorkbookArtifactRegistryTable" displayName="WorkbookArtifactRegistryTable" ref="A2:J61" headerRowCount="1">
   <autoFilter ref="A2:J61"/>
   <tableColumns count="10">
     <tableColumn id="1" name="artifact_id"/>
@@ -582,44 +682,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="AIUsageTable" displayName="AIUsageTable" ref="A1:J41" headerRowCount="1">
-  <autoFilter ref="A1:J41"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="Entry_ID"/>
-    <tableColumn id="2" name="Date"/>
-    <tableColumn id="3" name="Task"/>
-    <tableColumn id="4" name="Tool"/>
-    <tableColumn id="5" name="Input_Summary"/>
-    <tableColumn id="6" name="Output_Summary"/>
-    <tableColumn id="7" name="What_Was_Adopted"/>
-    <tableColumn id="8" name="Human_Verification_Status"/>
-    <tableColumn id="9" name="Thesis_Use"/>
-    <tableColumn id="10" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="EthicsTable" displayName="EthicsTable" ref="A1:H31" headerRowCount="1">
-  <autoFilter ref="A1:H31"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Note_ID"/>
-    <tableColumn id="2" name="Experiment_ID_or_Decision_ID"/>
-    <tableColumn id="3" name="Topic"/>
-    <tableColumn id="4" name="Risk_or_Concern"/>
-    <tableColumn id="5" name="Mitigation_or_Response"/>
-    <tableColumn id="6" name="Thesis_Section"/>
-    <tableColumn id="7" name="Status"/>
-    <tableColumn id="8" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FixedConfigsTable" displayName="FixedConfigsTable" ref="A2:G61" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FixedConfigsTable" displayName="FixedConfigsTable" ref="A2:G61" headerRowCount="1">
   <autoFilter ref="A2:G61"/>
   <tableColumns count="7">
     <tableColumn id="1" name="config_key"/>
@@ -634,8 +698,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ObjectivesTable" displayName="ObjectivesTable" ref="A2:H61" headerRowCount="1">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ObjectivesTable" displayName="ObjectivesTable" ref="A2:H61" headerRowCount="1">
   <autoFilter ref="A2:H61"/>
   <tableColumns count="8">
     <tableColumn id="1" name="objective_id"/>
@@ -651,8 +715,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="MachineStatusTable" displayName="MachineStatusTable" ref="A2:H61" headerRowCount="1">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="MachineStatusTable" displayName="MachineStatusTable" ref="A2:H61" headerRowCount="1">
   <autoFilter ref="A2:H61"/>
   <tableColumns count="8">
     <tableColumn id="1" name="machine_id"/>
@@ -668,8 +732,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TrialResultsTable" displayName="TrialResultsTable" ref="A2:J61" headerRowCount="1">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TrialResultsTable" displayName="TrialResultsTable" ref="A2:J61" headerRowCount="1">
   <autoFilter ref="A2:J61"/>
   <tableColumns count="10">
     <tableColumn id="1" name="trial_id"/>
@@ -687,8 +751,31 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="DataSelectionTable" displayName="DataSelectionTable" ref="A1:R41" headerRowCount="1">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="SummaryOutputsTable" displayName="SummaryOutputsTable" ref="A2:N61" headerRowCount="1">
+  <autoFilter ref="A2:N61"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="summary_type"/>
+    <tableColumn id="2" name="summary_key"/>
+    <tableColumn id="3" name="primary_metric_name"/>
+    <tableColumn id="4" name="primary_metric_value"/>
+    <tableColumn id="5" name="run_id"/>
+    <tableColumn id="6" name="experiment_id"/>
+    <tableColumn id="7" name="start_section"/>
+    <tableColumn id="8" name="end_section"/>
+    <tableColumn id="9" name="model"/>
+    <tableColumn id="10" name="cv"/>
+    <tableColumn id="11" name="target"/>
+    <tableColumn id="12" name="xai_method"/>
+    <tableColumn id="13" name="report_path"/>
+    <tableColumn id="14" name="notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="DataSelectionTable" displayName="DataSelectionTable" ref="A1:R41" headerRowCount="1">
   <autoFilter ref="A1:R41"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Data_Slice_ID"/>
@@ -711,44 +798,6 @@
     <tableColumn id="18" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="GroupingStrategyTable" displayName="GroupingStrategyTable" ref="A1:O41" headerRowCount="1">
-  <autoFilter ref="A1:O41"/>
-  <tableColumns count="15">
-    <tableColumn id="1" name="Grouping_Strategy_ID"/>
-    <tableColumn id="2" name="Strategy_Name"/>
-    <tableColumn id="3" name="Split_Family"/>
-    <tableColumn id="4" name="Train_Group_Unit"/>
-    <tableColumn id="5" name="Test_Group_Unit"/>
-    <tableColumn id="6" name="Grouping_Level"/>
-    <tableColumn id="7" name="Train_Rule"/>
-    <tableColumn id="8" name="Test_Rule"/>
-    <tableColumn id="9" name="Leakage_Safeguard"/>
-    <tableColumn id="10" name="Suitable_For"/>
-    <tableColumn id="11" name="Not_Suitable_For"/>
-    <tableColumn id="12" name="Interpretation_Boundary"/>
-    <tableColumn id="13" name="Typical_Experiments"/>
-    <tableColumn id="14" name="Thesis_Section"/>
-    <tableColumn id="15" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="ProfileSubjectTable" displayName="ProfileSubjectTable" ref="A12:E20" headerRowCount="1">
-  <autoFilter ref="A12:E20"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Subject_ID"/>
-    <tableColumn id="2" name="Count"/>
-    <tableColumn id="3" name="Share_of_Block"/>
-    <tableColumn id="4" name="Flag"/>
-    <tableColumn id="5" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1474,6 +1523,2581 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Machine Summary Outputs (Best Runs and Patterns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>summary_type</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>summary_key</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>primary_metric_name</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>primary_metric_value</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>run_id</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>experiment_id</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>start_section</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>end_section</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>cv</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>xai_method</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>report_path</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+      <c r="L42" s="8" t="n"/>
+      <c r="M42" s="8" t="n"/>
+      <c r="N42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n"/>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="8" t="n"/>
+      <c r="M44" s="8" t="n"/>
+      <c r="N44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n"/>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+      <c r="L46" s="8" t="n"/>
+      <c r="M46" s="8" t="n"/>
+      <c r="N46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="n"/>
+      <c r="N47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n"/>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
+      <c r="L49" s="3" t="n"/>
+      <c r="M49" s="3" t="n"/>
+      <c r="N49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="8" t="n"/>
+      <c r="N50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n"/>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="n"/>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
+      <c r="M52" s="8" t="n"/>
+      <c r="N52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n"/>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="n"/>
+      <c r="L53" s="3" t="n"/>
+      <c r="M53" s="3" t="n"/>
+      <c r="N53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="8" t="n"/>
+      <c r="N54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n"/>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="n"/>
+      <c r="L55" s="3" t="n"/>
+      <c r="M55" s="3" t="n"/>
+      <c r="N55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
+      <c r="M56" s="8" t="n"/>
+      <c r="N56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n"/>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
+      <c r="L57" s="3" t="n"/>
+      <c r="M57" s="3" t="n"/>
+      <c r="N57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="8" t="n"/>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
+      <c r="L58" s="8" t="n"/>
+      <c r="M58" s="8" t="n"/>
+      <c r="N58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n"/>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
+      <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
+      <c r="L59" s="3" t="n"/>
+      <c r="M59" s="3" t="n"/>
+      <c r="N59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
+      <c r="L60" s="8" t="n"/>
+      <c r="M60" s="8" t="n"/>
+      <c r="N60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n"/>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
+      <c r="L61" s="3" t="n"/>
+      <c r="M61" s="3" t="n"/>
+      <c r="N61" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:N61"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Data_Slice_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Slice_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Subject_Scope</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Session_Scope</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Time_Window</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Task_Scope</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Modality_Scope</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Target_Type</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Label_Set</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Inclusion_Rule</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Exclusion_Rule</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>Class_Balance_Policy</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Minimum_Samples_Rule</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Leakage_Risk</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Valid_Use_Case</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Thesis_Use</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>DS01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>All subjects, all sessions, pooled task, pooled modality, coarse_affect</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Global baseline for target/split/model method-choice comparisons.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>All QC-passed repeated-session beta maps with valid labels.</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>Drop failed-preprocessing rows and missing targets.</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>Prefer &gt;=20 per class before claim-level interpretation.</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P2" s="8" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>DS02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Subject-specific pooled-task pooled-modality</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Primary within-person held-out-session claim support.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>single_subject</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>held_out_session</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>One subject at a time with all eligible sessions.</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>No cross-subject pooling inside fold-level fit.</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>weighted_only</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Per-class floor checked per subject.</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>confirmatory_within_person</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>main_confirmatory</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Matches held-out-session inference boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>DS03</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Task-specific pooled-modality</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Task pooling vs task-specific method-choice and diagnostics.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>task_specific_other</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect by task</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Restrict each run to one task family.</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Exclude off-task records for that run.</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>Minimum counts checked per task-specific slice.</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>DS04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Modality-specific pooled-task</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Modality pooling vs modality-specific method-choice checks.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>audio_only</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>One modality family per run (audio/video/audiovisual variants).</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Exclude other modalities in each modality-specific run.</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Check sample sufficiency per modality variant.</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>method_choice</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Seed modality is audio_only; clone row for other modalities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>DS05</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Subject-specific task x modality subset</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Fine-grained diagnostic sensitivity slices.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>single_subject</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>task_specific_other</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>audiovisual_only</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Single subject + selected task + selected modality combination.</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Exclude all records outside the chosen intersection.</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>min_count_threshold</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>Hard floor required before reporting.</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>diagnostic_only</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>discussion_limitations</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DS06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Early sessions only</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Temporal drift checks and early-to-late transfer design.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>early_only</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>early_window</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Use sessions pre-registered as early window.</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Exclude late-window sessions.</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Check class floor by temporal window.</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>robustness_support</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>supporting_robustness</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>DS07</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Late sessions only</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Temporal drift checks and early-to-late transfer design.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>late_only</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>late_window</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Use sessions pre-registered as late window.</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Exclude early-window sessions.</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>as_is</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>Check class floor by temporal window.</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>robustness_support</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>supporting_robustness</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>DS08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Balanced subset only</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Imbalance-aware sensitivity diagnostics.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>all_subjects</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>all_sessions</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>full_study_window</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_tasks</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>pooled_all_modalities</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>coarse_affect</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Only include rows passing balancing policy.</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Exclude classes below predefined minimum count floor.</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>balanced_subset</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Set explicit class floor in analysis config.</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>robustness_support</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>supporting_robustness</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>Do not replace confirmatory as-is evidence with this slice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
+      <c r="R12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="8" t="n"/>
+      <c r="P18" s="8" t="n"/>
+      <c r="Q18" s="8" t="n"/>
+      <c r="R18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
+      <c r="R19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
+      <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="8" t="n"/>
+      <c r="R22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n"/>
+      <c r="Q25" s="3" t="n"/>
+      <c r="R25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="8" t="n"/>
+      <c r="O26" s="8" t="n"/>
+      <c r="P26" s="8" t="n"/>
+      <c r="Q26" s="8" t="n"/>
+      <c r="R26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="n"/>
+      <c r="P28" s="8" t="n"/>
+      <c r="Q28" s="8" t="n"/>
+      <c r="R28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n"/>
+      <c r="R29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="8" t="n"/>
+      <c r="O30" s="8" t="n"/>
+      <c r="P30" s="8" t="n"/>
+      <c r="Q30" s="8" t="n"/>
+      <c r="R30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="3" t="n"/>
+      <c r="Q31" s="3" t="n"/>
+      <c r="R31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="8" t="n"/>
+      <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="8" t="n"/>
+      <c r="R32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
+      <c r="R33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
+      <c r="O34" s="8" t="n"/>
+      <c r="P34" s="8" t="n"/>
+      <c r="Q34" s="8" t="n"/>
+      <c r="R34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="n"/>
+      <c r="Q35" s="3" t="n"/>
+      <c r="R35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="8" t="n"/>
+      <c r="O36" s="8" t="n"/>
+      <c r="P36" s="8" t="n"/>
+      <c r="Q36" s="8" t="n"/>
+      <c r="R36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="3" t="n"/>
+      <c r="Q37" s="3" t="n"/>
+      <c r="R37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="8" t="n"/>
+      <c r="O38" s="8" t="n"/>
+      <c r="P38" s="8" t="n"/>
+      <c r="Q38" s="8" t="n"/>
+      <c r="R38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
+      <c r="R39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="8" t="n"/>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="8" t="n"/>
+      <c r="R40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="n"/>
+      <c r="Q41" s="3" t="n"/>
+      <c r="R41" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R41"/>
+  <dataValidations count="9">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Subject_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Session_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Task_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Modality_Scope</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Target_Type</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Class_Balance_Policy</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Leakage_Risk_Level</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Use_Case</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Thesis_Use_Tag</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2791,7 +5415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3959,7 +6583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5804,7 +8428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6403,7 +9027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6816,7 +9440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7616,13 +10240,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7663,8 +10287,10 @@
     <col width="22" customWidth="1" min="36" max="36"/>
     <col width="22" customWidth="1" min="37" max="37"/>
     <col width="22" customWidth="1" min="38" max="38"/>
-    <col width="24" customWidth="1" min="39" max="39"/>
-    <col width="84" customWidth="1" min="40" max="40"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="40" max="40"/>
+    <col width="24" customWidth="1" min="41" max="41"/>
+    <col width="84" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7673,7 +10299,7 @@
           <t>Controlled vocabularies (drives dropdown validation)</t>
         </is>
       </c>
-      <c r="AM1" s="14" t="inlineStr">
+      <c r="AO1" s="14" t="inlineStr">
         <is>
           <t>Term definitions</t>
         </is>
@@ -7872,10 +10498,20 @@
       </c>
       <c r="AM2" s="15" t="inlineStr">
         <is>
+          <t>Search_Optimization_Mode</t>
+        </is>
+      </c>
+      <c r="AN2" s="15" t="inlineStr">
+        <is>
+          <t>Search_Parameter_Scope</t>
+        </is>
+      </c>
+      <c r="AO2" s="15" t="inlineStr">
+        <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="AN2" s="15" t="inlineStr">
+      <c r="AP2" s="15" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
@@ -8074,10 +10710,20 @@
       </c>
       <c r="AM3" s="4" t="inlineStr">
         <is>
+          <t>deterministic_grid</t>
+        </is>
+      </c>
+      <c r="AN3" s="4" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
           <t>confirmatory</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <t>Pre-specified, locked-pipeline evidence analysis supporting main thesis claims.</t>
         </is>
@@ -8276,10 +10922,20 @@
       </c>
       <c r="AM4" s="12" t="inlineStr">
         <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AN4" s="12" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="AO4" s="12" t="inlineStr">
+        <is>
           <t>decision-support</t>
         </is>
       </c>
-      <c r="AN4" s="8" t="inlineStr">
+      <c r="AP4" s="8" t="inlineStr">
         <is>
           <t>Method-choice analysis performed before locking confirmatory settings.</t>
         </is>
@@ -8436,12 +11092,17 @@
           <t>disallow</t>
         </is>
       </c>
-      <c r="AM5" s="4" t="inlineStr">
+      <c r="AN5" s="4" t="inlineStr">
+        <is>
+          <t>xai</t>
+        </is>
+      </c>
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>exploratory</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr">
         <is>
           <t>Hypothesis-generating extension outside confirmatory core.</t>
         </is>
@@ -8573,12 +11234,12 @@
           <t>spatial_validation</t>
         </is>
       </c>
-      <c r="AM6" s="12" t="inlineStr">
+      <c r="AO6" s="12" t="inlineStr">
         <is>
           <t>data slice</t>
         </is>
       </c>
-      <c r="AN6" s="8" t="inlineStr">
+      <c r="AP6" s="8" t="inlineStr">
         <is>
           <t>Explicit subset policy over subjects/sessions/tasks/modalities/labels used by runs.</t>
         </is>
@@ -8665,12 +11326,12 @@
           <t>model_fit</t>
         </is>
       </c>
-      <c r="AM7" s="4" t="inlineStr">
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>grouping strategy</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
+      <c r="AP7" s="3" t="inlineStr">
         <is>
           <t>Explicit train/test grouping logic and split family for claim-matched evaluation.</t>
         </is>
@@ -8717,12 +11378,12 @@
           <t>interpretability</t>
         </is>
       </c>
-      <c r="AM8" s="12" t="inlineStr">
+      <c r="AO8" s="12" t="inlineStr">
         <is>
           <t>weak split demo</t>
         </is>
       </c>
-      <c r="AN8" s="8" t="inlineStr">
+      <c r="AP8" s="8" t="inlineStr">
         <is>
           <t>Intentionally weak split used only to demonstrate inflation risk; not confirmatory evidence.</t>
         </is>
@@ -8759,84 +11420,84 @@
           <t>evaluation</t>
         </is>
       </c>
-      <c r="AM9" s="4" t="inlineStr">
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>construct validity</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
+      <c r="AP9" s="3" t="inlineStr">
         <is>
           <t>How well labels/features operationalize intended constructs.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="AM10" s="12" t="inlineStr">
+      <c r="AO10" s="12" t="inlineStr">
         <is>
           <t>internal validity</t>
         </is>
       </c>
-      <c r="AN10" s="8" t="inlineStr">
+      <c r="AP10" s="8" t="inlineStr">
         <is>
           <t>Protection against confounds and leakage in design and execution.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="AM11" s="4" t="inlineStr">
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>statistical conclusion validity</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
+      <c r="AP11" s="3" t="inlineStr">
         <is>
           <t>Reliability of metric-based inference.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="AM12" s="12" t="inlineStr">
+      <c r="AO12" s="12" t="inlineStr">
         <is>
           <t>external validity</t>
         </is>
       </c>
-      <c r="AN12" s="8" t="inlineStr">
+      <c r="AP12" s="8" t="inlineStr">
         <is>
           <t>Extent findings transfer to other data contexts.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="AM13" s="4" t="inlineStr">
+      <c r="AO13" s="4" t="inlineStr">
         <is>
           <t>leakage</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
+      <c r="AP13" s="3" t="inlineStr">
         <is>
           <t>Train-test information contamination that inflates apparent performance.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="AM14" s="12" t="inlineStr">
+      <c r="AO14" s="12" t="inlineStr">
         <is>
           <t>domain shift</t>
         </is>
       </c>
-      <c r="AN14" s="8" t="inlineStr">
+      <c r="AP14" s="8" t="inlineStr">
         <is>
           <t>Distribution shift between train and test domains.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="AM15" s="4" t="inlineStr">
+      <c r="AO15" s="4" t="inlineStr">
         <is>
           <t>interpretability stability</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
+      <c r="AP15" s="3" t="inlineStr">
         <is>
           <t>Consistency of model-behavior explanation signals across folds.</t>
         </is>
@@ -8844,14 +11505,14 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="A1:AN1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9549,1061 +12210,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Claim_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Claim_Text</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Claim_Type</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>Supported_By_Experiments</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Evidence_Status</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Writing_Location</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Interpretation_Limit</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Primary within-person held-out-session decoding demonstrates meaningful generalization under locked pipeline.</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Confirmatory finding</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>E16,E12,E13,E14</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>Chapter 4</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>Interpret only within claim-matched split and current dataset scope.</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Frozen directional cross-person transfer indicates cross-case portability under domain shift.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Confirmatory finding</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>E17,E12,E13</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Chapter 4</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Not a population-level generalization claim.</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Method lock decisions reduce leakage risk and interpretation drift.</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Method-choice</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>E01,E04,E05,E06,E09,E11</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Chapter 3</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Governance claim; not a performance claim.</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H31"/>
-  <dataValidations count="3">
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Claim_Type</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Evidence_Status</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Writing_Location</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Entry_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>Tool</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Input_Summary</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Output_Summary</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>What_Was_Adopted</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Human_Verification_Status</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>Thesis_Use</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>AI001</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>GPT-5.3-Codex</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Workbook package revision and governance alignment</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Not reviewed</t>
-        </is>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="8" t="n"/>
-      <c r="H4" s="8" t="n"/>
-      <c r="I4" s="8" t="n"/>
-      <c r="J4" s="8" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n"/>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="n"/>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-      <c r="J39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J41"/>
-  <dataValidations count="2">
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Human_Verification_Status</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Used_in_Thesis</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -13696,6 +15302,1061 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Claim_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Claim_Text</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Claim_Type</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Supported_By_Experiments</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Evidence_Status</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Writing_Location</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Interpretation_Limit</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Primary within-person held-out-session decoding demonstrates meaningful generalization under locked pipeline.</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Confirmatory finding</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>E16,E12,E13,E14</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 4</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Interpret only within claim-matched split and current dataset scope.</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Frozen directional cross-person transfer indicates cross-case portability under domain shift.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Confirmatory finding</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>E17,E12,E13</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Chapter 4</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Not a population-level generalization claim.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Method lock decisions reduce leakage risk and interpretation drift.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Method-choice</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>E01,E04,E05,E06,E09,E11</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Chapter 3</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Governance claim; not a performance claim.</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H31"/>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Claim_Type</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Evidence_Status</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Writing_Location</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Entry_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Input_Summary</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Output_Summary</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>What_Was_Adopted</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Human_Verification_Status</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Thesis_Use</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>AI001</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>GPT-5.3-Codex</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Workbook package revision and governance alignment</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Not reviewed</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J41"/>
+  <dataValidations count="2">
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Human_Verification_Status</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Used_in_Thesis</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
@@ -14126,7 +16787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14143,6 +16804,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14214,6 +16876,11 @@
       <c r="N1" s="7" t="inlineStr">
         <is>
           <t>reuse_policy</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>search_space_id</t>
         </is>
       </c>
     </row>
@@ -14268,6 +16935,7 @@
           <t>auto</t>
         </is>
       </c>
+      <c r="O2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -14324,6 +16992,7 @@
           <t>auto</t>
         </is>
       </c>
+      <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n"/>
@@ -14340,6 +17009,7 @@
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n"/>
+      <c r="O4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -14356,6 +17026,7 @@
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -14372,6 +17043,7 @@
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n"/>
+      <c r="O6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -14388,6 +17060,7 @@
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
       <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n"/>
@@ -14404,6 +17077,7 @@
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
       <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -14420,6 +17094,7 @@
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
@@ -14436,6 +17111,7 @@
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -14452,6 +17128,7 @@
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
       <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
@@ -14468,6 +17145,7 @@
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
+      <c r="O12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -14484,6 +17162,7 @@
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
@@ -14500,6 +17179,7 @@
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -14516,6 +17196,7 @@
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
       <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
@@ -14532,6 +17213,7 @@
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -14548,6 +17230,7 @@
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
       <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
@@ -14564,6 +17247,7 @@
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n"/>
+      <c r="O18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -14580,6 +17264,7 @@
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -14596,6 +17281,7 @@
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -14612,6 +17298,7 @@
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3" t="n"/>
       <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -14628,6 +17315,7 @@
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -14644,6 +17332,7 @@
       <c r="L23" s="3" t="n"/>
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n"/>
@@ -14660,6 +17349,7 @@
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -14676,6 +17366,7 @@
       <c r="L25" s="3" t="n"/>
       <c r="M25" s="3" t="n"/>
       <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n"/>
@@ -14692,6 +17383,7 @@
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
+      <c r="O26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -14708,6 +17400,7 @@
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
       <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
@@ -14724,6 +17417,7 @@
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
       <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -14740,6 +17434,7 @@
       <c r="L29" s="3" t="n"/>
       <c r="M29" s="3" t="n"/>
       <c r="N29" s="3" t="n"/>
+      <c r="O29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
@@ -14756,6 +17451,7 @@
       <c r="L30" s="8" t="n"/>
       <c r="M30" s="8" t="n"/>
       <c r="N30" s="8" t="n"/>
+      <c r="O30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -14772,6 +17468,7 @@
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="n"/>
       <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
@@ -14788,6 +17485,7 @@
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n"/>
+      <c r="O32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -14804,6 +17502,7 @@
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="n"/>
       <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
@@ -14820,6 +17519,7 @@
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="n"/>
+      <c r="O34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -14836,6 +17536,7 @@
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
@@ -14852,6 +17553,7 @@
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n"/>
+      <c r="O36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -14868,6 +17570,7 @@
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="3" t="n"/>
       <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
@@ -14884,6 +17587,7 @@
       <c r="L38" s="8" t="n"/>
       <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n"/>
+      <c r="O38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -14900,6 +17604,7 @@
       <c r="L39" s="3" t="n"/>
       <c r="M39" s="3" t="n"/>
       <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
@@ -14916,6 +17621,7 @@
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n"/>
+      <c r="O40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -14932,6 +17638,7 @@
       <c r="L41" s="3" t="n"/>
       <c r="M41" s="3" t="n"/>
       <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n"/>
@@ -14948,6 +17655,7 @@
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n"/>
+      <c r="O42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -14964,6 +17672,7 @@
       <c r="L43" s="3" t="n"/>
       <c r="M43" s="3" t="n"/>
       <c r="N43" s="3" t="n"/>
+      <c r="O43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n"/>
@@ -14980,6 +17689,7 @@
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n"/>
+      <c r="O44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -14996,6 +17706,7 @@
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="n"/>
+      <c r="O45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n"/>
@@ -15012,6 +17723,7 @@
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
       <c r="N46" s="8" t="n"/>
+      <c r="O46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -15028,6 +17740,7 @@
       <c r="L47" s="3" t="n"/>
       <c r="M47" s="3" t="n"/>
       <c r="N47" s="3" t="n"/>
+      <c r="O47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n"/>
@@ -15044,6 +17757,7 @@
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="n"/>
       <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -15060,6 +17774,7 @@
       <c r="L49" s="3" t="n"/>
       <c r="M49" s="3" t="n"/>
       <c r="N49" s="3" t="n"/>
+      <c r="O49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n"/>
@@ -15076,6 +17791,7 @@
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n"/>
+      <c r="O50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -15092,6 +17808,7 @@
       <c r="L51" s="3" t="n"/>
       <c r="M51" s="3" t="n"/>
       <c r="N51" s="3" t="n"/>
+      <c r="O51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>
@@ -15108,6 +17825,7 @@
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n"/>
+      <c r="O52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -15124,6 +17842,7 @@
       <c r="L53" s="3" t="n"/>
       <c r="M53" s="3" t="n"/>
       <c r="N53" s="3" t="n"/>
+      <c r="O53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n"/>
@@ -15140,6 +17859,7 @@
       <c r="L54" s="8" t="n"/>
       <c r="M54" s="8" t="n"/>
       <c r="N54" s="8" t="n"/>
+      <c r="O54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -15156,6 +17876,7 @@
       <c r="L55" s="3" t="n"/>
       <c r="M55" s="3" t="n"/>
       <c r="N55" s="3" t="n"/>
+      <c r="O55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n"/>
@@ -15172,6 +17893,7 @@
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n"/>
+      <c r="O56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n"/>
@@ -15188,6 +17910,7 @@
       <c r="L57" s="3" t="n"/>
       <c r="M57" s="3" t="n"/>
       <c r="N57" s="3" t="n"/>
+      <c r="O57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n"/>
@@ -15204,6 +17927,7 @@
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n"/>
+      <c r="O58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
@@ -15220,6 +17944,7 @@
       <c r="L59" s="3" t="n"/>
       <c r="M59" s="3" t="n"/>
       <c r="N59" s="3" t="n"/>
+      <c r="O59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
@@ -15236,6 +17961,7 @@
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n"/>
+      <c r="O60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
@@ -15252,6 +17978,7 @@
       <c r="L61" s="3" t="n"/>
       <c r="M61" s="3" t="n"/>
       <c r="N61" s="3" t="n"/>
+      <c r="O61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n"/>
@@ -15268,6 +17995,7 @@
       <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n"/>
+      <c r="O62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
@@ -15284,6 +18012,7 @@
       <c r="L63" s="3" t="n"/>
       <c r="M63" s="3" t="n"/>
       <c r="N63" s="3" t="n"/>
+      <c r="O63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n"/>
@@ -15300,6 +18029,7 @@
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n"/>
+      <c r="O64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
@@ -15316,6 +18046,7 @@
       <c r="L65" s="3" t="n"/>
       <c r="M65" s="3" t="n"/>
       <c r="N65" s="3" t="n"/>
+      <c r="O65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n"/>
@@ -15332,6 +18063,7 @@
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n"/>
+      <c r="O66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
@@ -15348,6 +18080,7 @@
       <c r="L67" s="3" t="n"/>
       <c r="M67" s="3" t="n"/>
       <c r="N67" s="3" t="n"/>
+      <c r="O67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n"/>
@@ -15364,6 +18097,7 @@
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n"/>
+      <c r="O68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n"/>
@@ -15380,6 +18114,7 @@
       <c r="L69" s="3" t="n"/>
       <c r="M69" s="3" t="n"/>
       <c r="N69" s="3" t="n"/>
+      <c r="O69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n"/>
@@ -15396,6 +18131,7 @@
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n"/>
+      <c r="O70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -15412,6 +18148,7 @@
       <c r="L71" s="3" t="n"/>
       <c r="M71" s="3" t="n"/>
       <c r="N71" s="3" t="n"/>
+      <c r="O71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n"/>
@@ -15428,6 +18165,7 @@
       <c r="L72" s="8" t="n"/>
       <c r="M72" s="8" t="n"/>
       <c r="N72" s="8" t="n"/>
+      <c r="O72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
@@ -15444,6 +18182,7 @@
       <c r="L73" s="3" t="n"/>
       <c r="M73" s="3" t="n"/>
       <c r="N73" s="3" t="n"/>
+      <c r="O73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n"/>
@@ -15460,6 +18199,7 @@
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
       <c r="N74" s="8" t="n"/>
+      <c r="O74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
@@ -15476,6 +18216,7 @@
       <c r="L75" s="3" t="n"/>
       <c r="M75" s="3" t="n"/>
       <c r="N75" s="3" t="n"/>
+      <c r="O75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n"/>
@@ -15492,6 +18233,7 @@
       <c r="L76" s="8" t="n"/>
       <c r="M76" s="8" t="n"/>
       <c r="N76" s="8" t="n"/>
+      <c r="O76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
@@ -15508,6 +18250,7 @@
       <c r="L77" s="3" t="n"/>
       <c r="M77" s="3" t="n"/>
       <c r="N77" s="3" t="n"/>
+      <c r="O77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n"/>
@@ -15524,6 +18267,7 @@
       <c r="L78" s="8" t="n"/>
       <c r="M78" s="8" t="n"/>
       <c r="N78" s="8" t="n"/>
+      <c r="O78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
@@ -15540,6 +18284,7 @@
       <c r="L79" s="3" t="n"/>
       <c r="M79" s="3" t="n"/>
       <c r="N79" s="3" t="n"/>
+      <c r="O79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n"/>
@@ -15556,6 +18301,7 @@
       <c r="L80" s="8" t="n"/>
       <c r="M80" s="8" t="n"/>
       <c r="N80" s="8" t="n"/>
+      <c r="O80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
@@ -15572,10 +18318,11 @@
       <c r="L81" s="3" t="n"/>
       <c r="M81" s="3" t="n"/>
       <c r="N81" s="3" t="n"/>
+      <c r="O81" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N81"/>
-  <dataValidations count="5">
+  <autoFilter ref="A1:O81"/>
+  <dataValidations count="6">
     <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=List_Experiment_ID</formula1>
     </dataValidation>
@@ -15591,6 +18338,9 @@
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=List_Reuse_Policy</formula1>
     </dataValidation>
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Search_Space_ID</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -15600,6 +18350,816 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Search Space Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>search_space_id</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>optimization_mode</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>parameter_name</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>parameter_values</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>parameter_scope</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>objective_metric</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>max_trials</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SS01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>deterministic_grid</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>ridge|logreg|linearsvc</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>balanced_accuracy</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Example model-family search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>SS01</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>deterministic_grid</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>start_section</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>dataset_selection|feature_matrix_load</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>balanced_accuracy</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Example section-start search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n"/>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n"/>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n"/>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n"/>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n"/>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n"/>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n"/>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="8" t="n"/>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n"/>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n"/>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:I61"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B3:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_YesNo</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Search_Optimization_Mode</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=List_Search_Parameter_Scope</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16403,7 +19963,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17057,7 +20617,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17766,7 +21326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18457,7 +22017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19263,1519 +22823,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Data_Slice_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Slice_Name</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>Subject_Scope</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Session_Scope</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Time_Window</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Task_Scope</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Modality_Scope</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>Target_Type</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>Label_Set</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>Inclusion_Rule</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>Exclusion_Rule</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>Class_Balance_Policy</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>Minimum_Samples_Rule</t>
-        </is>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
-        <is>
-          <t>Leakage_Risk</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
-        <is>
-          <t>Valid_Use_Case</t>
-        </is>
-      </c>
-      <c r="Q1" s="7" t="inlineStr">
-        <is>
-          <t>Thesis_Use</t>
-        </is>
-      </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>DS01</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>All subjects, all sessions, pooled task, pooled modality, coarse_affect</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Global baseline for target/split/model method-choice comparisons.</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>all_subjects</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>all_sessions</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>full_study_window</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>pooled_all_tasks</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>pooled_all_modalities</t>
-        </is>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>All QC-passed repeated-session beta maps with valid labels.</t>
-        </is>
-      </c>
-      <c r="L2" s="8" t="inlineStr">
-        <is>
-          <t>Drop failed-preprocessing rows and missing targets.</t>
-        </is>
-      </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>as_is</t>
-        </is>
-      </c>
-      <c r="N2" s="8" t="inlineStr">
-        <is>
-          <t>Prefer &gt;=20 per class before claim-level interpretation.</t>
-        </is>
-      </c>
-      <c r="O2" s="8" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="P2" s="8" t="inlineStr">
-        <is>
-          <t>method_choice</t>
-        </is>
-      </c>
-      <c r="Q2" s="8" t="inlineStr">
-        <is>
-          <t>method_choice</t>
-        </is>
-      </c>
-      <c r="R2" s="8" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>DS02</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Subject-specific pooled-task pooled-modality</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Primary within-person held-out-session claim support.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>single_subject</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>held_out_session</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>full_study_window</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>pooled_all_tasks</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>pooled_all_modalities</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>One subject at a time with all eligible sessions.</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>No cross-subject pooling inside fold-level fit.</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>weighted_only</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Per-class floor checked per subject.</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>confirmatory_within_person</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>main_confirmatory</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>Matches held-out-session inference boundary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>DS03</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Task-specific pooled-modality</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Task pooling vs task-specific method-choice and diagnostics.</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>all_subjects</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>all_sessions</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>full_study_window</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>task_specific_other</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>pooled_all_modalities</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>coarse_affect by task</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>Restrict each run to one task family.</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>Exclude off-task records for that run.</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>as_is</t>
-        </is>
-      </c>
-      <c r="N4" s="8" t="inlineStr">
-        <is>
-          <t>Minimum counts checked per task-specific slice.</t>
-        </is>
-      </c>
-      <c r="O4" s="8" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="P4" s="8" t="inlineStr">
-        <is>
-          <t>method_choice</t>
-        </is>
-      </c>
-      <c r="Q4" s="8" t="inlineStr">
-        <is>
-          <t>method_choice</t>
-        </is>
-      </c>
-      <c r="R4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>DS04</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Modality-specific pooled-task</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Modality pooling vs modality-specific method-choice checks.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>all_subjects</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>all_sessions</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>full_study_window</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>pooled_all_tasks</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>audio_only</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>One modality family per run (audio/video/audiovisual variants).</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Exclude other modalities in each modality-specific run.</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>as_is</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>Check sample sufficiency per modality variant.</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>method_choice</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>method_choice</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>Seed modality is audio_only; clone row for other modalities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>DS05</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Subject-specific task x modality subset</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Fine-grained diagnostic sensitivity slices.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>single_subject</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>all_sessions</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>full_study_window</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>task_specific_other</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>audiovisual_only</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>Single subject + selected task + selected modality combination.</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>Exclude all records outside the chosen intersection.</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>min_count_threshold</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>Hard floor required before reporting.</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>diagnostic_only</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t>discussion_limitations</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>DS06</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Early sessions only</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Temporal drift checks and early-to-late transfer design.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>all_subjects</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>early_only</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>early_window</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>pooled_all_tasks</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>pooled_all_modalities</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Use sessions pre-registered as early window.</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Exclude late-window sessions.</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>as_is</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>Check class floor by temporal window.</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>robustness_support</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>supporting_robustness</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>DS07</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Late sessions only</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Temporal drift checks and early-to-late transfer design.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>all_subjects</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>late_only</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>late_window</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>pooled_all_tasks</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>pooled_all_modalities</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>Use sessions pre-registered as late window.</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>Exclude early-window sessions.</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>as_is</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>Check class floor by temporal window.</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>robustness_support</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>supporting_robustness</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>DS08</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Balanced subset only</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Imbalance-aware sensitivity diagnostics.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>all_subjects</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>all_sessions</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>full_study_window</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>pooled_all_tasks</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>pooled_all_modalities</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>coarse_affect</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Only include rows passing balancing policy.</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Exclude classes below predefined minimum count floor.</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>balanced_subset</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Set explicit class floor in analysis config.</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>robustness_support</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>supporting_robustness</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>Do not replace confirmatory as-is evidence with this slice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
-      <c r="O10" s="8" t="n"/>
-      <c r="P10" s="8" t="n"/>
-      <c r="Q10" s="8" t="n"/>
-      <c r="R10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
-      <c r="R11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
-      <c r="O12" s="8" t="n"/>
-      <c r="P12" s="8" t="n"/>
-      <c r="Q12" s="8" t="n"/>
-      <c r="R12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
-      <c r="P14" s="8" t="n"/>
-      <c r="Q14" s="8" t="n"/>
-      <c r="R14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="n"/>
-      <c r="R15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
-      <c r="P16" s="8" t="n"/>
-      <c r="Q16" s="8" t="n"/>
-      <c r="R16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
-      <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
-      <c r="O18" s="8" t="n"/>
-      <c r="P18" s="8" t="n"/>
-      <c r="Q18" s="8" t="n"/>
-      <c r="R18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
-      <c r="R19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
-      <c r="P20" s="8" t="n"/>
-      <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n"/>
-      <c r="O22" s="8" t="n"/>
-      <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="3" t="n"/>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
-      <c r="O24" s="8" t="n"/>
-      <c r="P24" s="8" t="n"/>
-      <c r="Q24" s="8" t="n"/>
-      <c r="R24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
-      <c r="L26" s="8" t="n"/>
-      <c r="M26" s="8" t="n"/>
-      <c r="N26" s="8" t="n"/>
-      <c r="O26" s="8" t="n"/>
-      <c r="P26" s="8" t="n"/>
-      <c r="Q26" s="8" t="n"/>
-      <c r="R26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="n"/>
-      <c r="Q27" s="3" t="n"/>
-      <c r="R27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="8" t="n"/>
-      <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
-      <c r="N28" s="8" t="n"/>
-      <c r="O28" s="8" t="n"/>
-      <c r="P28" s="8" t="n"/>
-      <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="n"/>
-      <c r="Q29" s="3" t="n"/>
-      <c r="R29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
-      <c r="M30" s="8" t="n"/>
-      <c r="N30" s="8" t="n"/>
-      <c r="O30" s="8" t="n"/>
-      <c r="P30" s="8" t="n"/>
-      <c r="Q30" s="8" t="n"/>
-      <c r="R30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
-      <c r="P31" s="3" t="n"/>
-      <c r="Q31" s="3" t="n"/>
-      <c r="R31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n"/>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
-      <c r="M32" s="8" t="n"/>
-      <c r="N32" s="8" t="n"/>
-      <c r="O32" s="8" t="n"/>
-      <c r="P32" s="8" t="n"/>
-      <c r="Q32" s="8" t="n"/>
-      <c r="R32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n"/>
-      <c r="Q33" s="3" t="n"/>
-      <c r="R33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
-      <c r="L34" s="8" t="n"/>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="8" t="n"/>
-      <c r="O34" s="8" t="n"/>
-      <c r="P34" s="8" t="n"/>
-      <c r="Q34" s="8" t="n"/>
-      <c r="R34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="n"/>
-      <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
-      <c r="L36" s="8" t="n"/>
-      <c r="M36" s="8" t="n"/>
-      <c r="N36" s="8" t="n"/>
-      <c r="O36" s="8" t="n"/>
-      <c r="P36" s="8" t="n"/>
-      <c r="Q36" s="8" t="n"/>
-      <c r="R36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3" t="n"/>
-      <c r="P37" s="3" t="n"/>
-      <c r="Q37" s="3" t="n"/>
-      <c r="R37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="n"/>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-      <c r="L38" s="8" t="n"/>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="8" t="n"/>
-      <c r="O38" s="8" t="n"/>
-      <c r="P38" s="8" t="n"/>
-      <c r="Q38" s="8" t="n"/>
-      <c r="R38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n"/>
-      <c r="P39" s="3" t="n"/>
-      <c r="Q39" s="3" t="n"/>
-      <c r="R39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
-      <c r="L40" s="8" t="n"/>
-      <c r="M40" s="8" t="n"/>
-      <c r="N40" s="8" t="n"/>
-      <c r="O40" s="8" t="n"/>
-      <c r="P40" s="8" t="n"/>
-      <c r="Q40" s="8" t="n"/>
-      <c r="R40" s="8" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
-      <c r="P41" s="3" t="n"/>
-      <c r="Q41" s="3" t="n"/>
-      <c r="R41" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:R41"/>
-  <dataValidations count="9">
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Subject_Scope</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Session_Scope</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Task_Scope</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Modality_Scope</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Target_Type</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Class_Balance_Policy</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Leakage_Risk_Level</formula1>
-    </dataValidation>
-    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Use_Case</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=List_Thesis_Use_Tag</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>